--- a/ceramica_proyecto.xlsx
+++ b/ceramica_proyecto.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29103"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29108"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Camero\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F2B6DC3D-D6DF-4544-AA05-152944131E24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{67D89B04-FA05-4E94-B403-56B6AF243218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" xr2:uid="{6A0D054A-EA90-43D3-9946-5E896568E0A7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{6A0D054A-EA90-43D3-9946-5E896568E0A7}"/>
   </bookViews>
   <sheets>
     <sheet name="EXISTENCIA TOTAL" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1435" uniqueCount="638">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1435" uniqueCount="637">
   <si>
     <t>EAN</t>
   </si>
@@ -4032,76 +4032,73 @@
     <t>LAMA CLICK FOLK 3.2MM ROBLE NATURAL 122X15</t>
   </si>
   <si>
+    <t>ADINA SPC CLICK 5MM ROBLE NATURAL 122X23</t>
+  </si>
+  <si>
+    <t>LAMA CLICK ELIZA 4MM ROBLE GRIS CLARO 122X15</t>
+  </si>
+  <si>
+    <t>LAMA CLICK ELIZA 4MM ROBLE GRIS MARRON 122X15</t>
+  </si>
+  <si>
+    <t>LAMA CLICK ELIZA 4MM RAYAS MULTIPLES 122X15</t>
+  </si>
+  <si>
+    <t>LOSETA CLICK FOLK GRIS 3.2MM 30X60</t>
+  </si>
+  <si>
+    <t>LOSETA CLICK ELIZA 4MM GRIS CLARO 30X60</t>
+  </si>
+  <si>
+    <t>LOSETA CLICK ELIZA 4MM MOSAICO 30X60</t>
+  </si>
+  <si>
+    <t>LAMA PVC ROBLE RUSTICO 1.8MM 91X15</t>
+  </si>
+  <si>
+    <t>LOSETA PVC SLATE 1.2MM 30X30</t>
+  </si>
+  <si>
+    <t>LOSETA PVC GRIS 1.2MM 30X30</t>
+  </si>
+  <si>
+    <t>LOSETA PVC MULTI 2MM 30X60</t>
+  </si>
+  <si>
+    <t>LOSETA PVC GRIS OSCURO 2MM 30X60</t>
+  </si>
+  <si>
+    <t>#A LOSETA PVC BEIGE 2MM 30X60</t>
+  </si>
+  <si>
+    <t>HARMONIA SPC CLICK 5,5 MM ROBLE GRIS 122X18</t>
+  </si>
+  <si>
+    <t>HARMONIA SPC CLICK 5,5 MM ROBLE</t>
+  </si>
+  <si>
+    <t>HARMONIA SPC CLICK 5,5 MM ROBLE BLANCO 122X18</t>
+  </si>
+  <si>
+    <t>HARMONIA SPC CLICK 5,5 MM ROBLE VINTAGE 122X18</t>
+  </si>
+  <si>
+    <t>HARMONIA SPC CLICK 5,5 MM ROBLE NORDICO 122X18</t>
+  </si>
+  <si>
+    <t>LAMA PVC ROBLE BLANCO 2MM 91X15</t>
+  </si>
+  <si>
+    <t>LAMA PVC ROBLE MIEL 2MM 91X15</t>
+  </si>
+  <si>
+    <t>LAMA PVC GRIS CLARO 2MM 91X15</t>
+  </si>
+  <si>
+    <t>LLAMINADO OPP AC3 6MM 129X19</t>
+  </si>
+  <si>
     <t>RACK 07</t>
-  </si>
-  <si>
-    <t>ADINA SPC CLICK 5MM ROBLE NATURAL 122X23</t>
-  </si>
-  <si>
-    <t>LAMA CLICK ELIZA 4MM ROBLE GRIS CLARO 122X15</t>
-  </si>
-  <si>
-    <t>LAMA CLICK ELIZA 4MM ROBLE GRIS MARRON 122X15</t>
-  </si>
-  <si>
-    <t>LAMA CLICK ELIZA 4MM RAYAS MULTIPLES 122X15</t>
-  </si>
-  <si>
-    <t>LOSETA CLICK FOLK GRIS 3.2MM 30X60</t>
-  </si>
-  <si>
-    <t>LOSETA CLICK ELIZA 4MM GRIS CLARO 30X60</t>
-  </si>
-  <si>
-    <t>LOSETA CLICK ELIZA 4MM MOSAICO 30X60</t>
-  </si>
-  <si>
-    <t>LAMA PVC ROBLE RUSTICO 1.8MM 91X15</t>
-  </si>
-  <si>
-    <t>LOSETA PVC SLATE 1.2MM 30X30</t>
-  </si>
-  <si>
-    <t>LOSETA PVC GRIS 1.2MM 30X30</t>
-  </si>
-  <si>
-    <t>LOSETA PVC MULTI 2MM 30X60</t>
-  </si>
-  <si>
-    <t>LOSETA PVC GRIS OSCURO 2MM 30X60</t>
-  </si>
-  <si>
-    <t>#A LOSETA PVC BEIGE 2MM 30X60</t>
-  </si>
-  <si>
-    <t>HARMONIA SPC CLICK 5,5 MM ROBLE GRIS 122X18</t>
-  </si>
-  <si>
-    <t>HARMONIA SPC CLICK 5,5 MM ROBLE</t>
-  </si>
-  <si>
-    <t>HARMONIA SPC CLICK 5,5 MM ROBLE BLANCO 122X18</t>
-  </si>
-  <si>
-    <t>HARMONIA SPC CLICK 5,5 MM ROBLE VINTAGE 122X18</t>
-  </si>
-  <si>
-    <t>HARMONIA SPC CLICK 5,5 MM ROBLE NORDICO 122X18</t>
-  </si>
-  <si>
-    <t>LAMA PVC ROBLE BLANCO 2MM 91X15</t>
-  </si>
-  <si>
-    <t>LAMA PVC ROBLE MIEL 2MM 91X15</t>
-  </si>
-  <si>
-    <t>LAMA PVC GRIS CLARO 2MM 91X15</t>
-  </si>
-  <si>
-    <t>LLAMINADO OPP AC3 6MM 129X19</t>
-  </si>
-  <si>
-    <t>RACK 06</t>
   </si>
   <si>
     <t>SUELO LAM. ELICIA AC5 8MM ROBLE GRIS 138X19</t>
@@ -4344,7 +4341,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4404,7 +4401,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4412,9 +4408,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4427,13 +4420,6 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5281,7 +5267,7 @@
     <col min="9" max="9" width="12.140625" style="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75">
+    <row r="1" spans="1:10">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -8199,7 +8185,7 @@
         <v>28-06-203</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="16.5">
+    <row r="76" spans="1:10" ht="15.75">
       <c r="A76" s="20">
         <v>5063022638397</v>
       </c>
@@ -11475,7 +11461,7 @@
         <v>24-01-102</v>
       </c>
     </row>
-    <row r="160" spans="1:10" ht="16.5">
+    <row r="160" spans="1:10" ht="15.75">
       <c r="A160" s="20">
         <v>5059340459912</v>
       </c>
@@ -11514,7 +11500,7 @@
         <v>28-05-202</v>
       </c>
     </row>
-    <row r="161" spans="1:10" ht="16.5">
+    <row r="161" spans="1:10" ht="15.75">
       <c r="A161" s="20">
         <v>3663602678298</v>
       </c>
@@ -11892,7 +11878,7 @@
         <v>28-04-403</v>
       </c>
     </row>
-    <row r="171" spans="1:10" ht="18.75">
+    <row r="171" spans="1:10" ht="15.75">
       <c r="A171" s="33">
         <v>3663602678465</v>
       </c>
@@ -12040,27 +12026,27 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="175" spans="1:10" ht="32.25">
-      <c r="A175" s="44">
+    <row r="175" spans="1:10" ht="15.75">
+      <c r="A175" s="40">
         <v>5059340194073</v>
       </c>
-      <c r="B175" s="46" t="s">
+      <c r="B175" s="42" t="s">
         <v>183</v>
       </c>
       <c r="C175" s="14"/>
-      <c r="D175" s="48" t="str">
-        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="E175" s="48" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 06</v>
-      </c>
-      <c r="F175" s="48" t="str">
+      <c r="D175" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E175" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 07</v>
+      </c>
+      <c r="F175" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
         <v>MODULO 2</v>
       </c>
-      <c r="G175" s="48" t="str">
+      <c r="G175" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
         <v>FILA 5</v>
       </c>
@@ -12068,11 +12054,11 @@
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>SI</v>
       </c>
-      <c r="I175" s="49" t="str">
-        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>NO</v>
-      </c>
-      <c r="J175" s="50" t="str">
+      <c r="I175" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J175" s="13" t="str">
         <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
         <v>28-03-101</v>
       </c>
@@ -12085,19 +12071,19 @@
         <v>184</v>
       </c>
       <c r="C176" s="14"/>
-      <c r="D176" s="48" t="str">
-        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="E176" s="48" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 06</v>
-      </c>
-      <c r="F176" s="48" t="str">
+      <c r="D176" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E176" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 07</v>
+      </c>
+      <c r="F176" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
         <v>MODULO 1</v>
       </c>
-      <c r="G176" s="48" t="str">
+      <c r="G176" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
         <v>FILA 4</v>
       </c>
@@ -12105,36 +12091,36 @@
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>SI</v>
       </c>
-      <c r="I176" s="49" t="str">
-        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>NO</v>
-      </c>
-      <c r="J176" s="50" t="str">
+      <c r="I176" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J176" s="13" t="str">
         <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
         <v>28-03-102</v>
       </c>
     </row>
-    <row r="177" spans="1:10" ht="32.25">
-      <c r="A177" s="44">
+    <row r="177" spans="1:10" ht="15.75">
+      <c r="A177" s="40">
         <v>5059340194097</v>
       </c>
-      <c r="B177" s="46" t="s">
+      <c r="B177" s="42" t="s">
         <v>185</v>
       </c>
       <c r="C177" s="14"/>
-      <c r="D177" s="48" t="str">
-        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="E177" s="48" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 06</v>
-      </c>
-      <c r="F177" s="48" t="str">
+      <c r="D177" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E177" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 07</v>
+      </c>
+      <c r="F177" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
         <v>MODULO 1</v>
       </c>
-      <c r="G177" s="48" t="str">
+      <c r="G177" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
         <v>FILA 5</v>
       </c>
@@ -12142,36 +12128,36 @@
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>SI</v>
       </c>
-      <c r="I177" s="49" t="str">
-        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>NO</v>
-      </c>
-      <c r="J177" s="50" t="str">
+      <c r="I177" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J177" s="13" t="str">
         <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
         <v>28-03-103</v>
       </c>
     </row>
-    <row r="178" spans="1:10" ht="32.25">
-      <c r="A178" s="45">
+    <row r="178" spans="1:10" ht="15.75">
+      <c r="A178" s="41">
         <v>3663602997962</v>
       </c>
-      <c r="B178" s="47" t="s">
+      <c r="B178" s="43" t="s">
         <v>186</v>
       </c>
       <c r="C178" s="14"/>
-      <c r="D178" s="48" t="str">
-        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="E178" s="48" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 06</v>
-      </c>
-      <c r="F178" s="48" t="str">
+      <c r="D178" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E178" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 07</v>
+      </c>
+      <c r="F178" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
         <v>MODULO 1</v>
       </c>
-      <c r="G178" s="48" t="str">
+      <c r="G178" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
         <v>FILA 2</v>
       </c>
@@ -12179,36 +12165,36 @@
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>SI</v>
       </c>
-      <c r="I178" s="49" t="str">
-        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>NO</v>
-      </c>
-      <c r="J178" s="50" t="str">
+      <c r="I178" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J178" s="13" t="str">
         <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
         <v>28-03-201</v>
       </c>
     </row>
-    <row r="179" spans="1:10" ht="16.5">
-      <c r="A179" s="44">
+    <row r="179" spans="1:10" ht="15.75">
+      <c r="A179" s="40">
         <v>5059340484303</v>
       </c>
-      <c r="B179" s="46" t="s">
+      <c r="B179" s="42" t="s">
         <v>187</v>
       </c>
       <c r="C179" s="14"/>
-      <c r="D179" s="48" t="str">
-        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="E179" s="48" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 06</v>
-      </c>
-      <c r="F179" s="48" t="str">
+      <c r="D179" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E179" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 07</v>
+      </c>
+      <c r="F179" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
         <v>MODULO 2</v>
       </c>
-      <c r="G179" s="48" t="str">
+      <c r="G179" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
         <v>FILA 4</v>
       </c>
@@ -12216,36 +12202,36 @@
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>SI</v>
       </c>
-      <c r="I179" s="49" t="str">
-        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>NO</v>
-      </c>
-      <c r="J179" s="50" t="str">
+      <c r="I179" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J179" s="13" t="str">
         <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
         <v>28-03-202</v>
       </c>
     </row>
-    <row r="180" spans="1:10" ht="16.5">
-      <c r="A180" s="44">
+    <row r="180" spans="1:10" ht="15.75">
+      <c r="A180" s="40">
         <v>5063022047816</v>
       </c>
-      <c r="B180" s="46" t="s">
+      <c r="B180" s="42" t="s">
         <v>188</v>
       </c>
       <c r="C180" s="14"/>
-      <c r="D180" s="48" t="str">
-        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="E180" s="48" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 06</v>
-      </c>
-      <c r="F180" s="48" t="str">
+      <c r="D180" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E180" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 07</v>
+      </c>
+      <c r="F180" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
         <v>MODULO 2</v>
       </c>
-      <c r="G180" s="48" t="str">
+      <c r="G180" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
         <v>FILA 4</v>
       </c>
@@ -12253,36 +12239,36 @@
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>SI</v>
       </c>
-      <c r="I180" s="49" t="str">
-        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>NO</v>
-      </c>
-      <c r="J180" s="50" t="str">
+      <c r="I180" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J180" s="13" t="str">
         <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
         <v>28-03-203</v>
       </c>
     </row>
-    <row r="181" spans="1:10" ht="32.25">
-      <c r="A181" s="44">
+    <row r="181" spans="1:10" ht="15.75">
+      <c r="A181" s="40">
         <v>5059340194035</v>
       </c>
-      <c r="B181" s="46" t="s">
+      <c r="B181" s="42" t="s">
         <v>189</v>
       </c>
       <c r="C181" s="14"/>
-      <c r="D181" s="48" t="str">
-        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="E181" s="48" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 06</v>
-      </c>
-      <c r="F181" s="48" t="str">
+      <c r="D181" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E181" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 07</v>
+      </c>
+      <c r="F181" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
         <v>MODULO 2</v>
       </c>
-      <c r="G181" s="48" t="str">
+      <c r="G181" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
         <v>FILA 5</v>
       </c>
@@ -12290,36 +12276,36 @@
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>SI</v>
       </c>
-      <c r="I181" s="49" t="str">
-        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>NO</v>
-      </c>
-      <c r="J181" s="50" t="str">
+      <c r="I181" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J181" s="13" t="str">
         <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
         <v>28-03-301</v>
       </c>
     </row>
-    <row r="182" spans="1:10" ht="32.25">
-      <c r="A182" s="44">
+    <row r="182" spans="1:10" ht="15.75">
+      <c r="A182" s="40">
         <v>5063022047755</v>
       </c>
-      <c r="B182" s="46" t="s">
+      <c r="B182" s="42" t="s">
         <v>190</v>
       </c>
       <c r="C182" s="14"/>
-      <c r="D182" s="48" t="str">
-        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="E182" s="48" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 06</v>
-      </c>
-      <c r="F182" s="48" t="str">
+      <c r="D182" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E182" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 07</v>
+      </c>
+      <c r="F182" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
         <v>MODULO 1</v>
       </c>
-      <c r="G182" s="48" t="str">
+      <c r="G182" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
         <v>FILA 3</v>
       </c>
@@ -12327,36 +12313,36 @@
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>SI</v>
       </c>
-      <c r="I182" s="49" t="str">
-        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>NO</v>
-      </c>
-      <c r="J182" s="50" t="str">
+      <c r="I182" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J182" s="13" t="str">
         <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
         <v>28-03-302</v>
       </c>
     </row>
-    <row r="183" spans="1:10" ht="16.5">
-      <c r="A183" s="44">
+    <row r="183" spans="1:10" ht="15.75">
+      <c r="A183" s="40">
         <v>5063022069450</v>
       </c>
-      <c r="B183" s="46" t="s">
+      <c r="B183" s="42" t="s">
         <v>191</v>
       </c>
       <c r="C183" s="14"/>
-      <c r="D183" s="48" t="str">
-        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="E183" s="48" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 06</v>
-      </c>
-      <c r="F183" s="48" t="str">
+      <c r="D183" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E183" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 07</v>
+      </c>
+      <c r="F183" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
         <v>MODULO 1</v>
       </c>
-      <c r="G183" s="48" t="str">
+      <c r="G183" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
         <v>FILA 2</v>
       </c>
@@ -12364,36 +12350,36 @@
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>SI</v>
       </c>
-      <c r="I183" s="49" t="str">
-        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>NO</v>
-      </c>
-      <c r="J183" s="50" t="str">
+      <c r="I183" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J183" s="13" t="str">
         <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
         <v>28-03-303</v>
       </c>
     </row>
-    <row r="184" spans="1:10" ht="32.25">
-      <c r="A184" s="44">
+    <row r="184" spans="1:10" ht="15.75">
+      <c r="A184" s="40">
         <v>5063022085658</v>
       </c>
-      <c r="B184" s="46" t="s">
+      <c r="B184" s="42" t="s">
         <v>192</v>
       </c>
       <c r="C184" s="14"/>
-      <c r="D184" s="48" t="str">
-        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="E184" s="48" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 06</v>
-      </c>
-      <c r="F184" s="48" t="str">
+      <c r="D184" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E184" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 07</v>
+      </c>
+      <c r="F184" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
         <v>MODULO 1</v>
       </c>
-      <c r="G184" s="48" t="str">
+      <c r="G184" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
         <v>FILA 1</v>
       </c>
@@ -12401,36 +12387,36 @@
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>SI</v>
       </c>
-      <c r="I184" s="49" t="str">
-        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>NO</v>
-      </c>
-      <c r="J184" s="50" t="str">
+      <c r="I184" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J184" s="13" t="str">
         <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
         <v>28-03-401</v>
       </c>
     </row>
-    <row r="185" spans="1:10" ht="16.5">
-      <c r="A185" s="44">
+    <row r="185" spans="1:10" ht="15.75">
+      <c r="A185" s="40">
         <v>5063022085603</v>
       </c>
-      <c r="B185" s="46" t="s">
+      <c r="B185" s="42" t="s">
         <v>193</v>
       </c>
       <c r="C185" s="14"/>
-      <c r="D185" s="48" t="str">
-        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="E185" s="48" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 06</v>
-      </c>
-      <c r="F185" s="48" t="str">
+      <c r="D185" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E185" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 07</v>
+      </c>
+      <c r="F185" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
         <v>MODULO 1</v>
       </c>
-      <c r="G185" s="48" t="str">
+      <c r="G185" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
         <v>FILA 4</v>
       </c>
@@ -12438,36 +12424,36 @@
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>SI</v>
       </c>
-      <c r="I185" s="49" t="str">
-        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>NO</v>
-      </c>
-      <c r="J185" s="50" t="str">
+      <c r="I185" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J185" s="13" t="str">
         <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
         <v>28-03-402</v>
       </c>
     </row>
-    <row r="186" spans="1:10" ht="32.25">
-      <c r="A186" s="44">
+    <row r="186" spans="1:10" ht="15.75">
+      <c r="A186" s="40">
         <v>5059340216034</v>
       </c>
-      <c r="B186" s="46" t="s">
+      <c r="B186" s="42" t="s">
         <v>194</v>
       </c>
       <c r="C186" s="14"/>
-      <c r="D186" s="48" t="str">
-        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="E186" s="48" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 06</v>
-      </c>
-      <c r="F186" s="48" t="str">
+      <c r="D186" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E186" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 07</v>
+      </c>
+      <c r="F186" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
         <v>MODULO 1</v>
       </c>
-      <c r="G186" s="48" t="str">
+      <c r="G186" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
         <v>FILA 5</v>
       </c>
@@ -12475,36 +12461,36 @@
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>SI</v>
       </c>
-      <c r="I186" s="49" t="str">
-        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>NO</v>
-      </c>
-      <c r="J186" s="50" t="str">
+      <c r="I186" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J186" s="13" t="str">
         <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
         <v>28-03-403</v>
       </c>
     </row>
-    <row r="187" spans="1:10" ht="32.25">
-      <c r="A187" s="44">
+    <row r="187" spans="1:10" ht="30">
+      <c r="A187" s="40">
         <v>5063022606068</v>
       </c>
-      <c r="B187" s="46" t="s">
+      <c r="B187" s="42" t="s">
         <v>195</v>
       </c>
       <c r="C187" s="14"/>
-      <c r="D187" s="48" t="str">
-        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="E187" s="48" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 06</v>
-      </c>
-      <c r="F187" s="48" t="str">
+      <c r="D187" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E187" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 07</v>
+      </c>
+      <c r="F187" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
         <v>MODULO 1</v>
       </c>
-      <c r="G187" s="48" t="str">
+      <c r="G187" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
         <v>FILA 3</v>
       </c>
@@ -12512,36 +12498,36 @@
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>SI</v>
       </c>
-      <c r="I187" s="49" t="str">
-        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>NO</v>
-      </c>
-      <c r="J187" s="50" t="str">
+      <c r="I187" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J187" s="13" t="str">
         <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
         <v>28-02-202</v>
       </c>
     </row>
-    <row r="188" spans="1:10" ht="32.25">
-      <c r="A188" s="44">
+    <row r="188" spans="1:10" ht="30">
+      <c r="A188" s="40">
         <v>5063022606020</v>
       </c>
-      <c r="B188" s="46" t="s">
+      <c r="B188" s="42" t="s">
         <v>196</v>
       </c>
       <c r="C188" s="14"/>
-      <c r="D188" s="48" t="str">
-        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="E188" s="48" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 06</v>
-      </c>
-      <c r="F188" s="48" t="str">
+      <c r="D188" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E188" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 07</v>
+      </c>
+      <c r="F188" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
         <v>MODULO 2</v>
       </c>
-      <c r="G188" s="48" t="str">
+      <c r="G188" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
         <v>FILA 3</v>
       </c>
@@ -12549,36 +12535,36 @@
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>SI</v>
       </c>
-      <c r="I188" s="49" t="str">
-        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>NO</v>
-      </c>
-      <c r="J188" s="50" t="str">
+      <c r="I188" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J188" s="13" t="str">
         <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
         <v>28-02-301</v>
       </c>
     </row>
-    <row r="189" spans="1:10" ht="32.25">
-      <c r="A189" s="44">
+    <row r="189" spans="1:10" ht="30">
+      <c r="A189" s="40">
         <v>5063022606037</v>
       </c>
-      <c r="B189" s="46" t="s">
+      <c r="B189" s="42" t="s">
         <v>197</v>
       </c>
       <c r="C189" s="14"/>
-      <c r="D189" s="48" t="str">
-        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="E189" s="48" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 06</v>
-      </c>
-      <c r="F189" s="48" t="str">
+      <c r="D189" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E189" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 07</v>
+      </c>
+      <c r="F189" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
         <v>MODULO 2</v>
       </c>
-      <c r="G189" s="48" t="str">
+      <c r="G189" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
         <v>FILA 3</v>
       </c>
@@ -12586,36 +12572,36 @@
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>SI</v>
       </c>
-      <c r="I189" s="49" t="str">
-        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>NO</v>
-      </c>
-      <c r="J189" s="50" t="str">
+      <c r="I189" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J189" s="13" t="str">
         <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
         <v>28-02-302</v>
       </c>
     </row>
-    <row r="190" spans="1:10" ht="32.25">
-      <c r="A190" s="44">
+    <row r="190" spans="1:10" ht="30">
+      <c r="A190" s="40">
         <v>5063022606013</v>
       </c>
-      <c r="B190" s="46" t="s">
+      <c r="B190" s="42" t="s">
         <v>198</v>
       </c>
       <c r="C190" s="14"/>
-      <c r="D190" s="48" t="str">
-        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="E190" s="48" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 06</v>
-      </c>
-      <c r="F190" s="48" t="str">
+      <c r="D190" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E190" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 07</v>
+      </c>
+      <c r="F190" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
         <v>MODULO 2</v>
       </c>
-      <c r="G190" s="48" t="str">
+      <c r="G190" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
         <v>FILA 3</v>
       </c>
@@ -12623,36 +12609,36 @@
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>SI</v>
       </c>
-      <c r="I190" s="49" t="str">
-        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>NO</v>
-      </c>
-      <c r="J190" s="50" t="str">
+      <c r="I190" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J190" s="13" t="str">
         <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
         <v>28-02-303</v>
       </c>
     </row>
-    <row r="191" spans="1:10" ht="32.25">
-      <c r="A191" s="44">
+    <row r="191" spans="1:10" ht="15.75">
+      <c r="A191" s="40">
         <v>5059340194080</v>
       </c>
-      <c r="B191" s="46" t="s">
+      <c r="B191" s="42" t="s">
         <v>199</v>
       </c>
       <c r="C191" s="14"/>
-      <c r="D191" s="48" t="str">
-        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="E191" s="48" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 06</v>
-      </c>
-      <c r="F191" s="48" t="str">
+      <c r="D191" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E191" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 07</v>
+      </c>
+      <c r="F191" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
         <v>MODULO 1</v>
       </c>
-      <c r="G191" s="48" t="str">
+      <c r="G191" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
         <v>FILA 4</v>
       </c>
@@ -12660,36 +12646,36 @@
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>SI</v>
       </c>
-      <c r="I191" s="49" t="str">
-        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>NO</v>
-      </c>
-      <c r="J191" s="50" t="str">
+      <c r="I191" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J191" s="13" t="str">
         <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
         <v>28-02-401</v>
       </c>
     </row>
-    <row r="192" spans="1:10" ht="32.25">
-      <c r="A192" s="44">
+    <row r="192" spans="1:10" ht="30">
+      <c r="A192" s="40">
         <v>5063022606525</v>
       </c>
-      <c r="B192" s="46" t="s">
+      <c r="B192" s="42" t="s">
         <v>200</v>
       </c>
       <c r="C192" s="14"/>
-      <c r="D192" s="48" t="str">
-        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="E192" s="48" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 06</v>
-      </c>
-      <c r="F192" s="48" t="str">
+      <c r="D192" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E192" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 07</v>
+      </c>
+      <c r="F192" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
         <v>MODULO 1</v>
       </c>
-      <c r="G192" s="48" t="str">
+      <c r="G192" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
         <v>FILA 2</v>
       </c>
@@ -12697,36 +12683,36 @@
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>SI</v>
       </c>
-      <c r="I192" s="49" t="str">
-        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>NO</v>
-      </c>
-      <c r="J192" s="50" t="str">
+      <c r="I192" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J192" s="13" t="str">
         <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
         <v>28-02-402</v>
       </c>
     </row>
-    <row r="193" spans="1:10" ht="16.5">
-      <c r="A193" s="44">
+    <row r="193" spans="1:10" ht="15.75">
+      <c r="A193" s="40">
         <v>5063022047823</v>
       </c>
-      <c r="B193" s="46" t="s">
+      <c r="B193" s="42" t="s">
         <v>201</v>
       </c>
       <c r="C193" s="14"/>
-      <c r="D193" s="48" t="str">
-        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="E193" s="48" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 06</v>
-      </c>
-      <c r="F193" s="48" t="str">
+      <c r="D193" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E193" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 07</v>
+      </c>
+      <c r="F193" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
         <v>MODULO 2</v>
       </c>
-      <c r="G193" s="48" t="str">
+      <c r="G193" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
         <v>FILA 5</v>
       </c>
@@ -12734,36 +12720,36 @@
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>SI</v>
       </c>
-      <c r="I193" s="49" t="str">
-        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>NO</v>
-      </c>
-      <c r="J193" s="50" t="str">
+      <c r="I193" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J193" s="13" t="str">
         <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
         <v>28-02-403</v>
       </c>
     </row>
     <row r="194" spans="1:10" ht="15.75">
-      <c r="A194" s="41">
+      <c r="A194" s="9">
         <v>5059340194042</v>
       </c>
-      <c r="B194" s="42" t="s">
+      <c r="B194" s="10" t="s">
         <v>202</v>
       </c>
       <c r="C194" s="14"/>
-      <c r="D194" s="48" t="str">
-        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="E194" s="48" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 06</v>
-      </c>
-      <c r="F194" s="48" t="str">
+      <c r="D194" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E194" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 07</v>
+      </c>
+      <c r="F194" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
         <v>MODULO 1</v>
       </c>
-      <c r="G194" s="48" t="str">
+      <c r="G194" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
         <v>FILA 3</v>
       </c>
@@ -12771,36 +12757,36 @@
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>NO</v>
       </c>
-      <c r="I194" s="49" t="str">
-        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="J194" s="50" t="str">
+      <c r="I194" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="J194" s="13" t="str">
         <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
         <v>22-11-101</v>
       </c>
     </row>
     <row r="195" spans="1:10" ht="15.75">
-      <c r="A195" s="41">
+      <c r="A195" s="9">
         <v>5063022085641</v>
       </c>
-      <c r="B195" s="42" t="s">
+      <c r="B195" s="10" t="s">
         <v>203</v>
       </c>
       <c r="C195" s="14"/>
-      <c r="D195" s="48" t="str">
-        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="E195" s="48" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 06</v>
-      </c>
-      <c r="F195" s="48" t="str">
+      <c r="D195" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E195" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 07</v>
+      </c>
+      <c r="F195" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
         <v>MODULO 2</v>
       </c>
-      <c r="G195" s="48" t="str">
+      <c r="G195" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
         <v>FILA 1</v>
       </c>
@@ -12808,36 +12794,36 @@
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>NO</v>
       </c>
-      <c r="I195" s="49" t="str">
-        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="J195" s="50" t="str">
+      <c r="I195" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="J195" s="13" t="str">
         <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
         <v>22-11-102</v>
       </c>
     </row>
     <row r="196" spans="1:10" ht="15.75">
-      <c r="A196" s="41">
+      <c r="A196" s="9">
         <v>5063022047830</v>
       </c>
-      <c r="B196" s="42" t="s">
+      <c r="B196" s="10" t="s">
         <v>204</v>
       </c>
       <c r="C196" s="14"/>
-      <c r="D196" s="48" t="str">
-        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="E196" s="48" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 06</v>
-      </c>
-      <c r="F196" s="48" t="str">
+      <c r="D196" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E196" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 07</v>
+      </c>
+      <c r="F196" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
         <v>MODULO 2</v>
       </c>
-      <c r="G196" s="48" t="str">
+      <c r="G196" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
         <v>FILA 1</v>
       </c>
@@ -12845,36 +12831,36 @@
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>NO</v>
       </c>
-      <c r="I196" s="49" t="str">
-        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="J196" s="50" t="str">
+      <c r="I196" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="J196" s="13" t="str">
         <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
         <v>22-11-103</v>
       </c>
     </row>
     <row r="197" spans="1:10" ht="15.75">
-      <c r="A197" s="41">
+      <c r="A197" s="9">
         <v>3663602997436</v>
       </c>
-      <c r="B197" s="42" t="s">
+      <c r="B197" s="10" t="s">
         <v>205</v>
       </c>
       <c r="C197" s="14"/>
-      <c r="D197" s="48" t="str">
-        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="E197" s="48" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 06</v>
-      </c>
-      <c r="F197" s="48" t="str">
+      <c r="D197" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E197" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 07</v>
+      </c>
+      <c r="F197" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
         <v>MODULO 1</v>
       </c>
-      <c r="G197" s="48" t="str">
+      <c r="G197" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
         <v>FILA 1</v>
       </c>
@@ -12882,36 +12868,36 @@
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>NO</v>
       </c>
-      <c r="I197" s="49" t="str">
-        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="J197" s="50" t="str">
+      <c r="I197" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="J197" s="13" t="str">
         <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
         <v>22-12-101</v>
       </c>
     </row>
     <row r="198" spans="1:10" ht="15.75">
-      <c r="A198" s="41">
+      <c r="A198" s="9">
         <v>5063022047847</v>
       </c>
-      <c r="B198" s="42" t="s">
+      <c r="B198" s="10" t="s">
         <v>206</v>
       </c>
       <c r="C198" s="14"/>
-      <c r="D198" s="48" t="str">
-        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="E198" s="48" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 06</v>
-      </c>
-      <c r="F198" s="48" t="str">
+      <c r="D198" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E198" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 07</v>
+      </c>
+      <c r="F198" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
         <v>MODULO 1</v>
       </c>
-      <c r="G198" s="48" t="str">
+      <c r="G198" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
         <v>FILA 1</v>
       </c>
@@ -12919,36 +12905,36 @@
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>NO</v>
       </c>
-      <c r="I198" s="49" t="str">
-        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="J198" s="50" t="str">
+      <c r="I198" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="J198" s="13" t="str">
         <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
         <v>22-12-102</v>
       </c>
     </row>
     <row r="199" spans="1:10" ht="15.75">
-      <c r="A199" s="41">
+      <c r="A199" s="9">
         <v>5059340391441</v>
       </c>
-      <c r="B199" s="42" t="s">
+      <c r="B199" s="10" t="s">
         <v>207</v>
       </c>
       <c r="C199" s="14"/>
-      <c r="D199" s="48" t="str">
-        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="E199" s="48" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 06</v>
-      </c>
-      <c r="F199" s="48" t="str">
+      <c r="D199" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E199" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 07</v>
+      </c>
+      <c r="F199" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
         <v>MODULO 2</v>
       </c>
-      <c r="G199" s="48" t="str">
+      <c r="G199" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
         <v>FILA 2</v>
       </c>
@@ -12956,36 +12942,36 @@
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>NO</v>
       </c>
-      <c r="I199" s="49" t="str">
-        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="J199" s="50" t="str">
+      <c r="I199" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="J199" s="13" t="str">
         <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
         <v>22-12-103</v>
       </c>
     </row>
     <row r="200" spans="1:10" ht="15.75">
-      <c r="A200" s="41">
+      <c r="A200" s="9">
         <v>5063022611239</v>
       </c>
-      <c r="B200" s="42" t="s">
+      <c r="B200" s="10" t="s">
         <v>208</v>
       </c>
       <c r="C200" s="14"/>
-      <c r="D200" s="48" t="str">
-        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="E200" s="48" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 07</v>
-      </c>
-      <c r="F200" s="48" t="str">
+      <c r="D200" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E200" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 08</v>
+      </c>
+      <c r="F200" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
         <v>MODULO 1</v>
       </c>
-      <c r="G200" s="48" t="str">
+      <c r="G200" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
         <v>FILA 1</v>
       </c>
@@ -12993,36 +12979,36 @@
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>NO</v>
       </c>
-      <c r="I200" s="49" t="str">
-        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="J200" s="50" t="str">
+      <c r="I200" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="J200" s="13" t="str">
         <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
         <v>22-13-101</v>
       </c>
     </row>
     <row r="201" spans="1:10" ht="15.75">
-      <c r="A201" s="41">
+      <c r="A201" s="9">
         <v>5059340221700</v>
       </c>
-      <c r="B201" s="42" t="s">
+      <c r="B201" s="10" t="s">
         <v>209</v>
       </c>
       <c r="C201" s="14"/>
-      <c r="D201" s="48" t="str">
-        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="E201" s="48" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 07</v>
-      </c>
-      <c r="F201" s="48" t="str">
+      <c r="D201" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E201" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 08</v>
+      </c>
+      <c r="F201" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
         <v>MODULO 1</v>
       </c>
-      <c r="G201" s="48" t="str">
+      <c r="G201" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
         <v>FILA 1</v>
       </c>
@@ -13030,36 +13016,36 @@
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>NO</v>
       </c>
-      <c r="I201" s="49" t="str">
-        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="J201" s="50" t="str">
+      <c r="I201" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="J201" s="13" t="str">
         <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
         <v>22-13-102</v>
       </c>
     </row>
     <row r="202" spans="1:10" ht="15.75">
-      <c r="A202" s="41">
+      <c r="A202" s="9">
         <v>5059340969626</v>
       </c>
-      <c r="B202" s="42" t="s">
+      <c r="B202" s="10" t="s">
         <v>210</v>
       </c>
       <c r="C202" s="14"/>
-      <c r="D202" s="48" t="str">
-        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="E202" s="48" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 07</v>
-      </c>
-      <c r="F202" s="48" t="str">
+      <c r="D202" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E202" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 08</v>
+      </c>
+      <c r="F202" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
         <v>MODULO 2</v>
       </c>
-      <c r="G202" s="48" t="str">
+      <c r="G202" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
         <v>FILA 2</v>
       </c>
@@ -13067,36 +13053,36 @@
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>NO</v>
       </c>
-      <c r="I202" s="49" t="str">
-        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="J202" s="50" t="str">
+      <c r="I202" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="J202" s="13" t="str">
         <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
         <v>22-13-103</v>
       </c>
     </row>
     <row r="203" spans="1:10" ht="15.75">
-      <c r="A203" s="41">
+      <c r="A203" s="9">
         <v>5059340357461</v>
       </c>
-      <c r="B203" s="42" t="s">
+      <c r="B203" s="10" t="s">
         <v>211</v>
       </c>
       <c r="C203" s="14"/>
-      <c r="D203" s="48" t="str">
-        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="E203" s="48" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 07</v>
-      </c>
-      <c r="F203" s="48" t="str">
+      <c r="D203" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E203" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 08</v>
+      </c>
+      <c r="F203" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
         <v>MODULO 1</v>
       </c>
-      <c r="G203" s="48" t="str">
+      <c r="G203" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
         <v>FILA 2</v>
       </c>
@@ -13104,36 +13090,36 @@
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>NO</v>
       </c>
-      <c r="I203" s="49" t="str">
-        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="J203" s="50" t="str">
+      <c r="I203" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="J203" s="13" t="str">
         <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
         <v>22-14-101</v>
       </c>
     </row>
     <row r="204" spans="1:10" ht="15.75">
-      <c r="A204" s="41">
+      <c r="A204" s="9">
         <v>5059340969664</v>
       </c>
-      <c r="B204" s="42" t="s">
+      <c r="B204" s="10" t="s">
         <v>212</v>
       </c>
       <c r="C204" s="14"/>
-      <c r="D204" s="48" t="str">
-        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="E204" s="48" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 07</v>
-      </c>
-      <c r="F204" s="48" t="str">
+      <c r="D204" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E204" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 08</v>
+      </c>
+      <c r="F204" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
         <v>MODULO 2</v>
       </c>
-      <c r="G204" s="48" t="str">
+      <c r="G204" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
         <v>FILA 2</v>
       </c>
@@ -13141,36 +13127,36 @@
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>NO</v>
       </c>
-      <c r="I204" s="49" t="str">
-        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="J204" s="50" t="str">
+      <c r="I204" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="J204" s="13" t="str">
         <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
         <v>22-14-102</v>
       </c>
     </row>
     <row r="205" spans="1:10" ht="15.75">
-      <c r="A205" s="41">
+      <c r="A205" s="9">
         <v>5059340969633</v>
       </c>
-      <c r="B205" s="42" t="s">
+      <c r="B205" s="10" t="s">
         <v>213</v>
       </c>
       <c r="C205" s="14"/>
-      <c r="D205" s="48" t="str">
-        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="E205" s="48" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 07</v>
-      </c>
-      <c r="F205" s="48" t="str">
+      <c r="D205" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E205" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 08</v>
+      </c>
+      <c r="F205" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
         <v>MODULO 2</v>
       </c>
-      <c r="G205" s="48" t="str">
+      <c r="G205" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
         <v>FILA 1</v>
       </c>
@@ -13178,36 +13164,36 @@
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>NO</v>
       </c>
-      <c r="I205" s="49" t="str">
-        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="J205" s="50" t="str">
+      <c r="I205" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="J205" s="13" t="str">
         <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
         <v>22-14-103</v>
       </c>
     </row>
     <row r="206" spans="1:10" ht="15.75">
-      <c r="A206" s="41">
+      <c r="A206" s="9">
         <v>5059340357454</v>
       </c>
-      <c r="B206" s="42" t="s">
+      <c r="B206" s="10" t="s">
         <v>214</v>
       </c>
       <c r="C206" s="14"/>
-      <c r="D206" s="48" t="str">
-        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="E206" s="48" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 07</v>
-      </c>
-      <c r="F206" s="48" t="str">
+      <c r="D206" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E206" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 08</v>
+      </c>
+      <c r="F206" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
         <v>MODULO 1</v>
       </c>
-      <c r="G206" s="48" t="str">
+      <c r="G206" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
         <v>FILA 2</v>
       </c>
@@ -13215,36 +13201,36 @@
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>NO</v>
       </c>
-      <c r="I206" s="49" t="str">
-        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="J206" s="50" t="str">
+      <c r="I206" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="J206" s="13" t="str">
         <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
         <v>22-15-101</v>
       </c>
     </row>
     <row r="207" spans="1:10" ht="15.75">
-      <c r="A207" s="41">
+      <c r="A207" s="9">
         <v>5059340969640</v>
       </c>
-      <c r="B207" s="42" t="s">
+      <c r="B207" s="10" t="s">
         <v>215</v>
       </c>
       <c r="C207" s="14"/>
-      <c r="D207" s="48" t="str">
-        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="E207" s="48" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 07</v>
-      </c>
-      <c r="F207" s="48" t="str">
+      <c r="D207" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E207" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 08</v>
+      </c>
+      <c r="F207" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
         <v>MODULO 2</v>
       </c>
-      <c r="G207" s="48" t="str">
+      <c r="G207" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
         <v>FILA 1</v>
       </c>
@@ -13252,36 +13238,36 @@
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>NO</v>
       </c>
-      <c r="I207" s="49" t="str">
-        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="J207" s="50" t="str">
+      <c r="I207" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="J207" s="13" t="str">
         <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
         <v>22-15-102</v>
       </c>
     </row>
     <row r="208" spans="1:10" ht="15.75">
-      <c r="A208" s="41">
+      <c r="A208" s="9">
         <v>5059340969657</v>
       </c>
-      <c r="B208" s="42" t="s">
+      <c r="B208" s="10" t="s">
         <v>216</v>
       </c>
       <c r="C208" s="14"/>
-      <c r="D208" s="48" t="str">
-        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="E208" s="48" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 07</v>
-      </c>
-      <c r="F208" s="48" t="str">
+      <c r="D208" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E208" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 08</v>
+      </c>
+      <c r="F208" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
         <v>MODULO 2</v>
       </c>
-      <c r="G208" s="48" t="str">
+      <c r="G208" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
         <v>FILA 1</v>
       </c>
@@ -13289,11 +13275,11 @@
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>NO</v>
       </c>
-      <c r="I208" s="49" t="str">
-        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="J208" s="50" t="str">
+      <c r="I208" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="J208" s="13" t="str">
         <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
         <v>22-15-103</v>
       </c>
@@ -14537,14 +14523,14 @@
         <v>347</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="15.75">
+    <row r="112" spans="1:3">
       <c r="A112" s="24">
         <v>5059340485362</v>
       </c>
-      <c r="B112" s="38" t="s">
+      <c r="B112" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="C112" s="37" t="s">
+      <c r="C112" s="31" t="s">
         <v>348</v>
       </c>
     </row>
@@ -14555,18 +14541,18 @@
       <c r="B113" s="29" t="s">
         <v>185</v>
       </c>
-      <c r="C113" s="37" t="s">
+      <c r="C113" s="31" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="114" spans="1:3">
-      <c r="A114" s="39">
+      <c r="A114" s="38">
         <v>3663602997962</v>
       </c>
-      <c r="B114" s="40" t="s">
+      <c r="B114" s="39" t="s">
         <v>186</v>
       </c>
-      <c r="C114" s="37" t="s">
+      <c r="C114" s="31" t="s">
         <v>350</v>
       </c>
     </row>
@@ -14577,7 +14563,7 @@
       <c r="B115" s="29" t="s">
         <v>187</v>
       </c>
-      <c r="C115" s="37" t="s">
+      <c r="C115" s="31" t="s">
         <v>351</v>
       </c>
     </row>
@@ -14588,7 +14574,7 @@
       <c r="B116" s="29" t="s">
         <v>188</v>
       </c>
-      <c r="C116" s="37" t="s">
+      <c r="C116" s="31" t="s">
         <v>352</v>
       </c>
     </row>
@@ -14599,7 +14585,7 @@
       <c r="B117" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="C117" s="37" t="s">
+      <c r="C117" s="31" t="s">
         <v>353</v>
       </c>
     </row>
@@ -14610,7 +14596,7 @@
       <c r="B118" s="29" t="s">
         <v>190</v>
       </c>
-      <c r="C118" s="37" t="s">
+      <c r="C118" s="31" t="s">
         <v>354</v>
       </c>
     </row>
@@ -14621,7 +14607,7 @@
       <c r="B119" s="29" t="s">
         <v>191</v>
       </c>
-      <c r="C119" s="37" t="s">
+      <c r="C119" s="31" t="s">
         <v>355</v>
       </c>
     </row>
@@ -14632,7 +14618,7 @@
       <c r="B120" s="29" t="s">
         <v>192</v>
       </c>
-      <c r="C120" s="37" t="s">
+      <c r="C120" s="31" t="s">
         <v>356</v>
       </c>
     </row>
@@ -14643,7 +14629,7 @@
       <c r="B121" s="29" t="s">
         <v>193</v>
       </c>
-      <c r="C121" s="37" t="s">
+      <c r="C121" s="31" t="s">
         <v>357</v>
       </c>
     </row>
@@ -14654,7 +14640,7 @@
       <c r="B122" s="29" t="s">
         <v>194</v>
       </c>
-      <c r="C122" s="37" t="s">
+      <c r="C122" s="31" t="s">
         <v>358</v>
       </c>
     </row>
@@ -14665,7 +14651,7 @@
       <c r="B123" s="29" t="s">
         <v>195</v>
       </c>
-      <c r="C123" s="37" t="s">
+      <c r="C123" s="31" t="s">
         <v>359</v>
       </c>
     </row>
@@ -14676,7 +14662,7 @@
       <c r="B124" s="29" t="s">
         <v>196</v>
       </c>
-      <c r="C124" s="37" t="s">
+      <c r="C124" s="31" t="s">
         <v>360</v>
       </c>
     </row>
@@ -14687,7 +14673,7 @@
       <c r="B125" s="29" t="s">
         <v>197</v>
       </c>
-      <c r="C125" s="37" t="s">
+      <c r="C125" s="31" t="s">
         <v>361</v>
       </c>
     </row>
@@ -14698,7 +14684,7 @@
       <c r="B126" s="29" t="s">
         <v>198</v>
       </c>
-      <c r="C126" s="37" t="s">
+      <c r="C126" s="31" t="s">
         <v>362</v>
       </c>
     </row>
@@ -14709,7 +14695,7 @@
       <c r="B127" s="29" t="s">
         <v>199</v>
       </c>
-      <c r="C127" s="37" t="s">
+      <c r="C127" s="31" t="s">
         <v>363</v>
       </c>
     </row>
@@ -14720,7 +14706,7 @@
       <c r="B128" s="29" t="s">
         <v>200</v>
       </c>
-      <c r="C128" s="37" t="s">
+      <c r="C128" s="31" t="s">
         <v>364</v>
       </c>
     </row>
@@ -14731,7 +14717,7 @@
       <c r="B129" s="29" t="s">
         <v>201</v>
       </c>
-      <c r="C129" s="37" t="s">
+      <c r="C129" s="31" t="s">
         <v>365</v>
       </c>
     </row>
@@ -15232,168 +15218,168 @@
         <v>442</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15.75">
-      <c r="A44" s="41">
+    <row r="44" spans="1:3">
+      <c r="A44" s="9">
         <v>5059340194042</v>
       </c>
-      <c r="B44" s="42" t="s">
+      <c r="B44" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="C44" s="43" t="s">
+      <c r="C44" s="27" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15.75">
-      <c r="A45" s="41">
+    <row r="45" spans="1:3">
+      <c r="A45" s="9">
         <v>5063022085641</v>
       </c>
-      <c r="B45" s="42" t="s">
+      <c r="B45" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="C45" s="43" t="s">
+      <c r="C45" s="27" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15.75">
-      <c r="A46" s="41">
+    <row r="46" spans="1:3">
+      <c r="A46" s="9">
         <v>5063022047830</v>
       </c>
-      <c r="B46" s="42" t="s">
+      <c r="B46" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="C46" s="43" t="s">
+      <c r="C46" s="27" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="15.75">
-      <c r="A47" s="41">
+    <row r="47" spans="1:3">
+      <c r="A47" s="9">
         <v>3663602997436</v>
       </c>
-      <c r="B47" s="42" t="s">
+      <c r="B47" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="C47" s="43" t="s">
+      <c r="C47" s="27" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="15.75">
-      <c r="A48" s="41">
+    <row r="48" spans="1:3">
+      <c r="A48" s="9">
         <v>5063022047847</v>
       </c>
-      <c r="B48" s="42" t="s">
+      <c r="B48" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="C48" s="43" t="s">
+      <c r="C48" s="27" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="15.75">
-      <c r="A49" s="41">
+    <row r="49" spans="1:3">
+      <c r="A49" s="9">
         <v>5059340391441</v>
       </c>
-      <c r="B49" s="42" t="s">
+      <c r="B49" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="C49" s="43" t="s">
+      <c r="C49" s="27" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="15.75">
-      <c r="A50" s="41">
+    <row r="50" spans="1:3">
+      <c r="A50" s="9">
         <v>5063022611239</v>
       </c>
-      <c r="B50" s="42" t="s">
+      <c r="B50" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="C50" s="43" t="s">
+      <c r="C50" s="27" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="15.75">
-      <c r="A51" s="41">
+    <row r="51" spans="1:3">
+      <c r="A51" s="9">
         <v>5059340221700</v>
       </c>
-      <c r="B51" s="42" t="s">
+      <c r="B51" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="C51" s="43" t="s">
+      <c r="C51" s="27" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="15.75">
-      <c r="A52" s="41">
+    <row r="52" spans="1:3">
+      <c r="A52" s="9">
         <v>5059340969626</v>
       </c>
-      <c r="B52" s="42" t="s">
+      <c r="B52" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="C52" s="43" t="s">
+      <c r="C52" s="27" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="15.75">
-      <c r="A53" s="41">
+    <row r="53" spans="1:3">
+      <c r="A53" s="9">
         <v>5059340357461</v>
       </c>
-      <c r="B53" s="42" t="s">
+      <c r="B53" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="C53" s="43" t="s">
+      <c r="C53" s="27" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="15.75">
-      <c r="A54" s="41">
+    <row r="54" spans="1:3">
+      <c r="A54" s="9">
         <v>5059340969664</v>
       </c>
-      <c r="B54" s="42" t="s">
+      <c r="B54" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="C54" s="43" t="s">
+      <c r="C54" s="27" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="15.75">
-      <c r="A55" s="41">
+    <row r="55" spans="1:3">
+      <c r="A55" s="9">
         <v>5059340969633</v>
       </c>
-      <c r="B55" s="42" t="s">
+      <c r="B55" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="C55" s="43" t="s">
+      <c r="C55" s="27" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="15.75">
-      <c r="A56" s="41">
+    <row r="56" spans="1:3">
+      <c r="A56" s="9">
         <v>5059340357454</v>
       </c>
-      <c r="B56" s="42" t="s">
+      <c r="B56" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="C56" s="43" t="s">
+      <c r="C56" s="27" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="15.75">
-      <c r="A57" s="41">
+    <row r="57" spans="1:3">
+      <c r="A57" s="9">
         <v>5059340969640</v>
       </c>
-      <c r="B57" s="42" t="s">
+      <c r="B57" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="C57" s="43" t="s">
+      <c r="C57" s="27" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="15.75">
-      <c r="A58" s="41">
+    <row r="58" spans="1:3">
+      <c r="A58" s="9">
         <v>5059340969657</v>
       </c>
-      <c r="B58" s="42" t="s">
+      <c r="B58" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="C58" s="43" t="s">
+      <c r="C58" s="27" t="s">
         <v>457</v>
       </c>
     </row>
@@ -18178,7 +18164,7 @@
         <v>602</v>
       </c>
       <c r="C163" s="25" t="s">
-        <v>603</v>
+        <v>578</v>
       </c>
       <c r="D163" s="36" t="s">
         <v>460</v>
@@ -18192,10 +18178,10 @@
         <v>5063022611239</v>
       </c>
       <c r="B164" s="36" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C164" s="25" t="s">
-        <v>603</v>
+        <v>578</v>
       </c>
       <c r="D164" s="36" t="s">
         <v>460</v>
@@ -18209,10 +18195,10 @@
         <v>5059340357447</v>
       </c>
       <c r="B165" s="36" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C165" s="25" t="s">
-        <v>603</v>
+        <v>578</v>
       </c>
       <c r="D165" s="36" t="s">
         <v>460</v>
@@ -18226,10 +18212,10 @@
         <v>5059340357454</v>
       </c>
       <c r="B166" s="36" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C166" s="25" t="s">
-        <v>603</v>
+        <v>578</v>
       </c>
       <c r="D166" s="36" t="s">
         <v>460</v>
@@ -18243,10 +18229,10 @@
         <v>5059340357461</v>
       </c>
       <c r="B167" s="36" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C167" s="25" t="s">
-        <v>603</v>
+        <v>578</v>
       </c>
       <c r="D167" s="36" t="s">
         <v>460</v>
@@ -18260,10 +18246,10 @@
         <v>5059340221717</v>
       </c>
       <c r="B168" s="36" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C168" s="25" t="s">
-        <v>603</v>
+        <v>578</v>
       </c>
       <c r="D168" s="36" t="s">
         <v>460</v>
@@ -18277,10 +18263,10 @@
         <v>5059340802602</v>
       </c>
       <c r="B169" s="36" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C169" s="25" t="s">
-        <v>603</v>
+        <v>578</v>
       </c>
       <c r="D169" s="36" t="s">
         <v>460</v>
@@ -18294,10 +18280,10 @@
         <v>5059340802367</v>
       </c>
       <c r="B170" s="36" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C170" s="25" t="s">
-        <v>603</v>
+        <v>578</v>
       </c>
       <c r="D170" s="36" t="s">
         <v>460</v>
@@ -18311,10 +18297,10 @@
         <v>5059340802305</v>
       </c>
       <c r="B171" s="36" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C171" s="25" t="s">
-        <v>603</v>
+        <v>578</v>
       </c>
       <c r="D171" s="36" t="s">
         <v>460</v>
@@ -18328,10 +18314,10 @@
         <v>5059340802626</v>
       </c>
       <c r="B172" s="36" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C172" s="25" t="s">
-        <v>603</v>
+        <v>578</v>
       </c>
       <c r="D172" s="36" t="s">
         <v>460</v>
@@ -18345,10 +18331,10 @@
         <v>5059340802336</v>
       </c>
       <c r="B173" s="36" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C173" s="25" t="s">
-        <v>603</v>
+        <v>578</v>
       </c>
       <c r="D173" s="36" t="s">
         <v>460</v>
@@ -18362,10 +18348,10 @@
         <v>5059340802923</v>
       </c>
       <c r="B174" s="36" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C174" s="25" t="s">
-        <v>603</v>
+        <v>578</v>
       </c>
       <c r="D174" s="36" t="s">
         <v>460</v>
@@ -18379,10 +18365,10 @@
         <v>5059340802558</v>
       </c>
       <c r="B175" s="36" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C175" s="25" t="s">
-        <v>603</v>
+        <v>578</v>
       </c>
       <c r="D175" s="36" t="s">
         <v>460</v>
@@ -18396,10 +18382,10 @@
         <v>5059340802831</v>
       </c>
       <c r="B176" s="36" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C176" s="25" t="s">
-        <v>603</v>
+        <v>578</v>
       </c>
       <c r="D176" s="36" t="s">
         <v>460</v>
@@ -18413,10 +18399,10 @@
         <v>5059340969657</v>
       </c>
       <c r="B177" s="36" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C177" s="25" t="s">
-        <v>603</v>
+        <v>578</v>
       </c>
       <c r="D177" s="36" t="s">
         <v>476</v>
@@ -18430,10 +18416,10 @@
         <v>5059340969633</v>
       </c>
       <c r="B178" s="36" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C178" s="25" t="s">
-        <v>603</v>
+        <v>578</v>
       </c>
       <c r="D178" s="36" t="s">
         <v>476</v>
@@ -18447,10 +18433,10 @@
         <v>5059340969640</v>
       </c>
       <c r="B179" s="36" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C179" s="25" t="s">
-        <v>603</v>
+        <v>578</v>
       </c>
       <c r="D179" s="36" t="s">
         <v>476</v>
@@ -18464,10 +18450,10 @@
         <v>5059340969664</v>
       </c>
       <c r="B180" s="36" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C180" s="25" t="s">
-        <v>603</v>
+        <v>578</v>
       </c>
       <c r="D180" s="36" t="s">
         <v>476</v>
@@ -18481,10 +18467,10 @@
         <v>5059340969626</v>
       </c>
       <c r="B181" s="36" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C181" s="25" t="s">
-        <v>603</v>
+        <v>578</v>
       </c>
       <c r="D181" s="36" t="s">
         <v>476</v>
@@ -18498,10 +18484,10 @@
         <v>5059340802473</v>
       </c>
       <c r="B182" s="36" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C182" s="25" t="s">
-        <v>603</v>
+        <v>578</v>
       </c>
       <c r="D182" s="36" t="s">
         <v>476</v>
@@ -18515,10 +18501,10 @@
         <v>5059340802725</v>
       </c>
       <c r="B183" s="36" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C183" s="25" t="s">
-        <v>603</v>
+        <v>578</v>
       </c>
       <c r="D183" s="36" t="s">
         <v>476</v>
@@ -18532,10 +18518,10 @@
         <v>5059340803074</v>
       </c>
       <c r="B184" s="36" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C184" s="25" t="s">
-        <v>603</v>
+        <v>578</v>
       </c>
       <c r="D184" s="36" t="s">
         <v>476</v>
@@ -18549,10 +18535,10 @@
         <v>3663602997436</v>
       </c>
       <c r="B185" s="36" t="s">
+        <v>624</v>
+      </c>
+      <c r="C185" s="25" t="s">
         <v>625</v>
-      </c>
-      <c r="C185" s="25" t="s">
-        <v>626</v>
       </c>
       <c r="D185" s="36" t="s">
         <v>460</v>
@@ -18569,7 +18555,7 @@
         <v>206</v>
       </c>
       <c r="C186" s="25" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D186" s="36" t="s">
         <v>460</v>
@@ -18583,10 +18569,10 @@
         <v>5063022085658</v>
       </c>
       <c r="B187" s="36" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C187" s="25" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D187" s="36" t="s">
         <v>460</v>
@@ -18600,10 +18586,10 @@
         <v>3663602997962</v>
       </c>
       <c r="B188" s="36" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C188" s="25" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D188" s="36" t="s">
         <v>460</v>
@@ -18620,7 +18606,7 @@
         <v>191</v>
       </c>
       <c r="C189" s="25" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D189" s="36" t="s">
         <v>460</v>
@@ -18634,10 +18620,10 @@
         <v>5063022606525</v>
       </c>
       <c r="B190" s="36" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C190" s="25" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D190" s="36" t="s">
         <v>460</v>
@@ -18654,7 +18640,7 @@
         <v>190</v>
       </c>
       <c r="C191" s="25" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D191" s="36" t="s">
         <v>460</v>
@@ -18668,10 +18654,10 @@
         <v>5059340194042</v>
       </c>
       <c r="B192" s="36" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C192" s="25" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D192" s="36" t="s">
         <v>460</v>
@@ -18685,10 +18671,10 @@
         <v>5063022606068</v>
       </c>
       <c r="B193" s="36" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C193" s="25" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D193" s="36" t="s">
         <v>460</v>
@@ -18705,7 +18691,7 @@
         <v>184</v>
       </c>
       <c r="C194" s="25" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D194" s="36" t="s">
         <v>460</v>
@@ -18722,7 +18708,7 @@
         <v>193</v>
       </c>
       <c r="C195" s="25" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D195" s="36" t="s">
         <v>460</v>
@@ -18739,7 +18725,7 @@
         <v>199</v>
       </c>
       <c r="C196" s="25" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D196" s="36" t="s">
         <v>460</v>
@@ -18756,7 +18742,7 @@
         <v>194</v>
       </c>
       <c r="C197" s="25" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D197" s="36" t="s">
         <v>460</v>
@@ -18773,7 +18759,7 @@
         <v>185</v>
       </c>
       <c r="C198" s="25" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D198" s="36" t="s">
         <v>460</v>
@@ -18790,7 +18776,7 @@
         <v>204</v>
       </c>
       <c r="C199" s="25" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D199" s="36" t="s">
         <v>476</v>
@@ -18804,10 +18790,10 @@
         <v>5063022085641</v>
       </c>
       <c r="B200" s="36" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C200" s="25" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D200" s="36" t="s">
         <v>476</v>
@@ -18821,10 +18807,10 @@
         <v>5063022034496</v>
       </c>
       <c r="B201" s="36" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C201" s="25" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D201" s="36" t="s">
         <v>476</v>
@@ -18841,7 +18827,7 @@
         <v>207</v>
       </c>
       <c r="C202" s="25" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D202" s="36" t="s">
         <v>476</v>
@@ -18855,10 +18841,10 @@
         <v>5063022606020</v>
       </c>
       <c r="B203" s="36" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C203" s="25" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D203" s="36" t="s">
         <v>476</v>
@@ -18872,10 +18858,10 @@
         <v>5063022606037</v>
       </c>
       <c r="B204" s="36" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C204" s="25" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D204" s="36" t="s">
         <v>476</v>
@@ -18889,10 +18875,10 @@
         <v>5063022606013</v>
       </c>
       <c r="B205" s="36" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C205" s="25" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D205" s="36" t="s">
         <v>476</v>
@@ -18909,7 +18895,7 @@
         <v>188</v>
       </c>
       <c r="C206" s="25" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D206" s="36" t="s">
         <v>476</v>
@@ -18926,7 +18912,7 @@
         <v>187</v>
       </c>
       <c r="C207" s="25" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D207" s="36" t="s">
         <v>476</v>
@@ -18943,7 +18929,7 @@
         <v>201</v>
       </c>
       <c r="C208" s="25" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D208" s="36" t="s">
         <v>476</v>
@@ -18957,10 +18943,10 @@
         <v>5059340194035</v>
       </c>
       <c r="B209" s="36" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C209" s="25" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D209" s="36" t="s">
         <v>476</v>
@@ -18977,7 +18963,7 @@
         <v>183</v>
       </c>
       <c r="C210" s="25" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D210" s="36" t="s">
         <v>476</v>

--- a/ceramica_proyecto.xlsx
+++ b/ceramica_proyecto.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29108"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29122"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Camero\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{67D89B04-FA05-4E94-B403-56B6AF243218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{110E6A90-6A5B-4057-B3DF-3C305FC3FDF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{6A0D054A-EA90-43D3-9946-5E896568E0A7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" xr2:uid="{6A0D054A-EA90-43D3-9946-5E896568E0A7}"/>
   </bookViews>
   <sheets>
     <sheet name="EXISTENCIA TOTAL" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1435" uniqueCount="637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1433" uniqueCount="636">
   <si>
     <t>EAN</t>
   </si>
@@ -344,7 +344,7 @@
     <t>PAVIMENTO JANO ZARAUTZ C2 GRIS 23X120</t>
   </si>
   <si>
-    <t>PAV. PINE GREIGE 20X80.</t>
+    <t>PAVIMENTO PINE GREIGE 20X80.</t>
   </si>
   <si>
     <t>PAVIMENTO MÓNACO 22,5X90</t>
@@ -1340,91 +1340,6 @@
   </si>
   <si>
     <t>28-12-302</t>
-  </si>
-  <si>
-    <r>
-      <t>PAVIMENTO</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>CONCORDE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>NATURAL</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>MATE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>30X60</t>
-    </r>
   </si>
   <si>
     <t>28-08-401</t>
@@ -4138,7 +4053,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4251,12 +4166,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="6"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
@@ -4400,8 +4309,8 @@
     <xf numFmtId="1" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4919,8 +4828,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E092D5E8-DDBA-4DC5-B48F-DE814A493E02}" name="ALMACEN" displayName="ALMACEN" ref="A1:C129" totalsRowShown="0" dataDxfId="19" headerRowBorderDxfId="17" tableBorderDxfId="18">
-  <autoFilter ref="A1:C129" xr:uid="{E092D5E8-DDBA-4DC5-B48F-DE814A493E02}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E092D5E8-DDBA-4DC5-B48F-DE814A493E02}" name="ALMACEN" displayName="ALMACEN" ref="A1:C128" totalsRowShown="0" dataDxfId="19" headerRowBorderDxfId="17" tableBorderDxfId="18">
+  <autoFilter ref="A1:C128" xr:uid="{E092D5E8-DDBA-4DC5-B48F-DE814A493E02}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{3A65B69D-D98E-4AEB-961F-5593E79CA067}" name="EAN" dataDxfId="16"/>
     <tableColumn id="2" xr3:uid="{469CD1D5-7294-47E9-B0FB-BA7DD9CCC96D}" name="descrpcion_es" dataDxfId="15"/>
@@ -4944,7 +4853,13 @@
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{04895F0D-CED9-49B0-B76F-B45DB5CC94A2}" name="SHOWROOM" displayName="SHOWROOM" ref="A1:E210" totalsRowShown="0" dataDxfId="7" headerRowBorderDxfId="5" tableBorderDxfId="6">
-  <autoFilter ref="A1:E210" xr:uid="{04895F0D-CED9-49B0-B76F-B45DB5CC94A2}"/>
+  <autoFilter ref="A1:E210" xr:uid="{04895F0D-CED9-49B0-B76F-B45DB5CC94A2}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="MODULO 2"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{988177E9-8B74-4DA8-8D93-E60B539BC797}" name="EAN" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{9354D9B3-F652-4D41-B841-C67C7F44B562}" name="descrpcion_es" dataDxfId="3"/>
@@ -10986,11 +10901,11 @@
       </c>
       <c r="I147" s="16" t="str">
         <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
+        <v>NO</v>
       </c>
       <c r="J147" s="13" t="str">
         <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
-        <v>24-12-103</v>
+        <v>28-05-203</v>
       </c>
     </row>
     <row r="148" spans="1:10" ht="15.75">
@@ -11606,15 +11521,15 @@
       </c>
       <c r="H163" s="15" t="str">
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
+        <v>NO</v>
       </c>
       <c r="I163" s="16" t="str">
         <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="J163" s="13" t="str">
         <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
-        <v>28-05-203</v>
+        <v>24-12-103</v>
       </c>
     </row>
     <row r="164" spans="1:10" ht="15.75">
@@ -13295,7 +13210,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DD18BE2-0DBC-4BB4-8FBE-BFB232B0B51D}">
-  <dimension ref="A1:C129"/>
+  <dimension ref="A1:C128"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
@@ -14336,23 +14251,23 @@
         <v>330</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="17.25">
+    <row r="95" spans="1:3">
       <c r="A95" s="28">
-        <v>8435609378458</v>
+        <v>5036581066345</v>
       </c>
       <c r="B95" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="C95" s="31" t="s">
         <v>331</v>
-      </c>
-      <c r="C95" s="31" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" s="28">
-        <v>5036581066345</v>
+        <v>5036581065751</v>
       </c>
       <c r="B96" s="29" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C96" s="31" t="s">
         <v>332</v>
@@ -14360,10 +14275,10 @@
     </row>
     <row r="97" spans="1:3">
       <c r="A97" s="28">
-        <v>5036581065751</v>
+        <v>5059340854229</v>
       </c>
       <c r="B97" s="29" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="C97" s="31" t="s">
         <v>333</v>
@@ -14371,10 +14286,10 @@
     </row>
     <row r="98" spans="1:3">
       <c r="A98" s="28">
-        <v>5059340854229</v>
+        <v>5059340460284</v>
       </c>
       <c r="B98" s="29" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C98" s="31" t="s">
         <v>334</v>
@@ -14382,10 +14297,10 @@
     </row>
     <row r="99" spans="1:3">
       <c r="A99" s="28">
-        <v>5059340460284</v>
+        <v>5036581066406</v>
       </c>
       <c r="B99" s="29" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C99" s="31" t="s">
         <v>335</v>
@@ -14393,10 +14308,10 @@
     </row>
     <row r="100" spans="1:3">
       <c r="A100" s="28">
-        <v>5036581066406</v>
+        <v>8435433544173</v>
       </c>
       <c r="B100" s="29" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C100" s="31" t="s">
         <v>336</v>
@@ -14404,10 +14319,10 @@
     </row>
     <row r="101" spans="1:3">
       <c r="A101" s="28">
-        <v>8435433544173</v>
+        <v>8435433542438</v>
       </c>
       <c r="B101" s="29" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C101" s="31" t="s">
         <v>337</v>
@@ -14415,10 +14330,10 @@
     </row>
     <row r="102" spans="1:3">
       <c r="A102" s="28">
-        <v>8435433542438</v>
+        <v>5036581065201</v>
       </c>
       <c r="B102" s="29" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C102" s="31" t="s">
         <v>338</v>
@@ -14426,10 +14341,10 @@
     </row>
     <row r="103" spans="1:3">
       <c r="A103" s="28">
-        <v>5036581065201</v>
+        <v>5036581065218</v>
       </c>
       <c r="B103" s="29" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C103" s="31" t="s">
         <v>339</v>
@@ -14437,10 +14352,10 @@
     </row>
     <row r="104" spans="1:3">
       <c r="A104" s="28">
-        <v>5036581065218</v>
+        <v>3663602675846</v>
       </c>
       <c r="B104" s="29" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="C104" s="31" t="s">
         <v>340</v>
@@ -14448,10 +14363,10 @@
     </row>
     <row r="105" spans="1:3">
       <c r="A105" s="28">
-        <v>3663602675846</v>
+        <v>8435414109278</v>
       </c>
       <c r="B105" s="29" t="s">
-        <v>96</v>
+        <v>180</v>
       </c>
       <c r="C105" s="31" t="s">
         <v>341</v>
@@ -14459,10 +14374,10 @@
     </row>
     <row r="106" spans="1:3">
       <c r="A106" s="28">
-        <v>8435414109278</v>
+        <v>3663602677413</v>
       </c>
       <c r="B106" s="29" t="s">
-        <v>180</v>
+        <v>109</v>
       </c>
       <c r="C106" s="31" t="s">
         <v>342</v>
@@ -14470,10 +14385,10 @@
     </row>
     <row r="107" spans="1:3">
       <c r="A107" s="28">
-        <v>3663602677413</v>
+        <v>8429991798857</v>
       </c>
       <c r="B107" s="29" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="C107" s="31" t="s">
         <v>343</v>
@@ -14481,76 +14396,76 @@
     </row>
     <row r="108" spans="1:3">
       <c r="A108" s="28">
-        <v>8429991798857</v>
+        <v>8435433518471</v>
       </c>
       <c r="B108" s="29" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="C108" s="31" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="109" spans="1:3">
-      <c r="A109" s="28">
-        <v>8435433518471</v>
-      </c>
-      <c r="B109" s="29" t="s">
-        <v>144</v>
+    <row r="109" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A109" s="12">
+        <v>5059340781976</v>
+      </c>
+      <c r="B109" s="13" t="s">
+        <v>65</v>
       </c>
       <c r="C109" s="31" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A110" s="12">
-        <v>5059340781976</v>
-      </c>
-      <c r="B110" s="13" t="s">
-        <v>65</v>
+    <row r="110" spans="1:3">
+      <c r="A110" s="28">
+        <v>5059340194073</v>
+      </c>
+      <c r="B110" s="29" t="s">
+        <v>183</v>
       </c>
       <c r="C110" s="31" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="111" spans="1:3">
-      <c r="A111" s="28">
-        <v>5059340194073</v>
-      </c>
-      <c r="B111" s="29" t="s">
-        <v>183</v>
+      <c r="A111" s="24">
+        <v>5059340485362</v>
+      </c>
+      <c r="B111" s="37" t="s">
+        <v>184</v>
       </c>
       <c r="C111" s="31" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="112" spans="1:3">
-      <c r="A112" s="24">
-        <v>5059340485362</v>
-      </c>
-      <c r="B112" s="37" t="s">
-        <v>184</v>
+      <c r="A112" s="28">
+        <v>5059340194097</v>
+      </c>
+      <c r="B112" s="29" t="s">
+        <v>185</v>
       </c>
       <c r="C112" s="31" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="113" spans="1:3">
-      <c r="A113" s="28">
-        <v>5059340194097</v>
-      </c>
-      <c r="B113" s="29" t="s">
-        <v>185</v>
+      <c r="A113" s="38">
+        <v>3663602997962</v>
+      </c>
+      <c r="B113" s="39" t="s">
+        <v>186</v>
       </c>
       <c r="C113" s="31" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="114" spans="1:3">
-      <c r="A114" s="38">
-        <v>3663602997962</v>
-      </c>
-      <c r="B114" s="39" t="s">
-        <v>186</v>
+      <c r="A114" s="28">
+        <v>5059340484303</v>
+      </c>
+      <c r="B114" s="29" t="s">
+        <v>187</v>
       </c>
       <c r="C114" s="31" t="s">
         <v>350</v>
@@ -14558,10 +14473,10 @@
     </row>
     <row r="115" spans="1:3">
       <c r="A115" s="28">
-        <v>5059340484303</v>
+        <v>5063022047816</v>
       </c>
       <c r="B115" s="29" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C115" s="31" t="s">
         <v>351</v>
@@ -14569,10 +14484,10 @@
     </row>
     <row r="116" spans="1:3">
       <c r="A116" s="28">
-        <v>5063022047816</v>
+        <v>5059340194035</v>
       </c>
       <c r="B116" s="29" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C116" s="31" t="s">
         <v>352</v>
@@ -14580,10 +14495,10 @@
     </row>
     <row r="117" spans="1:3">
       <c r="A117" s="28">
-        <v>5059340194035</v>
+        <v>5063022047755</v>
       </c>
       <c r="B117" s="29" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C117" s="31" t="s">
         <v>353</v>
@@ -14591,10 +14506,10 @@
     </row>
     <row r="118" spans="1:3">
       <c r="A118" s="28">
-        <v>5063022047755</v>
+        <v>5063022069450</v>
       </c>
       <c r="B118" s="29" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C118" s="31" t="s">
         <v>354</v>
@@ -14602,10 +14517,10 @@
     </row>
     <row r="119" spans="1:3">
       <c r="A119" s="28">
-        <v>5063022069450</v>
+        <v>5063022085658</v>
       </c>
       <c r="B119" s="29" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C119" s="31" t="s">
         <v>355</v>
@@ -14613,10 +14528,10 @@
     </row>
     <row r="120" spans="1:3">
       <c r="A120" s="28">
-        <v>5063022085658</v>
+        <v>5063022085603</v>
       </c>
       <c r="B120" s="29" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C120" s="31" t="s">
         <v>356</v>
@@ -14624,10 +14539,10 @@
     </row>
     <row r="121" spans="1:3">
       <c r="A121" s="28">
-        <v>5063022085603</v>
+        <v>5059340216034</v>
       </c>
       <c r="B121" s="29" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C121" s="31" t="s">
         <v>357</v>
@@ -14635,10 +14550,10 @@
     </row>
     <row r="122" spans="1:3">
       <c r="A122" s="28">
-        <v>5059340216034</v>
+        <v>5063022606068</v>
       </c>
       <c r="B122" s="29" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C122" s="31" t="s">
         <v>358</v>
@@ -14646,10 +14561,10 @@
     </row>
     <row r="123" spans="1:3">
       <c r="A123" s="28">
-        <v>5063022606068</v>
+        <v>5063022606020</v>
       </c>
       <c r="B123" s="29" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C123" s="31" t="s">
         <v>359</v>
@@ -14657,10 +14572,10 @@
     </row>
     <row r="124" spans="1:3">
       <c r="A124" s="28">
-        <v>5063022606020</v>
+        <v>5063022606037</v>
       </c>
       <c r="B124" s="29" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C124" s="31" t="s">
         <v>360</v>
@@ -14668,10 +14583,10 @@
     </row>
     <row r="125" spans="1:3">
       <c r="A125" s="28">
-        <v>5063022606037</v>
+        <v>5063022606013</v>
       </c>
       <c r="B125" s="29" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C125" s="31" t="s">
         <v>361</v>
@@ -14679,10 +14594,10 @@
     </row>
     <row r="126" spans="1:3">
       <c r="A126" s="28">
-        <v>5063022606013</v>
+        <v>5059340194080</v>
       </c>
       <c r="B126" s="29" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C126" s="31" t="s">
         <v>362</v>
@@ -14690,10 +14605,10 @@
     </row>
     <row r="127" spans="1:3">
       <c r="A127" s="28">
-        <v>5059340194080</v>
+        <v>5063022606525</v>
       </c>
       <c r="B127" s="29" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C127" s="31" t="s">
         <v>363</v>
@@ -14701,24 +14616,13 @@
     </row>
     <row r="128" spans="1:3">
       <c r="A128" s="28">
-        <v>5063022606525</v>
+        <v>5063022047823</v>
       </c>
       <c r="B128" s="29" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C128" s="31" t="s">
         <v>364</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3">
-      <c r="A129" s="28">
-        <v>5063022047823</v>
-      </c>
-      <c r="B129" s="29" t="s">
-        <v>201</v>
-      </c>
-      <c r="C129" s="31" t="s">
-        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -14758,13 +14662,13 @@
         <v>5059340719535</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="C2" s="27" t="s">
         <v>366</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="J2" t="s">
         <v>367</v>
-      </c>
-      <c r="J2" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -14772,10 +14676,10 @@
         <v>5059340719658</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="C3" s="27" t="s">
         <v>369</v>
-      </c>
-      <c r="C3" s="27" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -14786,7 +14690,7 @@
         <v>64</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -14797,7 +14701,7 @@
         <v>46</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -14805,10 +14709,10 @@
         <v>5036581065768</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="C6" s="27" t="s">
         <v>373</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -14819,7 +14723,7 @@
         <v>72</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -14827,10 +14731,10 @@
         <v>8435414126275</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="C8" s="27" t="s">
         <v>376</v>
-      </c>
-      <c r="C8" s="27" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -14838,10 +14742,10 @@
         <v>5036581064877</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="C9" s="27" t="s">
         <v>378</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -14852,7 +14756,7 @@
         <v>28</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -14863,7 +14767,7 @@
         <v>20</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -14871,10 +14775,10 @@
         <v>5036581064310</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="C12" s="27" t="s">
         <v>382</v>
-      </c>
-      <c r="C12" s="27" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -14885,7 +14789,7 @@
         <v>21</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -14893,10 +14797,10 @@
         <v>3663602848349</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="C14" s="27" t="s">
         <v>385</v>
-      </c>
-      <c r="C14" s="27" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -14904,10 +14808,10 @@
         <v>5036581064679</v>
       </c>
       <c r="B15" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="C15" s="27" t="s">
         <v>387</v>
-      </c>
-      <c r="C15" s="27" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -14915,10 +14819,10 @@
         <v>5059340433233</v>
       </c>
       <c r="B16" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="C16" s="27" t="s">
         <v>389</v>
-      </c>
-      <c r="C16" s="27" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -14926,10 +14830,10 @@
         <v>8435414126282</v>
       </c>
       <c r="B17" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="C17" s="27" t="s">
         <v>391</v>
-      </c>
-      <c r="C17" s="27" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -14937,10 +14841,10 @@
         <v>3663602679332</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="C18" s="27" t="s">
         <v>393</v>
-      </c>
-      <c r="C18" s="27" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -14948,10 +14852,10 @@
         <v>8435414127845</v>
       </c>
       <c r="B19" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="C19" s="27" t="s">
         <v>395</v>
-      </c>
-      <c r="C19" s="27" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -14959,10 +14863,10 @@
         <v>8429178156050</v>
       </c>
       <c r="B20" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="C20" s="27" t="s">
         <v>397</v>
-      </c>
-      <c r="C20" s="27" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -14970,10 +14874,10 @@
         <v>8429178398283</v>
       </c>
       <c r="B21" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="C21" s="27" t="s">
         <v>399</v>
-      </c>
-      <c r="C21" s="27" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -14981,10 +14885,10 @@
         <v>8435609333952</v>
       </c>
       <c r="B22" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="C22" s="27" t="s">
         <v>401</v>
-      </c>
-      <c r="C22" s="27" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -14992,10 +14896,10 @@
         <v>8429178840003</v>
       </c>
       <c r="B23" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="C23" s="27" t="s">
         <v>403</v>
-      </c>
-      <c r="C23" s="27" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -15003,10 +14907,10 @@
         <v>8432712278026</v>
       </c>
       <c r="B24" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="C24" s="27" t="s">
         <v>405</v>
-      </c>
-      <c r="C24" s="27" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -15014,10 +14918,10 @@
         <v>5059340433240</v>
       </c>
       <c r="B25" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="C25" s="27" t="s">
         <v>407</v>
-      </c>
-      <c r="C25" s="27" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -15025,10 +14929,10 @@
         <v>5059340460383</v>
       </c>
       <c r="B26" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="C26" s="27" t="s">
         <v>409</v>
-      </c>
-      <c r="C26" s="27" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -15036,10 +14940,10 @@
         <v>5059340720968</v>
       </c>
       <c r="B27" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="C27" s="27" t="s">
         <v>411</v>
-      </c>
-      <c r="C27" s="27" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -15047,10 +14951,10 @@
         <v>8435609330777</v>
       </c>
       <c r="B28" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="C28" s="27" t="s">
         <v>413</v>
-      </c>
-      <c r="C28" s="27" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -15058,10 +14962,10 @@
         <v>8429991953478</v>
       </c>
       <c r="B29" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="C29" s="27" t="s">
         <v>415</v>
-      </c>
-      <c r="C29" s="27" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -15069,10 +14973,10 @@
         <v>5059340720951</v>
       </c>
       <c r="B30" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="C30" s="27" t="s">
         <v>417</v>
-      </c>
-      <c r="C30" s="27" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -15080,10 +14984,10 @@
         <v>5063022645289</v>
       </c>
       <c r="B31" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="C31" s="27" t="s">
         <v>419</v>
-      </c>
-      <c r="C31" s="27" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -15091,10 +14995,10 @@
         <v>8429991953577</v>
       </c>
       <c r="B32" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="C32" s="27" t="s">
         <v>421</v>
-      </c>
-      <c r="C32" s="27" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -15102,10 +15006,10 @@
         <v>5059340870663</v>
       </c>
       <c r="B33" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="C33" s="27" t="s">
         <v>423</v>
-      </c>
-      <c r="C33" s="27" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -15113,10 +15017,10 @@
         <v>3663602678366</v>
       </c>
       <c r="B34" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="C34" s="27" t="s">
         <v>425</v>
-      </c>
-      <c r="C34" s="27" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -15124,10 +15028,10 @@
         <v>5059340719610</v>
       </c>
       <c r="B35" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="C35" s="27" t="s">
         <v>427</v>
-      </c>
-      <c r="C35" s="27" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -15135,10 +15039,10 @@
         <v>5059340720982</v>
       </c>
       <c r="B36" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="C36" s="27" t="s">
         <v>429</v>
-      </c>
-      <c r="C36" s="27" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -15146,10 +15050,10 @@
         <v>5059340720975</v>
       </c>
       <c r="B37" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="C37" s="27" t="s">
         <v>431</v>
-      </c>
-      <c r="C37" s="27" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -15157,10 +15061,10 @@
         <v>8435414120211</v>
       </c>
       <c r="B38" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="C38" s="27" t="s">
         <v>433</v>
-      </c>
-      <c r="C38" s="27" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -15168,10 +15072,10 @@
         <v>8435414118669</v>
       </c>
       <c r="B39" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="C39" s="27" t="s">
         <v>435</v>
-      </c>
-      <c r="C39" s="27" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -15179,10 +15083,10 @@
         <v>5036581058319</v>
       </c>
       <c r="B40" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="C40" s="27" t="s">
         <v>437</v>
-      </c>
-      <c r="C40" s="27" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -15190,10 +15094,10 @@
         <v>5036581058326</v>
       </c>
       <c r="B41" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="C41" s="27" t="s">
         <v>439</v>
-      </c>
-      <c r="C41" s="27" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -15204,18 +15108,18 @@
         <v>105</v>
       </c>
       <c r="C42" s="27" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="15.75">
+      <c r="A43" s="22">
+        <v>8435609378458</v>
+      </c>
+      <c r="B43" s="23" t="s">
+        <v>171</v>
+      </c>
+      <c r="C43" s="27" t="s">
         <v>441</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="9">
-        <v>8435609351932</v>
-      </c>
-      <c r="B43" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="C43" s="27" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -15226,7 +15130,7 @@
         <v>202</v>
       </c>
       <c r="C44" s="27" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -15237,7 +15141,7 @@
         <v>203</v>
       </c>
       <c r="C45" s="27" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -15248,7 +15152,7 @@
         <v>204</v>
       </c>
       <c r="C46" s="27" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -15259,7 +15163,7 @@
         <v>205</v>
       </c>
       <c r="C47" s="27" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -15270,7 +15174,7 @@
         <v>206</v>
       </c>
       <c r="C48" s="27" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -15281,7 +15185,7 @@
         <v>207</v>
       </c>
       <c r="C49" s="27" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -15292,7 +15196,7 @@
         <v>208</v>
       </c>
       <c r="C50" s="27" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -15303,7 +15207,7 @@
         <v>209</v>
       </c>
       <c r="C51" s="27" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -15314,7 +15218,7 @@
         <v>210</v>
       </c>
       <c r="C52" s="27" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -15325,7 +15229,7 @@
         <v>211</v>
       </c>
       <c r="C53" s="27" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -15336,7 +15240,7 @@
         <v>212</v>
       </c>
       <c r="C54" s="27" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -15347,7 +15251,7 @@
         <v>213</v>
       </c>
       <c r="C55" s="27" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -15358,7 +15262,7 @@
         <v>214</v>
       </c>
       <c r="C56" s="27" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -15369,7 +15273,7 @@
         <v>215</v>
       </c>
       <c r="C57" s="27" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -15380,7 +15284,7 @@
         <v>216</v>
       </c>
       <c r="C58" s="27" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
   </sheetData>
@@ -15419,174 +15323,174 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" hidden="1">
       <c r="A2" s="24">
         <v>8432712278026</v>
       </c>
       <c r="B2" s="25" t="s">
+        <v>457</v>
+      </c>
+      <c r="C2" s="25" t="s">
         <v>458</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="D2" s="25" t="s">
         <v>459</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="E2" s="25" t="s">
         <v>460</v>
       </c>
-      <c r="E2" s="25" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+    </row>
+    <row r="3" spans="1:5" hidden="1">
       <c r="A3" s="24">
         <v>8435414127845</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C3" s="25" t="s">
+        <v>458</v>
+      </c>
+      <c r="D3" s="25" t="s">
         <v>459</v>
       </c>
-      <c r="D3" s="25" t="s">
+      <c r="E3" s="25" t="s">
         <v>460</v>
       </c>
-      <c r="E3" s="25" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+    </row>
+    <row r="4" spans="1:5" hidden="1">
       <c r="A4" s="24">
         <v>5059340433240</v>
       </c>
       <c r="B4" s="25" t="s">
+        <v>462</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>458</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>459</v>
+      </c>
+      <c r="E4" s="25" t="s">
         <v>463</v>
       </c>
-      <c r="C4" s="25" t="s">
-        <v>459</v>
-      </c>
-      <c r="D4" s="25" t="s">
-        <v>460</v>
-      </c>
-      <c r="E4" s="25" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+    </row>
+    <row r="5" spans="1:5" hidden="1">
       <c r="A5" s="24">
         <v>8429178398283</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C5" s="25" t="s">
+        <v>458</v>
+      </c>
+      <c r="D5" s="25" t="s">
         <v>459</v>
       </c>
-      <c r="D5" s="25" t="s">
-        <v>460</v>
-      </c>
       <c r="E5" s="25" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" hidden="1">
       <c r="A6" s="24">
         <v>5059340433233</v>
       </c>
       <c r="B6" s="25" t="s">
+        <v>465</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>458</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>459</v>
+      </c>
+      <c r="E6" s="25" t="s">
         <v>466</v>
       </c>
-      <c r="C6" s="25" t="s">
-        <v>459</v>
-      </c>
-      <c r="D6" s="25" t="s">
-        <v>460</v>
-      </c>
-      <c r="E6" s="25" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+    </row>
+    <row r="7" spans="1:5" hidden="1">
       <c r="A7" s="24">
         <v>8429991784881</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C7" s="25" t="s">
+        <v>458</v>
+      </c>
+      <c r="D7" s="25" t="s">
         <v>459</v>
       </c>
-      <c r="D7" s="25" t="s">
-        <v>460</v>
-      </c>
       <c r="E7" s="25" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" hidden="1">
       <c r="A8" s="24">
         <v>5063022022561</v>
       </c>
       <c r="B8" s="25" t="s">
+        <v>468</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>458</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>459</v>
+      </c>
+      <c r="E8" s="25" t="s">
         <v>469</v>
       </c>
-      <c r="C8" s="25" t="s">
-        <v>459</v>
-      </c>
-      <c r="D8" s="25" t="s">
-        <v>460</v>
-      </c>
-      <c r="E8" s="25" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+    </row>
+    <row r="9" spans="1:5" hidden="1">
       <c r="A9" s="24">
         <v>8435609333952</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C9" s="25" t="s">
+        <v>458</v>
+      </c>
+      <c r="D9" s="25" t="s">
         <v>459</v>
       </c>
-      <c r="D9" s="25" t="s">
-        <v>460</v>
-      </c>
       <c r="E9" s="25" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" hidden="1">
       <c r="A10" s="24">
         <v>8429991784904</v>
       </c>
       <c r="B10" s="25" t="s">
+        <v>471</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>458</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>459</v>
+      </c>
+      <c r="E10" s="25" t="s">
         <v>472</v>
       </c>
-      <c r="C10" s="25" t="s">
-        <v>459</v>
-      </c>
-      <c r="D10" s="25" t="s">
-        <v>460</v>
-      </c>
-      <c r="E10" s="25" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+    </row>
+    <row r="11" spans="1:5" hidden="1">
       <c r="A11" s="24">
         <v>8429991784898</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C11" s="25" t="s">
+        <v>458</v>
+      </c>
+      <c r="D11" s="25" t="s">
         <v>459</v>
       </c>
-      <c r="D11" s="25" t="s">
-        <v>460</v>
-      </c>
       <c r="E11" s="25" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -15594,16 +15498,16 @@
         <v>8429178840003</v>
       </c>
       <c r="B12" s="25" t="s">
+        <v>474</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>458</v>
+      </c>
+      <c r="D12" s="25" t="s">
         <v>475</v>
       </c>
-      <c r="C12" s="25" t="s">
-        <v>459</v>
-      </c>
-      <c r="D12" s="25" t="s">
-        <v>476</v>
-      </c>
       <c r="E12" s="25" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -15611,16 +15515,16 @@
         <v>8435609373682</v>
       </c>
       <c r="B13" s="25" t="s">
+        <v>476</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>458</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>475</v>
+      </c>
+      <c r="E13" s="25" t="s">
         <v>477</v>
-      </c>
-      <c r="C13" s="25" t="s">
-        <v>459</v>
-      </c>
-      <c r="D13" s="25" t="s">
-        <v>476</v>
-      </c>
-      <c r="E13" s="25" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -15628,16 +15532,16 @@
         <v>8435609378458</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D14" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -15645,16 +15549,16 @@
         <v>8429178156050</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D15" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -15662,16 +15566,16 @@
         <v>8435414126282</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -15679,16 +15583,16 @@
         <v>8435609333921</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -15696,16 +15600,16 @@
         <v>5059340433424</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C18" s="25" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E18" s="25" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -15713,16 +15617,16 @@
         <v>3663602679332</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C19" s="25" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D19" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E19" s="25" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -15730,16 +15634,16 @@
         <v>8435414109278</v>
       </c>
       <c r="B20" s="25" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D20" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -15747,169 +15651,169 @@
         <v>3663602675846</v>
       </c>
       <c r="B21" s="25" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D21" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E21" s="25" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" hidden="1">
       <c r="A22" s="24">
         <v>5059340721002</v>
       </c>
       <c r="B22" s="25" t="s">
+        <v>486</v>
+      </c>
+      <c r="C22" s="25" t="s">
         <v>487</v>
       </c>
-      <c r="C22" s="25" t="s">
-        <v>488</v>
-      </c>
       <c r="D22" s="25" t="s">
+        <v>459</v>
+      </c>
+      <c r="E22" s="25" t="s">
         <v>460</v>
       </c>
-      <c r="E22" s="25" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+    </row>
+    <row r="23" spans="1:5" hidden="1">
       <c r="A23" s="24">
         <v>8435609330777</v>
       </c>
       <c r="B23" s="25" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C23" s="25" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D23" s="25" t="s">
+        <v>459</v>
+      </c>
+      <c r="E23" s="25" t="s">
         <v>460</v>
       </c>
-      <c r="E23" s="25" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+    </row>
+    <row r="24" spans="1:5" hidden="1">
       <c r="A24" s="24">
         <v>8429991798857</v>
       </c>
       <c r="B24" s="25" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D24" s="25" t="s">
+        <v>459</v>
+      </c>
+      <c r="E24" s="25" t="s">
         <v>460</v>
       </c>
-      <c r="E24" s="25" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+    </row>
+    <row r="25" spans="1:5" hidden="1">
       <c r="A25" s="24">
         <v>5059340720968</v>
       </c>
       <c r="B25" s="25" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D25" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E25" s="25" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" hidden="1">
       <c r="A26" s="24">
         <v>5063022605061</v>
       </c>
       <c r="B26" s="25" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D26" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E26" s="25" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" hidden="1">
       <c r="A27" s="24">
         <v>5059340812311</v>
       </c>
       <c r="B27" s="25" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D27" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E27" s="25" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" hidden="1">
       <c r="A28" s="24">
         <v>8429991953478</v>
       </c>
       <c r="B28" s="25" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C28" s="25" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D28" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E28" s="25" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" hidden="1">
       <c r="A29" s="24">
         <v>5059340269610</v>
       </c>
       <c r="B29" s="25" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C29" s="25" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D29" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E29" s="25" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" hidden="1">
       <c r="A30" s="24">
         <v>5059340874937</v>
       </c>
       <c r="B30" s="25" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C30" s="25" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D30" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E30" s="25" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -15920,13 +15824,13 @@
         <v>181</v>
       </c>
       <c r="C31" s="25" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D31" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E31" s="25" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -15934,16 +15838,16 @@
         <v>5059340854212</v>
       </c>
       <c r="B32" s="25" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C32" s="25" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D32" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E32" s="25" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -15951,16 +15855,16 @@
         <v>8429991793449</v>
       </c>
       <c r="B33" s="25" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D33" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E33" s="25" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -15968,16 +15872,16 @@
         <v>5059340870663</v>
       </c>
       <c r="B34" s="25" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C34" s="25" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D34" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E34" s="25" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -15985,16 +15889,16 @@
         <v>5059340854267</v>
       </c>
       <c r="B35" s="25" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D35" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E35" s="25" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -16002,16 +15906,16 @@
         <v>3663602678298</v>
       </c>
       <c r="B36" s="25" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C36" s="25" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D36" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E36" s="25" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -16019,16 +15923,16 @@
         <v>5059340459912</v>
       </c>
       <c r="B37" s="25" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C37" s="25" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D37" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E37" s="25" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -16036,16 +15940,16 @@
         <v>5059340854236</v>
       </c>
       <c r="B38" s="25" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C38" s="25" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D38" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E38" s="25" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -16053,16 +15957,16 @@
         <v>3663602678366</v>
       </c>
       <c r="B39" s="25" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C39" s="25" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D39" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E39" s="25" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -16070,169 +15974,169 @@
         <v>3663602678465</v>
       </c>
       <c r="B40" s="25" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C40" s="25" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D40" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E40" s="25" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" hidden="1">
       <c r="A41" s="24">
         <v>5059340720951</v>
       </c>
       <c r="B41" s="25" t="s">
+        <v>505</v>
+      </c>
+      <c r="C41" s="25" t="s">
         <v>506</v>
       </c>
-      <c r="C41" s="25" t="s">
-        <v>507</v>
-      </c>
       <c r="D41" s="25" t="s">
+        <v>459</v>
+      </c>
+      <c r="E41" s="25" t="s">
         <v>460</v>
       </c>
-      <c r="E41" s="25" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
+    </row>
+    <row r="42" spans="1:5" hidden="1">
       <c r="A42" s="24">
         <v>5063022645289</v>
       </c>
       <c r="B42" s="25" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C42" s="25" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D42" s="25" t="s">
+        <v>459</v>
+      </c>
+      <c r="E42" s="25" t="s">
         <v>460</v>
       </c>
-      <c r="E42" s="25" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
+    </row>
+    <row r="43" spans="1:5" hidden="1">
       <c r="A43" s="24">
         <v>8429991798864</v>
       </c>
       <c r="B43" s="25" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C43" s="25" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D43" s="25" t="s">
+        <v>459</v>
+      </c>
+      <c r="E43" s="25" t="s">
         <v>460</v>
       </c>
-      <c r="E43" s="25" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
+    </row>
+    <row r="44" spans="1:5" hidden="1">
       <c r="A44" s="24">
         <v>5059340721026</v>
       </c>
       <c r="B44" s="25" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C44" s="25" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D44" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E44" s="25" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" hidden="1">
       <c r="A45" s="24">
         <v>3663602677413</v>
       </c>
       <c r="B45" s="25" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C45" s="25" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D45" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E45" s="25" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" hidden="1">
       <c r="A46" s="24">
         <v>8435609317396</v>
       </c>
       <c r="B46" s="25" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C46" s="25" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D46" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E46" s="25" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" hidden="1">
       <c r="A47" s="24">
         <v>8429991953577</v>
       </c>
       <c r="B47" s="25" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C47" s="25" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D47" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E47" s="25" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" hidden="1">
       <c r="A48" s="24">
         <v>8429991798888</v>
       </c>
       <c r="B48" s="25" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C48" s="25" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D48" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E48" s="25" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" hidden="1">
       <c r="A49" s="24">
         <v>8429991798901</v>
       </c>
       <c r="B49" s="25" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C49" s="25" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D49" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E49" s="25" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -16240,16 +16144,16 @@
         <v>5059340460383</v>
       </c>
       <c r="B50" s="25" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C50" s="25" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D50" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E50" s="25" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -16257,16 +16161,16 @@
         <v>5059340721040</v>
       </c>
       <c r="B51" s="25" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C51" s="25" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D51" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E51" s="25" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -16274,16 +16178,16 @@
         <v>5059340720999</v>
       </c>
       <c r="B52" s="25" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C52" s="25" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D52" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E52" s="25" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -16291,16 +16195,16 @@
         <v>8432712270556</v>
       </c>
       <c r="B53" s="25" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C53" s="25" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D53" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E53" s="25" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -16308,16 +16212,16 @@
         <v>8435414101517</v>
       </c>
       <c r="B54" s="25" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C54" s="25" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D54" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E54" s="25" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -16325,138 +16229,138 @@
         <v>8429991787479</v>
       </c>
       <c r="B55" s="25" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C55" s="25" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D55" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E55" s="25" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" hidden="1">
       <c r="A56" s="26">
         <v>5059340720982</v>
       </c>
       <c r="B56" s="27" t="s">
+        <v>521</v>
+      </c>
+      <c r="C56" s="25" t="s">
         <v>522</v>
       </c>
-      <c r="C56" s="25" t="s">
-        <v>523</v>
-      </c>
       <c r="D56" s="27" t="s">
+        <v>459</v>
+      </c>
+      <c r="E56" s="27" t="s">
         <v>460</v>
       </c>
-      <c r="E56" s="27" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
+    </row>
+    <row r="57" spans="1:5" hidden="1">
       <c r="A57" s="26">
         <v>5036581058319</v>
       </c>
       <c r="B57" s="27" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C57" s="25" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D57" s="27" t="s">
+        <v>459</v>
+      </c>
+      <c r="E57" s="27" t="s">
         <v>460</v>
       </c>
-      <c r="E57" s="27" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
+    </row>
+    <row r="58" spans="1:5" hidden="1">
       <c r="A58" s="26">
         <v>5036581058326</v>
       </c>
       <c r="B58" s="27" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C58" s="25" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D58" s="27" t="s">
+        <v>459</v>
+      </c>
+      <c r="E58" s="27" t="s">
         <v>460</v>
       </c>
-      <c r="E58" s="27" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
+    </row>
+    <row r="59" spans="1:5" hidden="1">
       <c r="A59" s="26">
         <v>8429991787486</v>
       </c>
       <c r="B59" s="27" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C59" s="25" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D59" s="27" t="s">
+        <v>459</v>
+      </c>
+      <c r="E59" s="27" t="s">
         <v>460</v>
       </c>
-      <c r="E59" s="27" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
+    </row>
+    <row r="60" spans="1:5" hidden="1">
       <c r="A60" s="26">
         <v>843543353813</v>
       </c>
       <c r="B60" s="27" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C60" s="25" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D60" s="27" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E60" s="27" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" hidden="1">
       <c r="A61" s="26">
         <v>8435414118669</v>
       </c>
       <c r="B61" s="27" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C61" s="25" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D61" s="27" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E61" s="27" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" hidden="1">
       <c r="A62" s="26">
         <v>8435414118645</v>
       </c>
       <c r="B62" s="27" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C62" s="25" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D62" s="27" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E62" s="27" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" hidden="1">
       <c r="A63" s="26">
         <v>8435414120211</v>
       </c>
@@ -16464,33 +16368,33 @@
         <v>151</v>
       </c>
       <c r="C63" s="25" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D63" s="27" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E63" s="27" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" hidden="1">
       <c r="A64" s="26">
         <v>8435609351932</v>
       </c>
       <c r="B64" s="27" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C64" s="25" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D64" s="27" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E64" s="27" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" hidden="1">
       <c r="A65" s="26">
         <v>5059340721033</v>
       </c>
@@ -16498,47 +16402,47 @@
         <v>283</v>
       </c>
       <c r="C65" s="25" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D65" s="27" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E65" s="27" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" hidden="1">
       <c r="A66" s="24">
         <v>8435433518471</v>
       </c>
       <c r="B66" s="25" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C66" s="25" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D66" s="27" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E66" s="27" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" hidden="1">
       <c r="A67" s="24">
         <v>8435425577783</v>
       </c>
       <c r="B67" s="25" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C67" s="25" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D67" s="27" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E67" s="27" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -16546,16 +16450,16 @@
         <v>8435433560159</v>
       </c>
       <c r="B68" s="27" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C68" s="25" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D68" s="27" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E68" s="27" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -16563,16 +16467,16 @@
         <v>8435433560210</v>
       </c>
       <c r="B69" s="27" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C69" s="25" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D69" s="27" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E69" s="27" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -16580,16 +16484,16 @@
         <v>8429991787493</v>
       </c>
       <c r="B70" s="27" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C70" s="25" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D70" s="27" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E70" s="27" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -16597,16 +16501,16 @@
         <v>8429991787509</v>
       </c>
       <c r="B71" s="27" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C71" s="25" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D71" s="27" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E71" s="27" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -16614,16 +16518,16 @@
         <v>8429991787516</v>
       </c>
       <c r="B72" s="27" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C72" s="25" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D72" s="27" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E72" s="27" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -16631,16 +16535,16 @@
         <v>8435433538103</v>
       </c>
       <c r="B73" s="27" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C73" s="25" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D73" s="27" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E73" s="27" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -16651,33 +16555,33 @@
         <v>147</v>
       </c>
       <c r="C74" s="25" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D74" s="27" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E74" s="27" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" hidden="1">
       <c r="A75" s="24">
         <v>3663602848349</v>
       </c>
       <c r="B75" s="25" t="s">
+        <v>538</v>
+      </c>
+      <c r="C75" s="25" t="s">
         <v>539</v>
       </c>
-      <c r="C75" s="25" t="s">
-        <v>540</v>
-      </c>
       <c r="D75" s="25" t="s">
+        <v>459</v>
+      </c>
+      <c r="E75" s="25" t="s">
         <v>460</v>
       </c>
-      <c r="E75" s="25" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
+    </row>
+    <row r="76" spans="1:5" hidden="1">
       <c r="A76" s="24">
         <v>5059340460222</v>
       </c>
@@ -16685,33 +16589,33 @@
         <v>10</v>
       </c>
       <c r="C76" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D76" s="25" t="s">
+        <v>459</v>
+      </c>
+      <c r="E76" s="25" t="s">
         <v>460</v>
       </c>
-      <c r="E76" s="25" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
+    </row>
+    <row r="77" spans="1:5" hidden="1">
       <c r="A77" s="24">
         <v>3663602848363</v>
       </c>
       <c r="B77" s="25" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C77" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D77" s="25" t="s">
+        <v>459</v>
+      </c>
+      <c r="E77" s="25" t="s">
         <v>460</v>
       </c>
-      <c r="E77" s="25" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
+    </row>
+    <row r="78" spans="1:5" hidden="1">
       <c r="A78" s="24">
         <v>5059340719559</v>
       </c>
@@ -16719,84 +16623,84 @@
         <v>28</v>
       </c>
       <c r="C78" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D78" s="25" t="s">
+        <v>459</v>
+      </c>
+      <c r="E78" s="25" t="s">
         <v>460</v>
       </c>
-      <c r="E78" s="25" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
+    </row>
+    <row r="79" spans="1:5" hidden="1">
       <c r="A79" s="24">
         <v>8432712279436</v>
       </c>
       <c r="B79" s="25" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C79" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D79" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E79" s="25" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" hidden="1">
       <c r="A80" s="24">
         <v>8432712279467</v>
       </c>
       <c r="B80" s="25" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C80" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D80" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E80" s="25" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" hidden="1">
       <c r="A81" s="24">
         <v>8435414111127</v>
       </c>
       <c r="B81" s="25" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C81" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D81" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E81" s="25" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" hidden="1">
       <c r="A82" s="24">
         <v>8435414124240</v>
       </c>
       <c r="B82" s="25" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C82" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D82" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E82" s="25" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" hidden="1">
       <c r="A83" s="24">
         <v>5036581063887</v>
       </c>
@@ -16804,268 +16708,268 @@
         <v>21</v>
       </c>
       <c r="C83" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D83" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E83" s="25" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" hidden="1">
       <c r="A84" s="24">
         <v>5036581063504</v>
       </c>
       <c r="B84" s="25" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C84" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D84" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E84" s="25" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" hidden="1">
       <c r="A85" s="24">
         <v>5036581063542</v>
       </c>
       <c r="B85" s="25" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C85" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D85" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E85" s="25" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" hidden="1">
       <c r="A86" s="24">
         <v>5036581063580</v>
       </c>
       <c r="B86" s="25" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C86" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D86" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E86" s="25" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" hidden="1">
       <c r="A87" s="24">
         <v>5036581064679</v>
       </c>
       <c r="B87" s="25" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C87" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D87" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E87" s="25" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" hidden="1">
       <c r="A88" s="24">
         <v>5036581064716</v>
       </c>
       <c r="B88" s="25" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C88" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D88" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E88" s="25" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" hidden="1">
       <c r="A89" s="24">
         <v>5036581064723</v>
       </c>
       <c r="B89" s="25" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C89" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D89" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E89" s="25" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" hidden="1">
       <c r="A90" s="24">
         <v>5036581064754</v>
       </c>
       <c r="B90" s="25" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C90" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D90" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E90" s="25" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" hidden="1">
       <c r="A91" s="24">
         <v>5036581064686</v>
       </c>
       <c r="B91" s="25" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C91" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D91" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E91" s="25" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" hidden="1">
       <c r="A92" s="24">
         <v>5063022089120</v>
       </c>
       <c r="B92" s="25" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C92" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D92" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E92" s="25" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" hidden="1">
       <c r="A93" s="24">
         <v>5059340719634</v>
       </c>
       <c r="B93" s="25" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C93" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D93" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E93" s="25" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" hidden="1">
       <c r="A94" s="24">
         <v>5059340719603</v>
       </c>
       <c r="B94" s="25" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C94" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D94" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E94" s="25" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" hidden="1">
       <c r="A95" s="24">
         <v>5036581064310</v>
       </c>
       <c r="B95" s="25" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C95" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D95" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E95" s="25" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" hidden="1">
       <c r="A96" s="24">
         <v>5036581064327</v>
       </c>
       <c r="B96" s="25" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C96" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D96" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E96" s="25" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" hidden="1">
       <c r="A97" s="24">
         <v>5059340269535</v>
       </c>
       <c r="B97" s="25" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C97" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D97" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E97" s="25" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" hidden="1">
       <c r="A98" s="24">
         <v>8429991787660</v>
       </c>
       <c r="B98" s="25" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C98" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D98" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E98" s="25" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -17073,16 +16977,16 @@
         <v>5036581065768</v>
       </c>
       <c r="B99" s="25" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C99" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D99" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E99" s="25" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -17090,16 +16994,16 @@
         <v>5036581065775</v>
       </c>
       <c r="B100" s="25" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C100" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D100" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E100" s="25" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -17110,13 +17014,13 @@
         <v>38</v>
       </c>
       <c r="C101" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D101" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E101" s="25" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -17127,13 +17031,13 @@
         <v>64</v>
       </c>
       <c r="C102" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D102" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E102" s="25" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -17144,13 +17048,13 @@
         <v>58</v>
       </c>
       <c r="C103" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D103" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E103" s="25" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -17161,13 +17065,13 @@
         <v>61</v>
       </c>
       <c r="C104" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D104" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E104" s="25" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -17175,16 +17079,16 @@
         <v>5036581065744</v>
       </c>
       <c r="B105" s="25" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C105" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D105" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E105" s="25" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -17192,16 +17096,16 @@
         <v>5036581065751</v>
       </c>
       <c r="B106" s="25" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C106" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D106" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E106" s="25" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -17209,16 +17113,16 @@
         <v>5036581089542</v>
       </c>
       <c r="B107" s="25" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C107" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D107" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E107" s="25" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -17226,16 +17130,16 @@
         <v>5036581089566</v>
       </c>
       <c r="B108" s="25" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C108" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D108" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E108" s="25" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -17243,16 +17147,16 @@
         <v>5036581089597</v>
       </c>
       <c r="B109" s="25" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C109" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D109" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E109" s="25" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -17260,16 +17164,16 @@
         <v>5036581089535</v>
       </c>
       <c r="B110" s="25" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C110" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D110" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E110" s="25" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -17277,16 +17181,16 @@
         <v>5036581089559</v>
       </c>
       <c r="B111" s="25" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C111" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D111" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E111" s="25" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -17294,16 +17198,16 @@
         <v>5036581089580</v>
       </c>
       <c r="B112" s="25" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C112" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D112" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E112" s="25" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -17311,16 +17215,16 @@
         <v>8435433542377</v>
       </c>
       <c r="B113" s="25" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C113" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D113" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E113" s="25" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -17328,16 +17232,16 @@
         <v>8435433542438</v>
       </c>
       <c r="B114" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C114" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D114" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E114" s="25" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -17345,16 +17249,16 @@
         <v>8435433544142</v>
       </c>
       <c r="B115" s="25" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C115" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D115" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E115" s="25" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -17362,16 +17266,16 @@
         <v>8435433544173</v>
       </c>
       <c r="B116" s="25" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C116" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D116" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E116" s="25" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -17379,16 +17283,16 @@
         <v>8429991787707</v>
       </c>
       <c r="B117" s="25" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C117" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D117" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E117" s="25" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -17396,16 +17300,16 @@
         <v>8429991787714</v>
       </c>
       <c r="B118" s="25" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C118" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D118" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E118" s="25" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -17416,13 +17320,13 @@
         <v>49</v>
       </c>
       <c r="C119" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D119" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E119" s="25" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -17433,13 +17337,13 @@
         <v>46</v>
       </c>
       <c r="C120" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D120" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E120" s="25" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -17450,13 +17354,13 @@
         <v>43</v>
       </c>
       <c r="C121" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D121" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E121" s="25" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -17467,84 +17371,84 @@
         <v>40</v>
       </c>
       <c r="C122" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D122" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E122" s="25" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" hidden="1">
       <c r="A123" s="24">
         <v>5036581064877</v>
       </c>
       <c r="B123" s="25" t="s">
+        <v>576</v>
+      </c>
+      <c r="C123" s="25" t="s">
         <v>577</v>
       </c>
-      <c r="C123" s="25" t="s">
-        <v>578</v>
-      </c>
       <c r="D123" s="25" t="s">
+        <v>459</v>
+      </c>
+      <c r="E123" s="25" t="s">
         <v>460</v>
       </c>
-      <c r="E123" s="25" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5">
+    </row>
+    <row r="124" spans="1:5" hidden="1">
       <c r="A124" s="24">
         <v>5036581064884</v>
       </c>
       <c r="B124" s="25" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C124" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D124" s="25" t="s">
+        <v>459</v>
+      </c>
+      <c r="E124" s="25" t="s">
         <v>460</v>
       </c>
-      <c r="E124" s="25" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5">
+    </row>
+    <row r="125" spans="1:5" hidden="1">
       <c r="A125" s="24">
         <v>8429991787653</v>
       </c>
       <c r="B125" s="25" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C125" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D125" s="25" t="s">
+        <v>459</v>
+      </c>
+      <c r="E125" s="25" t="s">
         <v>460</v>
       </c>
-      <c r="E125" s="25" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5">
+    </row>
+    <row r="126" spans="1:5" hidden="1">
       <c r="A126" s="24">
         <v>8435414126275</v>
       </c>
       <c r="B126" s="25" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C126" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D126" s="25" t="s">
+        <v>459</v>
+      </c>
+      <c r="E126" s="25" t="s">
         <v>460</v>
       </c>
-      <c r="E126" s="25" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5">
+    </row>
+    <row r="127" spans="1:5" hidden="1">
       <c r="A127" s="24">
         <v>5059340719542</v>
       </c>
@@ -17552,16 +17456,16 @@
         <v>72</v>
       </c>
       <c r="C127" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D127" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E127" s="25" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" hidden="1">
       <c r="A128" s="24">
         <v>5059340719627</v>
       </c>
@@ -17569,16 +17473,16 @@
         <v>71</v>
       </c>
       <c r="C128" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D128" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E128" s="25" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" hidden="1">
       <c r="A129" s="24">
         <v>5059340719528</v>
       </c>
@@ -17586,16 +17490,16 @@
         <v>69</v>
       </c>
       <c r="C129" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D129" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E129" s="25" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" hidden="1">
       <c r="A130" s="24">
         <v>5059340781976</v>
       </c>
@@ -17603,67 +17507,67 @@
         <v>65</v>
       </c>
       <c r="C130" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D130" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E130" s="25" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" hidden="1">
       <c r="A131" s="24">
         <v>5036581065201</v>
       </c>
       <c r="B131" s="25" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C131" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D131" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E131" s="25" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" hidden="1">
       <c r="A132" s="24">
         <v>5036581065218</v>
       </c>
       <c r="B132" s="25" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C132" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D132" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E132" s="25" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" hidden="1">
       <c r="A133" s="24">
         <v>8429991787646</v>
       </c>
       <c r="B133" s="25" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C133" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D133" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E133" s="25" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" hidden="1">
       <c r="A134" s="24">
         <v>8432712288490</v>
       </c>
@@ -17671,33 +17575,33 @@
         <v>81</v>
       </c>
       <c r="C134" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D134" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E134" s="25" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" hidden="1">
       <c r="A135" s="24">
         <v>8432712289541</v>
       </c>
       <c r="B135" s="25" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C135" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D135" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E135" s="25" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" hidden="1">
       <c r="A136" s="24">
         <v>8432712288551</v>
       </c>
@@ -17705,16 +17609,16 @@
         <v>77</v>
       </c>
       <c r="C136" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D136" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E136" s="25" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" hidden="1">
       <c r="A137" s="24">
         <v>8432712292367</v>
       </c>
@@ -17722,16 +17626,16 @@
         <v>76</v>
       </c>
       <c r="C137" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D137" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E137" s="25" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" hidden="1">
       <c r="A138" s="24">
         <v>8432712288582</v>
       </c>
@@ -17739,16 +17643,16 @@
         <v>249</v>
       </c>
       <c r="C138" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D138" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E138" s="25" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" hidden="1">
       <c r="A139" s="24">
         <v>8432712292398</v>
       </c>
@@ -17756,98 +17660,98 @@
         <v>70</v>
       </c>
       <c r="C139" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D139" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E139" s="25" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" hidden="1">
       <c r="A140" s="24">
         <v>5059340719610</v>
       </c>
       <c r="B140" s="25" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C140" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D140" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E140" s="25" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" hidden="1">
       <c r="A141" s="24">
         <v>5059340719566</v>
       </c>
       <c r="B141" s="25" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C141" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D141" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E141" s="25" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" hidden="1">
       <c r="A142" s="24">
         <v>5059340719511</v>
       </c>
       <c r="B142" s="25" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C142" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D142" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E142" s="25" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" hidden="1">
       <c r="A143" s="24">
         <v>5063022525574</v>
       </c>
       <c r="B143" s="25" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C143" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D143" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E143" s="25" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" hidden="1">
       <c r="A144" s="24">
         <v>8435433537328</v>
       </c>
       <c r="B144" s="25" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C144" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D144" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E144" s="25" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -17858,13 +17762,13 @@
         <v>84</v>
       </c>
       <c r="C145" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D145" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E145" s="25" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -17872,16 +17776,16 @@
         <v>8429991787622</v>
       </c>
       <c r="B146" s="25" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C146" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D146" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E146" s="25" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -17889,16 +17793,16 @@
         <v>8429991792282</v>
       </c>
       <c r="B147" s="25" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C147" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D147" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E147" s="25" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -17906,16 +17810,16 @@
         <v>5059340719658</v>
       </c>
       <c r="B148" s="25" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C148" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D148" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E148" s="25" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -17923,16 +17827,16 @@
         <v>5059340460277</v>
       </c>
       <c r="B149" s="25" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C149" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D149" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E149" s="25" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -17940,16 +17844,16 @@
         <v>5059340460284</v>
       </c>
       <c r="B150" s="25" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C150" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D150" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E150" s="25" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -17957,16 +17861,16 @@
         <v>5059340719535</v>
       </c>
       <c r="B151" s="25" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C151" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D151" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E151" s="25" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -17974,16 +17878,16 @@
         <v>8429991787639</v>
       </c>
       <c r="B152" s="25" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C152" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D152" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E152" s="25" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -17994,13 +17898,13 @@
         <v>39</v>
       </c>
       <c r="C153" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D153" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E153" s="25" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -18011,13 +17915,13 @@
         <v>32</v>
       </c>
       <c r="C154" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D154" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E154" s="25" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -18028,13 +17932,13 @@
         <v>75</v>
       </c>
       <c r="C155" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D155" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E155" s="25" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -18042,16 +17946,16 @@
         <v>5059340854229</v>
       </c>
       <c r="B156" s="25" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C156" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D156" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E156" s="25" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -18062,13 +17966,13 @@
         <v>263</v>
       </c>
       <c r="C157" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D157" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E157" s="25" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -18076,16 +17980,16 @@
         <v>8435414125100</v>
       </c>
       <c r="B158" s="25" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C158" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D158" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E158" s="25" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -18093,16 +17997,16 @@
         <v>8435414125131</v>
       </c>
       <c r="B159" s="25" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C159" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D159" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E159" s="25" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -18110,16 +18014,16 @@
         <v>8435414124189</v>
       </c>
       <c r="B160" s="25" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C160" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D160" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E160" s="25" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -18127,16 +18031,16 @@
         <v>8435414122574</v>
       </c>
       <c r="B161" s="25" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C161" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D161" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E161" s="25" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -18144,254 +18048,254 @@
         <v>8435414122468</v>
       </c>
       <c r="B162" s="25" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C162" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D162" s="25" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E162" s="25" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" hidden="1">
       <c r="A163" s="24">
         <v>5059340221700</v>
       </c>
       <c r="B163" s="36" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C163" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D163" s="36" t="s">
+        <v>459</v>
+      </c>
+      <c r="E163" s="36" t="s">
         <v>460</v>
       </c>
-      <c r="E163" s="36" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5">
+    </row>
+    <row r="164" spans="1:5" hidden="1">
       <c r="A164" s="24">
         <v>5063022611239</v>
       </c>
       <c r="B164" s="36" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C164" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D164" s="36" t="s">
+        <v>459</v>
+      </c>
+      <c r="E164" s="36" t="s">
         <v>460</v>
       </c>
-      <c r="E164" s="36" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5">
+    </row>
+    <row r="165" spans="1:5" hidden="1">
       <c r="A165" s="24">
         <v>5059340357447</v>
       </c>
       <c r="B165" s="36" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C165" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D165" s="36" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E165" s="36" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" hidden="1">
       <c r="A166" s="24">
         <v>5059340357454</v>
       </c>
       <c r="B166" s="36" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C166" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D166" s="36" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E166" s="36" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" hidden="1">
       <c r="A167" s="24">
         <v>5059340357461</v>
       </c>
       <c r="B167" s="36" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C167" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D167" s="36" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E167" s="36" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" hidden="1">
       <c r="A168" s="24">
         <v>5059340221717</v>
       </c>
       <c r="B168" s="36" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C168" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D168" s="36" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E168" s="36" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" hidden="1">
       <c r="A169" s="24">
         <v>5059340802602</v>
       </c>
       <c r="B169" s="36" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C169" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D169" s="36" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E169" s="36" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" hidden="1">
       <c r="A170" s="24">
         <v>5059340802367</v>
       </c>
       <c r="B170" s="36" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C170" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D170" s="36" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E170" s="36" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" hidden="1">
       <c r="A171" s="24">
         <v>5059340802305</v>
       </c>
       <c r="B171" s="36" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C171" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D171" s="36" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E171" s="36" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" hidden="1">
       <c r="A172" s="24">
         <v>5059340802626</v>
       </c>
       <c r="B172" s="36" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C172" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D172" s="36" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E172" s="36" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" hidden="1">
       <c r="A173" s="24">
         <v>5059340802336</v>
       </c>
       <c r="B173" s="36" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C173" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D173" s="36" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E173" s="36" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" hidden="1">
       <c r="A174" s="24">
         <v>5059340802923</v>
       </c>
       <c r="B174" s="36" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C174" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D174" s="36" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E174" s="36" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" hidden="1">
       <c r="A175" s="24">
         <v>5059340802558</v>
       </c>
       <c r="B175" s="36" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C175" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D175" s="36" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E175" s="36" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" hidden="1">
       <c r="A176" s="24">
         <v>5059340802831</v>
       </c>
       <c r="B176" s="36" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C176" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D176" s="36" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E176" s="36" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -18399,16 +18303,16 @@
         <v>5059340969657</v>
       </c>
       <c r="B177" s="36" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C177" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D177" s="36" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E177" s="36" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -18416,16 +18320,16 @@
         <v>5059340969633</v>
       </c>
       <c r="B178" s="36" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C178" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D178" s="36" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E178" s="36" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -18433,16 +18337,16 @@
         <v>5059340969640</v>
       </c>
       <c r="B179" s="36" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C179" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D179" s="36" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E179" s="36" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -18450,16 +18354,16 @@
         <v>5059340969664</v>
       </c>
       <c r="B180" s="36" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C180" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D180" s="36" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E180" s="36" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -18467,16 +18371,16 @@
         <v>5059340969626</v>
       </c>
       <c r="B181" s="36" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C181" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D181" s="36" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E181" s="36" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -18484,16 +18388,16 @@
         <v>5059340802473</v>
       </c>
       <c r="B182" s="36" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C182" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D182" s="36" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E182" s="36" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -18501,16 +18405,16 @@
         <v>5059340802725</v>
       </c>
       <c r="B183" s="36" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C183" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D183" s="36" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E183" s="36" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -18518,36 +18422,36 @@
         <v>5059340803074</v>
       </c>
       <c r="B184" s="36" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C184" s="25" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D184" s="36" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E184" s="36" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" hidden="1">
       <c r="A185" s="24">
         <v>3663602997436</v>
       </c>
       <c r="B185" s="36" t="s">
+        <v>623</v>
+      </c>
+      <c r="C185" s="25" t="s">
         <v>624</v>
       </c>
-      <c r="C185" s="25" t="s">
-        <v>625</v>
-      </c>
       <c r="D185" s="36" t="s">
+        <v>459</v>
+      </c>
+      <c r="E185" s="36" t="s">
         <v>460</v>
       </c>
-      <c r="E185" s="36" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5">
+    </row>
+    <row r="186" spans="1:5" hidden="1">
       <c r="A186" s="24">
         <v>5063022047847</v>
       </c>
@@ -18555,50 +18459,50 @@
         <v>206</v>
       </c>
       <c r="C186" s="25" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D186" s="36" t="s">
+        <v>459</v>
+      </c>
+      <c r="E186" s="36" t="s">
         <v>460</v>
       </c>
-      <c r="E186" s="36" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5">
+    </row>
+    <row r="187" spans="1:5" hidden="1">
       <c r="A187" s="24">
         <v>5063022085658</v>
       </c>
       <c r="B187" s="36" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C187" s="25" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D187" s="36" t="s">
+        <v>459</v>
+      </c>
+      <c r="E187" s="36" t="s">
         <v>460</v>
       </c>
-      <c r="E187" s="36" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5">
+    </row>
+    <row r="188" spans="1:5" hidden="1">
       <c r="A188" s="24">
         <v>3663602997962</v>
       </c>
       <c r="B188" s="36" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C188" s="25" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D188" s="36" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E188" s="36" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" hidden="1">
       <c r="A189" s="24">
         <v>5063022069450</v>
       </c>
@@ -18606,33 +18510,33 @@
         <v>191</v>
       </c>
       <c r="C189" s="25" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D189" s="36" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E189" s="36" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" hidden="1">
       <c r="A190" s="24">
         <v>5063022606525</v>
       </c>
       <c r="B190" s="36" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C190" s="25" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D190" s="36" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E190" s="36" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" hidden="1">
       <c r="A191" s="24">
         <v>5063022047755</v>
       </c>
@@ -18640,50 +18544,50 @@
         <v>190</v>
       </c>
       <c r="C191" s="25" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D191" s="36" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E191" s="36" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" hidden="1">
       <c r="A192" s="24">
         <v>5059340194042</v>
       </c>
       <c r="B192" s="36" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C192" s="25" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D192" s="36" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E192" s="36" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="193" spans="1:5">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" hidden="1">
       <c r="A193" s="24">
         <v>5063022606068</v>
       </c>
       <c r="B193" s="36" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C193" s="25" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D193" s="36" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E193" s="36" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="194" spans="1:5">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" hidden="1">
       <c r="A194" s="24">
         <v>5059340485362</v>
       </c>
@@ -18691,16 +18595,16 @@
         <v>184</v>
       </c>
       <c r="C194" s="25" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D194" s="36" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E194" s="36" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="195" spans="1:5">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" hidden="1">
       <c r="A195" s="24">
         <v>5063022085603</v>
       </c>
@@ -18708,16 +18612,16 @@
         <v>193</v>
       </c>
       <c r="C195" s="25" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D195" s="36" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E195" s="36" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="196" spans="1:5">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" hidden="1">
       <c r="A196" s="24">
         <v>5059340194080</v>
       </c>
@@ -18725,16 +18629,16 @@
         <v>199</v>
       </c>
       <c r="C196" s="25" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D196" s="36" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E196" s="36" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="197" spans="1:5">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" hidden="1">
       <c r="A197" s="24">
         <v>5059340216034</v>
       </c>
@@ -18742,16 +18646,16 @@
         <v>194</v>
       </c>
       <c r="C197" s="25" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D197" s="36" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E197" s="36" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="198" spans="1:5">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" hidden="1">
       <c r="A198" s="24">
         <v>5059340194097</v>
       </c>
@@ -18759,13 +18663,13 @@
         <v>185</v>
       </c>
       <c r="C198" s="25" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D198" s="36" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E198" s="36" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -18776,13 +18680,13 @@
         <v>204</v>
       </c>
       <c r="C199" s="25" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D199" s="36" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E199" s="36" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -18790,16 +18694,16 @@
         <v>5063022085641</v>
       </c>
       <c r="B200" s="36" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C200" s="25" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D200" s="36" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E200" s="36" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -18807,16 +18711,16 @@
         <v>5063022034496</v>
       </c>
       <c r="B201" s="36" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C201" s="25" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D201" s="36" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E201" s="36" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -18827,13 +18731,13 @@
         <v>207</v>
       </c>
       <c r="C202" s="25" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D202" s="36" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E202" s="36" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -18841,16 +18745,16 @@
         <v>5063022606020</v>
       </c>
       <c r="B203" s="36" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C203" s="25" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D203" s="36" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E203" s="36" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -18858,16 +18762,16 @@
         <v>5063022606037</v>
       </c>
       <c r="B204" s="36" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C204" s="25" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D204" s="36" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E204" s="36" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -18875,16 +18779,16 @@
         <v>5063022606013</v>
       </c>
       <c r="B205" s="36" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C205" s="25" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D205" s="36" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E205" s="36" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -18895,13 +18799,13 @@
         <v>188</v>
       </c>
       <c r="C206" s="25" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D206" s="36" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E206" s="36" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -18912,13 +18816,13 @@
         <v>187</v>
       </c>
       <c r="C207" s="25" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D207" s="36" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E207" s="36" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -18929,13 +18833,13 @@
         <v>201</v>
       </c>
       <c r="C208" s="25" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D208" s="36" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E208" s="36" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -18943,16 +18847,16 @@
         <v>5059340194035</v>
       </c>
       <c r="B209" s="36" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C209" s="25" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D209" s="36" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E209" s="36" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -18963,13 +18867,13 @@
         <v>183</v>
       </c>
       <c r="C210" s="25" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D210" s="36" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E210" s="36" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
   </sheetData>

--- a/ceramica_proyecto.xlsx
+++ b/ceramica_proyecto.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29203"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Camero\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{110E6A90-6A5B-4057-B3DF-3C305FC3FDF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF455C7E-FD3B-469C-BCFA-6261F67DC0D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" xr2:uid="{6A0D054A-EA90-43D3-9946-5E896568E0A7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{6A0D054A-EA90-43D3-9946-5E896568E0A7}"/>
   </bookViews>
   <sheets>
     <sheet name="EXISTENCIA TOTAL" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1433" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1472" uniqueCount="650">
   <si>
     <t>EAN</t>
   </si>
@@ -1000,6 +1000,45 @@
     <t>LAMA CLICK HARMONIA SPC 5,5 MM ROBLE GRIS 122X18</t>
   </si>
   <si>
+    <t>LOSETA CLICK ELIZA 4MM MOSAICO 30X60</t>
+  </si>
+  <si>
+    <t>LOSETA CLICK FOLK GRIS 3.2MM 30X60</t>
+  </si>
+  <si>
+    <t>LAMA CLICK ELIZA 4MM ROBLE GRIS CLARO 122X15</t>
+  </si>
+  <si>
+    <t>LOSETA CLICK ELIZA 4MM GRIS CLARO 30X60</t>
+  </si>
+  <si>
+    <t>LOSETA PVC AUTOADHESIVO PIZARRA 1.2MM 30X30</t>
+  </si>
+  <si>
+    <t>LOSETA PVC AUTOADHESIVO GRIS CLARO 1.2MM 30X30</t>
+  </si>
+  <si>
+    <t>LAMA PVC AUTOADHESIVO ROBLE RUSTICO 1.8MM 91X15</t>
+  </si>
+  <si>
+    <t>LAMA PVC AUTOADHESIVO ROBLE OSCURO POPROCK 2MM 91X15</t>
+  </si>
+  <si>
+    <t>LAMA PVC AUTOADHESIVO ROBLE MIEL POPROCK 2MM 91X15</t>
+  </si>
+  <si>
+    <t>LAMA PVC AUTOADHESIVO ROBLE BLANCO POPROCK 2MM 91X15</t>
+  </si>
+  <si>
+    <t>LOSETA PVC AUTOADHESIVO MULTI COLOR POPROCK 2MM 30X60</t>
+  </si>
+  <si>
+    <t>LOSETA PVC AUTOADHESICO PIEDRA POPROCK 2MM 30X60</t>
+  </si>
+  <si>
+    <t>LOSETA PVC AUTOADHESICO GRIS OSCURO POPROCK 2MM 30X60</t>
+  </si>
+  <si>
     <t>ubicacion</t>
   </si>
   <si>
@@ -1442,6 +1481,45 @@
   </si>
   <si>
     <t>28-02-403</t>
+  </si>
+  <si>
+    <t>28-01-202</t>
+  </si>
+  <si>
+    <t>28-01-301</t>
+  </si>
+  <si>
+    <t>28-01-302</t>
+  </si>
+  <si>
+    <t>28-01-303</t>
+  </si>
+  <si>
+    <t>28-01-401</t>
+  </si>
+  <si>
+    <t>28-01-402</t>
+  </si>
+  <si>
+    <t>28-01-403</t>
+  </si>
+  <si>
+    <t>28-01-501</t>
+  </si>
+  <si>
+    <t>28-01-502</t>
+  </si>
+  <si>
+    <t>28-01-503</t>
+  </si>
+  <si>
+    <t>28-01-601</t>
+  </si>
+  <si>
+    <t>28-01-602</t>
+  </si>
+  <si>
+    <t>28-01-603</t>
   </si>
   <si>
     <t>AZ. OCTAVIO 30X90 MADERA NATURAL</t>
@@ -3947,45 +4025,18 @@
     <t>LAMA CLICK FOLK 3.2MM ROBLE NATURAL 122X15</t>
   </si>
   <si>
+    <t>RACK 08b</t>
+  </si>
+  <si>
     <t>ADINA SPC CLICK 5MM ROBLE NATURAL 122X23</t>
   </si>
   <si>
-    <t>LAMA CLICK ELIZA 4MM ROBLE GRIS CLARO 122X15</t>
-  </si>
-  <si>
     <t>LAMA CLICK ELIZA 4MM ROBLE GRIS MARRON 122X15</t>
   </si>
   <si>
     <t>LAMA CLICK ELIZA 4MM RAYAS MULTIPLES 122X15</t>
   </si>
   <si>
-    <t>LOSETA CLICK FOLK GRIS 3.2MM 30X60</t>
-  </si>
-  <si>
-    <t>LOSETA CLICK ELIZA 4MM GRIS CLARO 30X60</t>
-  </si>
-  <si>
-    <t>LOSETA CLICK ELIZA 4MM MOSAICO 30X60</t>
-  </si>
-  <si>
-    <t>LAMA PVC ROBLE RUSTICO 1.8MM 91X15</t>
-  </si>
-  <si>
-    <t>LOSETA PVC SLATE 1.2MM 30X30</t>
-  </si>
-  <si>
-    <t>LOSETA PVC GRIS 1.2MM 30X30</t>
-  </si>
-  <si>
-    <t>LOSETA PVC MULTI 2MM 30X60</t>
-  </si>
-  <si>
-    <t>LOSETA PVC GRIS OSCURO 2MM 30X60</t>
-  </si>
-  <si>
-    <t>#A LOSETA PVC BEIGE 2MM 30X60</t>
-  </si>
-  <si>
     <t>HARMONIA SPC CLICK 5,5 MM ROBLE GRIS 122X18</t>
   </si>
   <si>
@@ -3999,15 +4050,6 @@
   </si>
   <si>
     <t>HARMONIA SPC CLICK 5,5 MM ROBLE NORDICO 122X18</t>
-  </si>
-  <si>
-    <t>LAMA PVC ROBLE BLANCO 2MM 91X15</t>
-  </si>
-  <si>
-    <t>LAMA PVC ROBLE MIEL 2MM 91X15</t>
-  </si>
-  <si>
-    <t>LAMA PVC GRIS CLARO 2MM 91X15</t>
   </si>
   <si>
     <t>LLAMINADO OPP AC3 6MM 129X19</t>
@@ -4053,7 +4095,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4166,12 +4208,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="6"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -4250,7 +4286,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4310,7 +4346,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4795,8 +4830,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B316A91F-BC6A-408F-AA01-35561A65966D}" name="EXISTENCIA" displayName="EXISTENCIA" ref="A1:J208" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
-  <autoFilter ref="A1:J208" xr:uid="{B316A91F-BC6A-408F-AA01-35561A65966D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B316A91F-BC6A-408F-AA01-35561A65966D}" name="EXISTENCIA" displayName="EXISTENCIA" ref="A1:J221" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+  <autoFilter ref="A1:J221" xr:uid="{B316A91F-BC6A-408F-AA01-35561A65966D}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{6CD20384-3102-4E56-BA14-58859CA75225}" name="EAN" dataDxfId="29"/>
     <tableColumn id="2" xr3:uid="{B5149655-3C4D-42C7-B824-E60428700228}" name="descrpcion_es" dataDxfId="28"/>
@@ -4828,8 +4863,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E092D5E8-DDBA-4DC5-B48F-DE814A493E02}" name="ALMACEN" displayName="ALMACEN" ref="A1:C128" totalsRowShown="0" dataDxfId="19" headerRowBorderDxfId="17" tableBorderDxfId="18">
-  <autoFilter ref="A1:C128" xr:uid="{E092D5E8-DDBA-4DC5-B48F-DE814A493E02}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E092D5E8-DDBA-4DC5-B48F-DE814A493E02}" name="ALMACEN" displayName="ALMACEN" ref="A1:C141" totalsRowShown="0" dataDxfId="19" headerRowBorderDxfId="17" tableBorderDxfId="18">
+  <autoFilter ref="A1:C141" xr:uid="{E092D5E8-DDBA-4DC5-B48F-DE814A493E02}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{3A65B69D-D98E-4AEB-961F-5593E79CA067}" name="EAN" dataDxfId="16"/>
     <tableColumn id="2" xr3:uid="{469CD1D5-7294-47E9-B0FB-BA7DD9CCC96D}" name="descrpcion_es" dataDxfId="15"/>
@@ -4853,13 +4888,7 @@
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{04895F0D-CED9-49B0-B76F-B45DB5CC94A2}" name="SHOWROOM" displayName="SHOWROOM" ref="A1:E210" totalsRowShown="0" dataDxfId="7" headerRowBorderDxfId="5" tableBorderDxfId="6">
-  <autoFilter ref="A1:E210" xr:uid="{04895F0D-CED9-49B0-B76F-B45DB5CC94A2}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="MODULO 2"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:E210" xr:uid="{04895F0D-CED9-49B0-B76F-B45DB5CC94A2}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{988177E9-8B74-4DA8-8D93-E60B539BC797}" name="EAN" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{9354D9B3-F652-4D41-B841-C67C7F44B562}" name="descrpcion_es" dataDxfId="3"/>
@@ -5171,11 +5200,11 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J208"/>
+  <dimension ref="A1:J221"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="59.7109375" customWidth="1"/>
+    <col min="2" max="2" width="65.42578125" customWidth="1"/>
     <col min="3" max="3" width="25.7109375" style="11" hidden="1" customWidth="1"/>
     <col min="4" max="7" width="22.42578125" style="11" customWidth="1"/>
     <col min="8" max="8" width="16.7109375" style="11" bestFit="1" customWidth="1"/>
@@ -5316,7 +5345,7 @@
       </c>
       <c r="G4" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
-        <v>FILA 4</v>
+        <v>FILA 5</v>
       </c>
       <c r="H4" s="15" t="str">
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
@@ -5433,7 +5462,7 @@
       </c>
       <c r="G7" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
-        <v>FILA 4</v>
+        <v>FILA 5</v>
       </c>
       <c r="H7" s="15" t="str">
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
@@ -5628,7 +5657,7 @@
       </c>
       <c r="G12" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
-        <v>FILA 5</v>
+        <v>FILA 4</v>
       </c>
       <c r="H12" s="15" t="str">
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
@@ -5745,7 +5774,7 @@
       </c>
       <c r="G15" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
-        <v>FILA 5</v>
+        <v>FILA 4</v>
       </c>
       <c r="H15" s="15" t="str">
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
@@ -5784,7 +5813,7 @@
       </c>
       <c r="G16" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
-        <v>FILA 5</v>
+        <v>FILA 4</v>
       </c>
       <c r="H16" s="15" t="str">
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
@@ -5862,7 +5891,7 @@
       </c>
       <c r="G18" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
-        <v>FILA 5</v>
+        <v>FILA 4</v>
       </c>
       <c r="H18" s="15" t="str">
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
@@ -11037,19 +11066,19 @@
       </c>
       <c r="D151" s="14" t="str">
         <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>NO</v>
-      </c>
-      <c r="E151" s="14" t="e">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F151" s="14" t="e">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G151" s="14" t="e">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
-        <v>#N/A</v>
+        <v>SI</v>
+      </c>
+      <c r="E151" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 10</v>
+      </c>
+      <c r="F151" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
+        <v>MODULO 1</v>
+      </c>
+      <c r="G151" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
+        <v>FILA 2</v>
       </c>
       <c r="H151" s="15" t="str">
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
@@ -11942,10 +11971,10 @@
       </c>
     </row>
     <row r="175" spans="1:10" ht="15.75">
-      <c r="A175" s="40">
+      <c r="A175" s="39">
         <v>5059340194073</v>
       </c>
-      <c r="B175" s="42" t="s">
+      <c r="B175" s="41" t="s">
         <v>183</v>
       </c>
       <c r="C175" s="14"/>
@@ -12016,10 +12045,10 @@
       </c>
     </row>
     <row r="177" spans="1:10" ht="15.75">
-      <c r="A177" s="40">
+      <c r="A177" s="39">
         <v>5059340194097</v>
       </c>
-      <c r="B177" s="42" t="s">
+      <c r="B177" s="41" t="s">
         <v>185</v>
       </c>
       <c r="C177" s="14"/>
@@ -12053,10 +12082,10 @@
       </c>
     </row>
     <row r="178" spans="1:10" ht="15.75">
-      <c r="A178" s="41">
+      <c r="A178" s="40">
         <v>3663602997962</v>
       </c>
-      <c r="B178" s="43" t="s">
+      <c r="B178" s="42" t="s">
         <v>186</v>
       </c>
       <c r="C178" s="14"/>
@@ -12090,10 +12119,10 @@
       </c>
     </row>
     <row r="179" spans="1:10" ht="15.75">
-      <c r="A179" s="40">
+      <c r="A179" s="39">
         <v>5059340484303</v>
       </c>
-      <c r="B179" s="42" t="s">
+      <c r="B179" s="41" t="s">
         <v>187</v>
       </c>
       <c r="C179" s="14"/>
@@ -12127,10 +12156,10 @@
       </c>
     </row>
     <row r="180" spans="1:10" ht="15.75">
-      <c r="A180" s="40">
+      <c r="A180" s="39">
         <v>5063022047816</v>
       </c>
-      <c r="B180" s="42" t="s">
+      <c r="B180" s="41" t="s">
         <v>188</v>
       </c>
       <c r="C180" s="14"/>
@@ -12164,10 +12193,10 @@
       </c>
     </row>
     <row r="181" spans="1:10" ht="15.75">
-      <c r="A181" s="40">
+      <c r="A181" s="39">
         <v>5059340194035</v>
       </c>
-      <c r="B181" s="42" t="s">
+      <c r="B181" s="41" t="s">
         <v>189</v>
       </c>
       <c r="C181" s="14"/>
@@ -12201,10 +12230,10 @@
       </c>
     </row>
     <row r="182" spans="1:10" ht="15.75">
-      <c r="A182" s="40">
+      <c r="A182" s="39">
         <v>5063022047755</v>
       </c>
-      <c r="B182" s="42" t="s">
+      <c r="B182" s="41" t="s">
         <v>190</v>
       </c>
       <c r="C182" s="14"/>
@@ -12238,10 +12267,10 @@
       </c>
     </row>
     <row r="183" spans="1:10" ht="15.75">
-      <c r="A183" s="40">
+      <c r="A183" s="39">
         <v>5063022069450</v>
       </c>
-      <c r="B183" s="42" t="s">
+      <c r="B183" s="41" t="s">
         <v>191</v>
       </c>
       <c r="C183" s="14"/>
@@ -12275,10 +12304,10 @@
       </c>
     </row>
     <row r="184" spans="1:10" ht="15.75">
-      <c r="A184" s="40">
+      <c r="A184" s="39">
         <v>5063022085658</v>
       </c>
-      <c r="B184" s="42" t="s">
+      <c r="B184" s="41" t="s">
         <v>192</v>
       </c>
       <c r="C184" s="14"/>
@@ -12312,10 +12341,10 @@
       </c>
     </row>
     <row r="185" spans="1:10" ht="15.75">
-      <c r="A185" s="40">
+      <c r="A185" s="39">
         <v>5063022085603</v>
       </c>
-      <c r="B185" s="42" t="s">
+      <c r="B185" s="41" t="s">
         <v>193</v>
       </c>
       <c r="C185" s="14"/>
@@ -12349,10 +12378,10 @@
       </c>
     </row>
     <row r="186" spans="1:10" ht="15.75">
-      <c r="A186" s="40">
+      <c r="A186" s="39">
         <v>5059340216034</v>
       </c>
-      <c r="B186" s="42" t="s">
+      <c r="B186" s="41" t="s">
         <v>194</v>
       </c>
       <c r="C186" s="14"/>
@@ -12386,10 +12415,10 @@
       </c>
     </row>
     <row r="187" spans="1:10" ht="30">
-      <c r="A187" s="40">
+      <c r="A187" s="39">
         <v>5063022606068</v>
       </c>
-      <c r="B187" s="42" t="s">
+      <c r="B187" s="41" t="s">
         <v>195</v>
       </c>
       <c r="C187" s="14"/>
@@ -12423,10 +12452,10 @@
       </c>
     </row>
     <row r="188" spans="1:10" ht="30">
-      <c r="A188" s="40">
+      <c r="A188" s="39">
         <v>5063022606020</v>
       </c>
-      <c r="B188" s="42" t="s">
+      <c r="B188" s="41" t="s">
         <v>196</v>
       </c>
       <c r="C188" s="14"/>
@@ -12460,10 +12489,10 @@
       </c>
     </row>
     <row r="189" spans="1:10" ht="30">
-      <c r="A189" s="40">
+      <c r="A189" s="39">
         <v>5063022606037</v>
       </c>
-      <c r="B189" s="42" t="s">
+      <c r="B189" s="41" t="s">
         <v>197</v>
       </c>
       <c r="C189" s="14"/>
@@ -12497,10 +12526,10 @@
       </c>
     </row>
     <row r="190" spans="1:10" ht="30">
-      <c r="A190" s="40">
+      <c r="A190" s="39">
         <v>5063022606013</v>
       </c>
-      <c r="B190" s="42" t="s">
+      <c r="B190" s="41" t="s">
         <v>198</v>
       </c>
       <c r="C190" s="14"/>
@@ -12534,10 +12563,10 @@
       </c>
     </row>
     <row r="191" spans="1:10" ht="15.75">
-      <c r="A191" s="40">
+      <c r="A191" s="39">
         <v>5059340194080</v>
       </c>
-      <c r="B191" s="42" t="s">
+      <c r="B191" s="41" t="s">
         <v>199</v>
       </c>
       <c r="C191" s="14"/>
@@ -12571,10 +12600,10 @@
       </c>
     </row>
     <row r="192" spans="1:10" ht="30">
-      <c r="A192" s="40">
+      <c r="A192" s="39">
         <v>5063022606525</v>
       </c>
-      <c r="B192" s="42" t="s">
+      <c r="B192" s="41" t="s">
         <v>200</v>
       </c>
       <c r="C192" s="14"/>
@@ -12608,10 +12637,10 @@
       </c>
     </row>
     <row r="193" spans="1:10" ht="15.75">
-      <c r="A193" s="40">
+      <c r="A193" s="39">
         <v>5063022047823</v>
       </c>
-      <c r="B193" s="42" t="s">
+      <c r="B193" s="41" t="s">
         <v>201</v>
       </c>
       <c r="C193" s="14"/>
@@ -12880,7 +12909,7 @@
       </c>
       <c r="E200" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 08</v>
+        <v>RACK 08b</v>
       </c>
       <c r="F200" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
@@ -12917,7 +12946,7 @@
       </c>
       <c r="E201" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 08</v>
+        <v>RACK 08b</v>
       </c>
       <c r="F201" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
@@ -12954,7 +12983,7 @@
       </c>
       <c r="E202" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 08</v>
+        <v>RACK 08b</v>
       </c>
       <c r="F202" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
@@ -12991,7 +13020,7 @@
       </c>
       <c r="E203" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 08</v>
+        <v>RACK 08b</v>
       </c>
       <c r="F203" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
@@ -13028,7 +13057,7 @@
       </c>
       <c r="E204" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 08</v>
+        <v>RACK 08b</v>
       </c>
       <c r="F204" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
@@ -13065,7 +13094,7 @@
       </c>
       <c r="E205" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 08</v>
+        <v>RACK 08b</v>
       </c>
       <c r="F205" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
@@ -13102,7 +13131,7 @@
       </c>
       <c r="E206" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 08</v>
+        <v>RACK 08b</v>
       </c>
       <c r="F206" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
@@ -13139,7 +13168,7 @@
       </c>
       <c r="E207" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 08</v>
+        <v>RACK 08b</v>
       </c>
       <c r="F207" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
@@ -13176,7 +13205,7 @@
       </c>
       <c r="E208" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 08</v>
+        <v>RACK 08b</v>
       </c>
       <c r="F208" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
@@ -13197,6 +13226,487 @@
       <c r="J208" s="13" t="str">
         <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
         <v>22-15-103</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10" ht="16.5">
+      <c r="A209" s="39">
+        <v>5059340802367</v>
+      </c>
+      <c r="B209" s="41" t="s">
+        <v>217</v>
+      </c>
+      <c r="C209" s="14"/>
+      <c r="D209" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E209" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 08b</v>
+      </c>
+      <c r="F209" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
+        <v>MODULO 1</v>
+      </c>
+      <c r="G209" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
+        <v>FILA 3</v>
+      </c>
+      <c r="H209" s="15" t="str">
+        <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="I209" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J209" s="13" t="str">
+        <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
+        <v>28-01-202</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" ht="16.5">
+      <c r="A210" s="39">
+        <v>5059340221717</v>
+      </c>
+      <c r="B210" s="41" t="s">
+        <v>218</v>
+      </c>
+      <c r="C210" s="14"/>
+      <c r="D210" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E210" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 08b</v>
+      </c>
+      <c r="F210" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
+        <v>MODULO 1</v>
+      </c>
+      <c r="G210" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
+        <v>FILA 3</v>
+      </c>
+      <c r="H210" s="15" t="str">
+        <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="I210" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J210" s="13" t="str">
+        <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
+        <v>28-01-301</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" ht="16.5">
+      <c r="A211" s="39">
+        <v>5059340357447</v>
+      </c>
+      <c r="B211" s="41" t="s">
+        <v>219</v>
+      </c>
+      <c r="C211" s="14"/>
+      <c r="D211" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E211" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 08b</v>
+      </c>
+      <c r="F211" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
+        <v>MODULO 1</v>
+      </c>
+      <c r="G211" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
+        <v>FILA 2</v>
+      </c>
+      <c r="H211" s="15" t="str">
+        <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="I211" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J211" s="13" t="str">
+        <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
+        <v>28-01-302</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10" ht="16.5">
+      <c r="A212" s="39">
+        <v>5059340802602</v>
+      </c>
+      <c r="B212" s="41" t="s">
+        <v>220</v>
+      </c>
+      <c r="C212" s="14"/>
+      <c r="D212" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E212" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 08b</v>
+      </c>
+      <c r="F212" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
+        <v>MODULO 1</v>
+      </c>
+      <c r="G212" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
+        <v>FILA 3</v>
+      </c>
+      <c r="H212" s="15" t="str">
+        <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="I212" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J212" s="13" t="str">
+        <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
+        <v>28-01-303</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10" ht="16.5">
+      <c r="A213" s="39">
+        <v>5059340802626</v>
+      </c>
+      <c r="B213" s="41" t="s">
+        <v>221</v>
+      </c>
+      <c r="C213" s="14"/>
+      <c r="D213" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E213" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 08b</v>
+      </c>
+      <c r="F213" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
+        <v>MODULO 1</v>
+      </c>
+      <c r="G213" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
+        <v>FILA 4</v>
+      </c>
+      <c r="H213" s="15" t="str">
+        <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="I213" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J213" s="13" t="str">
+        <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
+        <v>28-01-401</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10" ht="16.5">
+      <c r="A214" s="39">
+        <v>5059340802336</v>
+      </c>
+      <c r="B214" s="41" t="s">
+        <v>222</v>
+      </c>
+      <c r="C214" s="14"/>
+      <c r="D214" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E214" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 08b</v>
+      </c>
+      <c r="F214" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
+        <v>MODULO 1</v>
+      </c>
+      <c r="G214" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
+        <v>FILA 4</v>
+      </c>
+      <c r="H214" s="15" t="str">
+        <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="I214" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J214" s="13" t="str">
+        <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
+        <v>28-01-402</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10" ht="16.5">
+      <c r="A215" s="39">
+        <v>5059340802305</v>
+      </c>
+      <c r="B215" s="41" t="s">
+        <v>223</v>
+      </c>
+      <c r="C215" s="14"/>
+      <c r="D215" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E215" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 08b</v>
+      </c>
+      <c r="F215" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
+        <v>MODULO 1</v>
+      </c>
+      <c r="G215" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
+        <v>FILA 4</v>
+      </c>
+      <c r="H215" s="15" t="str">
+        <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="I215" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J215" s="13" t="str">
+        <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
+        <v>28-01-403</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10" ht="16.5">
+      <c r="A216" s="39">
+        <v>5059340803074</v>
+      </c>
+      <c r="B216" s="41" t="s">
+        <v>224</v>
+      </c>
+      <c r="C216" s="14"/>
+      <c r="D216" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E216" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 08b</v>
+      </c>
+      <c r="F216" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
+        <v>MODULO 2</v>
+      </c>
+      <c r="G216" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
+        <v>FILA 5</v>
+      </c>
+      <c r="H216" s="15" t="str">
+        <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="I216" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J216" s="13" t="str">
+        <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
+        <v>28-01-501</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10" ht="16.5">
+      <c r="A217" s="39">
+        <v>5059340802725</v>
+      </c>
+      <c r="B217" s="41" t="s">
+        <v>225</v>
+      </c>
+      <c r="C217" s="14"/>
+      <c r="D217" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E217" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 08b</v>
+      </c>
+      <c r="F217" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
+        <v>MODULO 2</v>
+      </c>
+      <c r="G217" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
+        <v>FILA 5</v>
+      </c>
+      <c r="H217" s="15" t="str">
+        <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="I217" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J217" s="13" t="str">
+        <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
+        <v>28-01-502</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10" ht="16.5">
+      <c r="A218" s="39">
+        <v>5059340802473</v>
+      </c>
+      <c r="B218" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="C218" s="14"/>
+      <c r="D218" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E218" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 08b</v>
+      </c>
+      <c r="F218" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
+        <v>MODULO 2</v>
+      </c>
+      <c r="G218" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
+        <v>FILA 5</v>
+      </c>
+      <c r="H218" s="15" t="str">
+        <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="I218" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J218" s="13" t="str">
+        <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
+        <v>28-01-503</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10" ht="16.5">
+      <c r="A219" s="39">
+        <v>5059340802923</v>
+      </c>
+      <c r="B219" s="41" t="s">
+        <v>227</v>
+      </c>
+      <c r="C219" s="14"/>
+      <c r="D219" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E219" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 08b</v>
+      </c>
+      <c r="F219" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
+        <v>MODULO 1</v>
+      </c>
+      <c r="G219" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
+        <v>FILA 5</v>
+      </c>
+      <c r="H219" s="15" t="str">
+        <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="I219" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J219" s="13" t="str">
+        <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
+        <v>28-01-601</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10" ht="16.5">
+      <c r="A220" s="39">
+        <v>5059340802831</v>
+      </c>
+      <c r="B220" s="41" t="s">
+        <v>228</v>
+      </c>
+      <c r="C220" s="14"/>
+      <c r="D220" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E220" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 08b</v>
+      </c>
+      <c r="F220" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
+        <v>MODULO 1</v>
+      </c>
+      <c r="G220" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
+        <v>FILA 5</v>
+      </c>
+      <c r="H220" s="15" t="str">
+        <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="I220" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J220" s="13" t="str">
+        <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
+        <v>28-01-602</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" ht="16.5">
+      <c r="A221" s="39">
+        <v>5059340802558</v>
+      </c>
+      <c r="B221" s="41" t="s">
+        <v>229</v>
+      </c>
+      <c r="C221" s="14"/>
+      <c r="D221" s="14" t="str">
+        <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="E221" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>RACK 08b</v>
+      </c>
+      <c r="F221" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
+        <v>MODULO 1</v>
+      </c>
+      <c r="G221" s="14" t="str">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
+        <v>FILA 5</v>
+      </c>
+      <c r="H221" s="15" t="str">
+        <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="I221" s="16" t="str">
+        <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J221" s="13" t="str">
+        <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
+        <v>28-01-603</v>
       </c>
     </row>
   </sheetData>
@@ -13210,7 +13720,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DD18BE2-0DBC-4BB4-8FBE-BFB232B0B51D}">
-  <dimension ref="A1:C128"/>
+  <dimension ref="A1:C141"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
@@ -13225,7 +13735,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -13233,10 +13743,10 @@
         <v>5036581063542</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="C2" s="31" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -13247,7 +13757,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -13258,7 +13768,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -13269,7 +13779,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -13280,7 +13790,7 @@
         <v>12</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -13291,7 +13801,7 @@
         <v>10</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -13302,7 +13812,7 @@
         <v>17</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -13313,7 +13823,7 @@
         <v>13</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -13321,10 +13831,10 @@
         <v>5036581064327</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -13335,7 +13845,7 @@
         <v>14</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -13346,7 +13856,7 @@
         <v>24</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -13354,10 +13864,10 @@
         <v>8435433544142</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -13368,7 +13878,7 @@
         <v>48</v>
       </c>
       <c r="C14" s="31" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -13379,7 +13889,7 @@
         <v>47</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -13390,7 +13900,7 @@
         <v>56</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -13401,7 +13911,7 @@
         <v>60</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -13412,7 +13922,7 @@
         <v>58</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -13423,7 +13933,7 @@
         <v>57</v>
       </c>
       <c r="C19" s="31" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -13434,7 +13944,7 @@
         <v>59</v>
       </c>
       <c r="C20" s="31" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -13445,7 +13955,7 @@
         <v>63</v>
       </c>
       <c r="C21" s="31" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -13456,7 +13966,7 @@
         <v>43</v>
       </c>
       <c r="C22" s="31" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -13464,10 +13974,10 @@
         <v>8435433542377</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="C23" s="31" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -13478,7 +13988,7 @@
         <v>50</v>
       </c>
       <c r="C24" s="31" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -13489,7 +13999,7 @@
         <v>40</v>
       </c>
       <c r="C25" s="31" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -13500,7 +14010,7 @@
         <v>70</v>
       </c>
       <c r="C26" s="34" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -13511,7 +14021,7 @@
         <v>76</v>
       </c>
       <c r="C27" s="31" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -13522,7 +14032,7 @@
         <v>81</v>
       </c>
       <c r="C28" s="31" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -13530,10 +14040,10 @@
         <v>8432712288582</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="C29" s="31" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -13544,7 +14054,7 @@
         <v>69</v>
       </c>
       <c r="C30" s="31" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -13552,10 +14062,10 @@
         <v>5036581064884</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="C31" s="31" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -13566,7 +14076,7 @@
         <v>77</v>
       </c>
       <c r="C32" s="31" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -13577,7 +14087,7 @@
         <v>67</v>
       </c>
       <c r="C33" s="31" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -13588,7 +14098,7 @@
         <v>66</v>
       </c>
       <c r="C34" s="31" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -13599,7 +14109,7 @@
         <v>71</v>
       </c>
       <c r="C35" s="31" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -13610,7 +14120,7 @@
         <v>136</v>
       </c>
       <c r="C36" s="31" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -13621,7 +14131,7 @@
         <v>137</v>
       </c>
       <c r="C37" s="31" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -13632,7 +14142,7 @@
         <v>140</v>
       </c>
       <c r="C38" s="31" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -13643,7 +14153,7 @@
         <v>139</v>
       </c>
       <c r="C39" s="31" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -13654,7 +14164,7 @@
         <v>138</v>
       </c>
       <c r="C40" s="31" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -13662,10 +14172,10 @@
         <v>5059340854205</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="C41" s="31" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -13676,7 +14186,7 @@
         <v>39</v>
       </c>
       <c r="C42" s="31" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -13687,7 +14197,7 @@
         <v>84</v>
       </c>
       <c r="C43" s="31" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -13698,7 +14208,7 @@
         <v>34</v>
       </c>
       <c r="C44" s="31" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -13709,7 +14219,7 @@
         <v>31</v>
       </c>
       <c r="C45" s="31" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -13720,7 +14230,7 @@
         <v>37</v>
       </c>
       <c r="C46" s="31" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -13731,7 +14241,7 @@
         <v>131</v>
       </c>
       <c r="C47" s="31" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -13742,7 +14252,7 @@
         <v>132</v>
       </c>
       <c r="C48" s="31" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -13753,7 +14263,7 @@
         <v>135</v>
       </c>
       <c r="C49" s="31" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -13764,7 +14274,7 @@
         <v>134</v>
       </c>
       <c r="C50" s="31" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -13775,7 +14285,7 @@
         <v>148</v>
       </c>
       <c r="C51" s="31" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -13786,7 +14296,7 @@
         <v>147</v>
       </c>
       <c r="C52" s="31" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -13797,7 +14307,7 @@
         <v>142</v>
       </c>
       <c r="C53" s="31" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -13808,7 +14318,7 @@
         <v>145</v>
       </c>
       <c r="C54" s="31" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -13819,7 +14329,7 @@
         <v>152</v>
       </c>
       <c r="C55" s="31" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -13827,10 +14337,10 @@
         <v>8435609351932</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="C56" s="32" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -13838,10 +14348,10 @@
         <v>8435425577783</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="C57" s="31" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -13849,10 +14359,10 @@
         <v>5059340721033</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="C58" s="31" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -13860,10 +14370,10 @@
         <v>8435433538103</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C59" s="32" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -13871,10 +14381,10 @@
         <v>8435433560210</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="C60" s="31" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -13885,7 +14395,7 @@
         <v>179</v>
       </c>
       <c r="C61" s="31" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -13896,7 +14406,7 @@
         <v>153</v>
       </c>
       <c r="C62" s="31" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -13907,7 +14417,7 @@
         <v>161</v>
       </c>
       <c r="C63" s="32" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -13918,7 +14428,7 @@
         <v>130</v>
       </c>
       <c r="C64" s="31" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -13929,7 +14439,7 @@
         <v>123</v>
       </c>
       <c r="C65" s="31" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -13937,10 +14447,10 @@
         <v>8432712270556</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="C66" s="31" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -13948,10 +14458,10 @@
         <v>8435609373682</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="C67" s="31" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -13959,10 +14469,10 @@
         <v>8429991784904</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C68" s="31" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -13973,7 +14483,7 @@
         <v>103</v>
       </c>
       <c r="C69" s="31" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -13984,7 +14494,7 @@
         <v>100</v>
       </c>
       <c r="C70" s="31" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -13995,7 +14505,7 @@
         <v>95</v>
       </c>
       <c r="C71" s="31" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -14006,7 +14516,7 @@
         <v>93</v>
       </c>
       <c r="C72" s="31" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -14017,7 +14527,7 @@
         <v>107</v>
       </c>
       <c r="C73" s="31" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -14028,7 +14538,7 @@
         <v>126</v>
       </c>
       <c r="C74" s="31" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -14039,7 +14549,7 @@
         <v>119</v>
       </c>
       <c r="C75" s="32" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -14050,7 +14560,7 @@
         <v>113</v>
       </c>
       <c r="C76" s="32" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -14061,7 +14571,7 @@
         <v>116</v>
       </c>
       <c r="C77" s="32" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -14072,7 +14582,7 @@
         <v>168</v>
       </c>
       <c r="C78" s="32" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -14080,10 +14590,10 @@
         <v>3663602678298</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="C79" s="31" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -14094,7 +14604,7 @@
         <v>114</v>
       </c>
       <c r="C80" s="31" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -14105,7 +14615,7 @@
         <v>118</v>
       </c>
       <c r="C81" s="31" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -14116,7 +14626,7 @@
         <v>122</v>
       </c>
       <c r="C82" s="32" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -14127,7 +14637,7 @@
         <v>117</v>
       </c>
       <c r="C83" s="31" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -14135,10 +14645,10 @@
         <v>5059340721026</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="C84" s="31" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -14146,10 +14656,10 @@
         <v>8429991798864</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="C85" s="31" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -14157,10 +14667,10 @@
         <v>8429991798901</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="C86" s="31" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -14168,10 +14678,10 @@
         <v>8429991798888</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="C87" s="31" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -14182,7 +14692,7 @@
         <v>22</v>
       </c>
       <c r="C88" s="31" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -14193,7 +14703,7 @@
         <v>45</v>
       </c>
       <c r="C89" s="31" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -14204,7 +14714,7 @@
         <v>62</v>
       </c>
       <c r="C90" s="31" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -14215,7 +14725,7 @@
         <v>25</v>
       </c>
       <c r="C91" s="31" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -14226,7 +14736,7 @@
         <v>32</v>
       </c>
       <c r="C92" s="31" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -14237,7 +14747,7 @@
         <v>44</v>
       </c>
       <c r="C93" s="31" t="s">
-        <v>329</v>
+        <v>342</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -14248,7 +14758,7 @@
         <v>61</v>
       </c>
       <c r="C94" s="31" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -14259,7 +14769,7 @@
         <v>38</v>
       </c>
       <c r="C95" s="31" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -14270,7 +14780,7 @@
         <v>41</v>
       </c>
       <c r="C96" s="31" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -14281,7 +14791,7 @@
         <v>29</v>
       </c>
       <c r="C97" s="31" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -14292,7 +14802,7 @@
         <v>42</v>
       </c>
       <c r="C98" s="31" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -14303,7 +14813,7 @@
         <v>49</v>
       </c>
       <c r="C99" s="31" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -14314,7 +14824,7 @@
         <v>52</v>
       </c>
       <c r="C100" s="31" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -14325,7 +14835,7 @@
         <v>55</v>
       </c>
       <c r="C101" s="31" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -14336,7 +14846,7 @@
         <v>80</v>
       </c>
       <c r="C102" s="31" t="s">
-        <v>338</v>
+        <v>351</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -14347,7 +14857,7 @@
         <v>83</v>
       </c>
       <c r="C103" s="31" t="s">
-        <v>339</v>
+        <v>352</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -14358,7 +14868,7 @@
         <v>96</v>
       </c>
       <c r="C104" s="31" t="s">
-        <v>340</v>
+        <v>353</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -14369,7 +14879,7 @@
         <v>180</v>
       </c>
       <c r="C105" s="31" t="s">
-        <v>341</v>
+        <v>354</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -14380,7 +14890,7 @@
         <v>109</v>
       </c>
       <c r="C106" s="31" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -14391,7 +14901,7 @@
         <v>128</v>
       </c>
       <c r="C107" s="31" t="s">
-        <v>343</v>
+        <v>356</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -14402,7 +14912,7 @@
         <v>144</v>
       </c>
       <c r="C108" s="31" t="s">
-        <v>344</v>
+        <v>357</v>
       </c>
     </row>
     <row r="109" spans="1:3" ht="14.25" customHeight="1">
@@ -14413,7 +14923,7 @@
         <v>65</v>
       </c>
       <c r="C109" s="31" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -14424,18 +14934,18 @@
         <v>183</v>
       </c>
       <c r="C110" s="31" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" s="24">
         <v>5059340485362</v>
       </c>
-      <c r="B111" s="37" t="s">
+      <c r="B111" s="36" t="s">
         <v>184</v>
       </c>
       <c r="C111" s="31" t="s">
-        <v>347</v>
+        <v>360</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -14446,18 +14956,18 @@
         <v>185</v>
       </c>
       <c r="C112" s="31" t="s">
-        <v>348</v>
+        <v>361</v>
       </c>
     </row>
     <row r="113" spans="1:3">
-      <c r="A113" s="38">
+      <c r="A113" s="37">
         <v>3663602997962</v>
       </c>
-      <c r="B113" s="39" t="s">
+      <c r="B113" s="38" t="s">
         <v>186</v>
       </c>
       <c r="C113" s="31" t="s">
-        <v>349</v>
+        <v>362</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -14468,7 +14978,7 @@
         <v>187</v>
       </c>
       <c r="C114" s="31" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -14479,7 +14989,7 @@
         <v>188</v>
       </c>
       <c r="C115" s="31" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -14490,7 +15000,7 @@
         <v>189</v>
       </c>
       <c r="C116" s="31" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -14501,7 +15011,7 @@
         <v>190</v>
       </c>
       <c r="C117" s="31" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -14512,7 +15022,7 @@
         <v>191</v>
       </c>
       <c r="C118" s="31" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -14523,7 +15033,7 @@
         <v>192</v>
       </c>
       <c r="C119" s="31" t="s">
-        <v>355</v>
+        <v>368</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -14534,7 +15044,7 @@
         <v>193</v>
       </c>
       <c r="C120" s="31" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -14545,7 +15055,7 @@
         <v>194</v>
       </c>
       <c r="C121" s="31" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -14556,7 +15066,7 @@
         <v>195</v>
       </c>
       <c r="C122" s="31" t="s">
-        <v>358</v>
+        <v>371</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -14567,7 +15077,7 @@
         <v>196</v>
       </c>
       <c r="C123" s="31" t="s">
-        <v>359</v>
+        <v>372</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -14578,7 +15088,7 @@
         <v>197</v>
       </c>
       <c r="C124" s="31" t="s">
-        <v>360</v>
+        <v>373</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -14589,7 +15099,7 @@
         <v>198</v>
       </c>
       <c r="C125" s="31" t="s">
-        <v>361</v>
+        <v>374</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -14600,7 +15110,7 @@
         <v>199</v>
       </c>
       <c r="C126" s="31" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -14611,7 +15121,7 @@
         <v>200</v>
       </c>
       <c r="C127" s="31" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -14622,7 +15132,150 @@
         <v>201</v>
       </c>
       <c r="C128" s="31" t="s">
-        <v>364</v>
+        <v>377</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129" s="28">
+        <v>5059340802367</v>
+      </c>
+      <c r="B129" s="29" t="s">
+        <v>217</v>
+      </c>
+      <c r="C129" s="31" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130" s="28">
+        <v>5059340221717</v>
+      </c>
+      <c r="B130" s="29" t="s">
+        <v>218</v>
+      </c>
+      <c r="C130" s="31" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131" s="28">
+        <v>5059340357447</v>
+      </c>
+      <c r="B131" s="29" t="s">
+        <v>219</v>
+      </c>
+      <c r="C131" s="31" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
+      <c r="A132" s="28">
+        <v>5059340802602</v>
+      </c>
+      <c r="B132" s="29" t="s">
+        <v>220</v>
+      </c>
+      <c r="C132" s="31" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="A133" s="28">
+        <v>5059340802626</v>
+      </c>
+      <c r="B133" s="29" t="s">
+        <v>221</v>
+      </c>
+      <c r="C133" s="31" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="A134" s="28">
+        <v>5059340802336</v>
+      </c>
+      <c r="B134" s="29" t="s">
+        <v>222</v>
+      </c>
+      <c r="C134" s="31" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
+      <c r="A135" s="28">
+        <v>5059340802305</v>
+      </c>
+      <c r="B135" s="29" t="s">
+        <v>223</v>
+      </c>
+      <c r="C135" s="31" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
+      <c r="A136" s="28">
+        <v>5059340803074</v>
+      </c>
+      <c r="B136" s="29" t="s">
+        <v>224</v>
+      </c>
+      <c r="C136" s="31" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3">
+      <c r="A137" s="28">
+        <v>5059340802725</v>
+      </c>
+      <c r="B137" s="29" t="s">
+        <v>225</v>
+      </c>
+      <c r="C137" s="31" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="A138" s="28">
+        <v>5059340802473</v>
+      </c>
+      <c r="B138" s="29" t="s">
+        <v>226</v>
+      </c>
+      <c r="C138" s="31" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139" s="28">
+        <v>5059340802923</v>
+      </c>
+      <c r="B139" s="29" t="s">
+        <v>227</v>
+      </c>
+      <c r="C139" s="31" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3">
+      <c r="A140" s="28">
+        <v>5059340802831</v>
+      </c>
+      <c r="B140" s="29" t="s">
+        <v>228</v>
+      </c>
+      <c r="C140" s="31" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3">
+      <c r="A141" s="28">
+        <v>5059340802558</v>
+      </c>
+      <c r="B141" s="29" t="s">
+        <v>229</v>
+      </c>
+      <c r="C141" s="31" t="s">
+        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -14654,7 +15307,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -14662,13 +15315,13 @@
         <v>5059340719535</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>365</v>
+        <v>391</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>366</v>
+        <v>392</v>
       </c>
       <c r="J2" t="s">
-        <v>367</v>
+        <v>393</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -14676,10 +15329,10 @@
         <v>5059340719658</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>368</v>
+        <v>394</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -14690,7 +15343,7 @@
         <v>64</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>370</v>
+        <v>396</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -14701,7 +15354,7 @@
         <v>46</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>371</v>
+        <v>397</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -14709,10 +15362,10 @@
         <v>5036581065768</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>372</v>
+        <v>398</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>373</v>
+        <v>399</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -14723,7 +15376,7 @@
         <v>72</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>374</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -14731,10 +15384,10 @@
         <v>8435414126275</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>375</v>
+        <v>401</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>376</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -14742,10 +15395,10 @@
         <v>5036581064877</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>377</v>
+        <v>403</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>378</v>
+        <v>404</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -14756,7 +15409,7 @@
         <v>28</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>379</v>
+        <v>405</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -14767,7 +15420,7 @@
         <v>20</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>380</v>
+        <v>406</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -14775,10 +15428,10 @@
         <v>5036581064310</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>381</v>
+        <v>407</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>382</v>
+        <v>408</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -14789,7 +15442,7 @@
         <v>21</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>383</v>
+        <v>409</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -14797,10 +15450,10 @@
         <v>3663602848349</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>384</v>
+        <v>410</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>385</v>
+        <v>411</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -14808,10 +15461,10 @@
         <v>5036581064679</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>386</v>
+        <v>412</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>387</v>
+        <v>413</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -14819,10 +15472,10 @@
         <v>5059340433233</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>388</v>
+        <v>414</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>389</v>
+        <v>415</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -14830,10 +15483,10 @@
         <v>8435414126282</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>390</v>
+        <v>416</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>391</v>
+        <v>417</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -14841,10 +15494,10 @@
         <v>3663602679332</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>392</v>
+        <v>418</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -14852,10 +15505,10 @@
         <v>8435414127845</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>394</v>
+        <v>420</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>395</v>
+        <v>421</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -14863,10 +15516,10 @@
         <v>8429178156050</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>396</v>
+        <v>422</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>397</v>
+        <v>423</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -14874,10 +15527,10 @@
         <v>8429178398283</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>398</v>
+        <v>424</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>399</v>
+        <v>425</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -14885,10 +15538,10 @@
         <v>8435609333952</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>400</v>
+        <v>426</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>401</v>
+        <v>427</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -14896,10 +15549,10 @@
         <v>8429178840003</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>402</v>
+        <v>428</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>403</v>
+        <v>429</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -14907,10 +15560,10 @@
         <v>8432712278026</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>404</v>
+        <v>430</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>405</v>
+        <v>431</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -14918,10 +15571,10 @@
         <v>5059340433240</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>406</v>
+        <v>432</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>407</v>
+        <v>433</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -14929,10 +15582,10 @@
         <v>5059340460383</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>408</v>
+        <v>434</v>
       </c>
       <c r="C26" s="27" t="s">
-        <v>409</v>
+        <v>435</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -14940,10 +15593,10 @@
         <v>5059340720968</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>410</v>
+        <v>436</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>411</v>
+        <v>437</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -14951,10 +15604,10 @@
         <v>8435609330777</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>412</v>
+        <v>438</v>
       </c>
       <c r="C28" s="27" t="s">
-        <v>413</v>
+        <v>439</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -14962,10 +15615,10 @@
         <v>8429991953478</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>414</v>
+        <v>440</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>415</v>
+        <v>441</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -14973,10 +15626,10 @@
         <v>5059340720951</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>416</v>
+        <v>442</v>
       </c>
       <c r="C30" s="27" t="s">
-        <v>417</v>
+        <v>443</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -14984,10 +15637,10 @@
         <v>5063022645289</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>418</v>
+        <v>444</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>419</v>
+        <v>445</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -14995,10 +15648,10 @@
         <v>8429991953577</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="C32" s="27" t="s">
-        <v>421</v>
+        <v>447</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -15006,10 +15659,10 @@
         <v>5059340870663</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>422</v>
+        <v>448</v>
       </c>
       <c r="C33" s="27" t="s">
-        <v>423</v>
+        <v>449</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -15017,10 +15670,10 @@
         <v>3663602678366</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>424</v>
+        <v>450</v>
       </c>
       <c r="C34" s="27" t="s">
-        <v>425</v>
+        <v>451</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -15028,10 +15681,10 @@
         <v>5059340719610</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>426</v>
+        <v>452</v>
       </c>
       <c r="C35" s="27" t="s">
-        <v>427</v>
+        <v>453</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -15039,10 +15692,10 @@
         <v>5059340720982</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>428</v>
+        <v>454</v>
       </c>
       <c r="C36" s="27" t="s">
-        <v>429</v>
+        <v>455</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -15050,10 +15703,10 @@
         <v>5059340720975</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>430</v>
+        <v>456</v>
       </c>
       <c r="C37" s="27" t="s">
-        <v>431</v>
+        <v>457</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -15061,10 +15714,10 @@
         <v>8435414120211</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>432</v>
+        <v>458</v>
       </c>
       <c r="C38" s="27" t="s">
-        <v>433</v>
+        <v>459</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -15072,10 +15725,10 @@
         <v>8435414118669</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>434</v>
+        <v>460</v>
       </c>
       <c r="C39" s="27" t="s">
-        <v>435</v>
+        <v>461</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -15083,10 +15736,10 @@
         <v>5036581058319</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>436</v>
+        <v>462</v>
       </c>
       <c r="C40" s="27" t="s">
-        <v>437</v>
+        <v>463</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -15094,10 +15747,10 @@
         <v>5036581058326</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>438</v>
+        <v>464</v>
       </c>
       <c r="C41" s="27" t="s">
-        <v>439</v>
+        <v>465</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -15108,10 +15761,10 @@
         <v>105</v>
       </c>
       <c r="C42" s="27" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="15.75">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
       <c r="A43" s="22">
         <v>8435609378458</v>
       </c>
@@ -15119,7 +15772,7 @@
         <v>171</v>
       </c>
       <c r="C43" s="27" t="s">
-        <v>441</v>
+        <v>467</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -15130,7 +15783,7 @@
         <v>202</v>
       </c>
       <c r="C44" s="27" t="s">
-        <v>442</v>
+        <v>468</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -15141,7 +15794,7 @@
         <v>203</v>
       </c>
       <c r="C45" s="27" t="s">
-        <v>443</v>
+        <v>469</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -15152,7 +15805,7 @@
         <v>204</v>
       </c>
       <c r="C46" s="27" t="s">
-        <v>444</v>
+        <v>470</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -15163,7 +15816,7 @@
         <v>205</v>
       </c>
       <c r="C47" s="27" t="s">
-        <v>445</v>
+        <v>471</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -15174,7 +15827,7 @@
         <v>206</v>
       </c>
       <c r="C48" s="27" t="s">
-        <v>446</v>
+        <v>472</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -15185,7 +15838,7 @@
         <v>207</v>
       </c>
       <c r="C49" s="27" t="s">
-        <v>447</v>
+        <v>473</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -15196,7 +15849,7 @@
         <v>208</v>
       </c>
       <c r="C50" s="27" t="s">
-        <v>448</v>
+        <v>474</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -15207,7 +15860,7 @@
         <v>209</v>
       </c>
       <c r="C51" s="27" t="s">
-        <v>449</v>
+        <v>475</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -15218,7 +15871,7 @@
         <v>210</v>
       </c>
       <c r="C52" s="27" t="s">
-        <v>450</v>
+        <v>476</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -15229,7 +15882,7 @@
         <v>211</v>
       </c>
       <c r="C53" s="27" t="s">
-        <v>451</v>
+        <v>477</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -15240,7 +15893,7 @@
         <v>212</v>
       </c>
       <c r="C54" s="27" t="s">
-        <v>452</v>
+        <v>478</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -15251,7 +15904,7 @@
         <v>213</v>
       </c>
       <c r="C55" s="27" t="s">
-        <v>453</v>
+        <v>479</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -15262,7 +15915,7 @@
         <v>214</v>
       </c>
       <c r="C56" s="27" t="s">
-        <v>454</v>
+        <v>480</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -15273,7 +15926,7 @@
         <v>215</v>
       </c>
       <c r="C57" s="27" t="s">
-        <v>455</v>
+        <v>481</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -15284,7 +15937,7 @@
         <v>216</v>
       </c>
       <c r="C58" s="27" t="s">
-        <v>456</v>
+        <v>482</v>
       </c>
     </row>
   </sheetData>
@@ -15301,7 +15954,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="51.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="64" customWidth="1"/>
     <col min="3" max="3" width="17.7109375" customWidth="1"/>
     <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
@@ -15323,174 +15976,174 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:5" hidden="1">
+    <row r="2" spans="1:5">
       <c r="A2" s="24">
         <v>8432712278026</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>457</v>
+        <v>483</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>458</v>
+        <v>484</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" hidden="1">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="24">
         <v>8435414127845</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>461</v>
+        <v>487</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>458</v>
+        <v>484</v>
       </c>
       <c r="D3" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" hidden="1">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="24">
         <v>5059340433240</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>462</v>
+        <v>488</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>458</v>
+        <v>484</v>
       </c>
       <c r="D4" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E4" s="25" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" hidden="1">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="24">
         <v>8429178398283</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>464</v>
+        <v>490</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>458</v>
+        <v>484</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E5" s="25" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" hidden="1">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="24">
         <v>5059340433233</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>465</v>
+        <v>491</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>458</v>
+        <v>484</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" hidden="1">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="24">
         <v>8429991784881</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>467</v>
+        <v>493</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>458</v>
+        <v>484</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" hidden="1">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="24">
         <v>5063022022561</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>468</v>
+        <v>494</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>458</v>
+        <v>484</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" hidden="1">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="24">
         <v>8435609333952</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>470</v>
+        <v>496</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>458</v>
+        <v>484</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E9" s="25" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" hidden="1">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="24">
         <v>8429991784904</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>471</v>
+        <v>497</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>458</v>
+        <v>484</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" hidden="1">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="24">
         <v>8429991784898</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>473</v>
+        <v>499</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>458</v>
+        <v>484</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>472</v>
+        <v>498</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -15498,16 +16151,16 @@
         <v>8429178840003</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>474</v>
+        <v>500</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>458</v>
+        <v>484</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>460</v>
+        <v>486</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -15515,16 +16168,16 @@
         <v>8435609373682</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>476</v>
+        <v>502</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>458</v>
+        <v>484</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -15532,16 +16185,16 @@
         <v>8435609378458</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>478</v>
+        <v>504</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>458</v>
+        <v>484</v>
       </c>
       <c r="D14" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>463</v>
+        <v>489</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -15549,16 +16202,16 @@
         <v>8429178156050</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>479</v>
+        <v>505</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>458</v>
+        <v>484</v>
       </c>
       <c r="D15" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>463</v>
+        <v>489</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -15566,16 +16219,16 @@
         <v>8435414126282</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>480</v>
+        <v>506</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>458</v>
+        <v>484</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>466</v>
+        <v>492</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -15583,16 +16236,16 @@
         <v>8435609333921</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>481</v>
+        <v>507</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>458</v>
+        <v>484</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>466</v>
+        <v>492</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -15600,16 +16253,16 @@
         <v>5059340433424</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>482</v>
+        <v>508</v>
       </c>
       <c r="C18" s="25" t="s">
-        <v>458</v>
+        <v>484</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E18" s="25" t="s">
-        <v>469</v>
+        <v>495</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -15617,16 +16270,16 @@
         <v>3663602679332</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>483</v>
+        <v>509</v>
       </c>
       <c r="C19" s="25" t="s">
-        <v>458</v>
+        <v>484</v>
       </c>
       <c r="D19" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E19" s="25" t="s">
-        <v>469</v>
+        <v>495</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -15634,16 +16287,16 @@
         <v>8435414109278</v>
       </c>
       <c r="B20" s="25" t="s">
+        <v>510</v>
+      </c>
+      <c r="C20" s="25" t="s">
         <v>484</v>
       </c>
-      <c r="C20" s="25" t="s">
-        <v>458</v>
-      </c>
       <c r="D20" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>472</v>
+        <v>498</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -15651,169 +16304,169 @@
         <v>3663602675846</v>
       </c>
       <c r="B21" s="25" t="s">
-        <v>485</v>
+        <v>511</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>458</v>
+        <v>484</v>
       </c>
       <c r="D21" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E21" s="25" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" hidden="1">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="24">
         <v>5059340721002</v>
       </c>
       <c r="B22" s="25" t="s">
+        <v>512</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>513</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="E22" s="25" t="s">
         <v>486</v>
       </c>
-      <c r="C22" s="25" t="s">
-        <v>487</v>
-      </c>
-      <c r="D22" s="25" t="s">
-        <v>459</v>
-      </c>
-      <c r="E22" s="25" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" hidden="1">
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" s="24">
         <v>8435609330777</v>
       </c>
       <c r="B23" s="25" t="s">
-        <v>488</v>
+        <v>514</v>
       </c>
       <c r="C23" s="25" t="s">
-        <v>487</v>
+        <v>513</v>
       </c>
       <c r="D23" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E23" s="25" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" hidden="1">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" s="24">
         <v>8429991798857</v>
       </c>
       <c r="B24" s="25" t="s">
-        <v>489</v>
+        <v>515</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>487</v>
+        <v>513</v>
       </c>
       <c r="D24" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E24" s="25" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" hidden="1">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" s="24">
         <v>5059340720968</v>
       </c>
       <c r="B25" s="25" t="s">
-        <v>490</v>
+        <v>516</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>487</v>
+        <v>513</v>
       </c>
       <c r="D25" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E25" s="25" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" hidden="1">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" s="24">
         <v>5063022605061</v>
       </c>
       <c r="B26" s="25" t="s">
-        <v>491</v>
+        <v>517</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>487</v>
+        <v>513</v>
       </c>
       <c r="D26" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E26" s="25" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" hidden="1">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" s="24">
         <v>5059340812311</v>
       </c>
       <c r="B27" s="25" t="s">
+        <v>518</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>513</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="E27" s="25" t="s">
         <v>492</v>
       </c>
-      <c r="C27" s="25" t="s">
-        <v>487</v>
-      </c>
-      <c r="D27" s="25" t="s">
-        <v>459</v>
-      </c>
-      <c r="E27" s="25" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" hidden="1">
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" s="24">
         <v>8429991953478</v>
       </c>
       <c r="B28" s="25" t="s">
-        <v>493</v>
+        <v>519</v>
       </c>
       <c r="C28" s="25" t="s">
-        <v>487</v>
+        <v>513</v>
       </c>
       <c r="D28" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E28" s="25" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" hidden="1">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" s="24">
         <v>5059340269610</v>
       </c>
       <c r="B29" s="25" t="s">
-        <v>494</v>
+        <v>520</v>
       </c>
       <c r="C29" s="25" t="s">
-        <v>487</v>
+        <v>513</v>
       </c>
       <c r="D29" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E29" s="25" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" hidden="1">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" s="24">
         <v>5059340874937</v>
       </c>
       <c r="B30" s="25" t="s">
+        <v>521</v>
+      </c>
+      <c r="C30" s="25" t="s">
+        <v>513</v>
+      </c>
+      <c r="D30" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="E30" s="25" t="s">
         <v>495</v>
-      </c>
-      <c r="C30" s="25" t="s">
-        <v>487</v>
-      </c>
-      <c r="D30" s="25" t="s">
-        <v>459</v>
-      </c>
-      <c r="E30" s="25" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -15824,13 +16477,13 @@
         <v>181</v>
       </c>
       <c r="C31" s="25" t="s">
-        <v>487</v>
+        <v>513</v>
       </c>
       <c r="D31" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E31" s="25" t="s">
-        <v>460</v>
+        <v>486</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -15838,16 +16491,16 @@
         <v>5059340854212</v>
       </c>
       <c r="B32" s="25" t="s">
-        <v>496</v>
+        <v>522</v>
       </c>
       <c r="C32" s="25" t="s">
-        <v>487</v>
+        <v>513</v>
       </c>
       <c r="D32" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E32" s="25" t="s">
-        <v>460</v>
+        <v>486</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -15855,16 +16508,16 @@
         <v>8429991793449</v>
       </c>
       <c r="B33" s="25" t="s">
-        <v>497</v>
+        <v>523</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>487</v>
+        <v>513</v>
       </c>
       <c r="D33" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E33" s="25" t="s">
-        <v>460</v>
+        <v>486</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -15872,16 +16525,16 @@
         <v>5059340870663</v>
       </c>
       <c r="B34" s="25" t="s">
-        <v>498</v>
+        <v>524</v>
       </c>
       <c r="C34" s="25" t="s">
-        <v>487</v>
+        <v>513</v>
       </c>
       <c r="D34" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E34" s="25" t="s">
-        <v>463</v>
+        <v>489</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -15889,16 +16542,16 @@
         <v>5059340854267</v>
       </c>
       <c r="B35" s="25" t="s">
-        <v>499</v>
+        <v>525</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>487</v>
+        <v>513</v>
       </c>
       <c r="D35" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E35" s="25" t="s">
-        <v>463</v>
+        <v>489</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -15906,16 +16559,16 @@
         <v>3663602678298</v>
       </c>
       <c r="B36" s="25" t="s">
-        <v>500</v>
+        <v>526</v>
       </c>
       <c r="C36" s="25" t="s">
-        <v>487</v>
+        <v>513</v>
       </c>
       <c r="D36" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E36" s="25" t="s">
-        <v>463</v>
+        <v>489</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -15923,16 +16576,16 @@
         <v>5059340459912</v>
       </c>
       <c r="B37" s="25" t="s">
+        <v>527</v>
+      </c>
+      <c r="C37" s="25" t="s">
+        <v>513</v>
+      </c>
+      <c r="D37" s="25" t="s">
         <v>501</v>
       </c>
-      <c r="C37" s="25" t="s">
-        <v>487</v>
-      </c>
-      <c r="D37" s="25" t="s">
-        <v>475</v>
-      </c>
       <c r="E37" s="25" t="s">
-        <v>466</v>
+        <v>492</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -15940,16 +16593,16 @@
         <v>5059340854236</v>
       </c>
       <c r="B38" s="25" t="s">
-        <v>502</v>
+        <v>528</v>
       </c>
       <c r="C38" s="25" t="s">
-        <v>487</v>
+        <v>513</v>
       </c>
       <c r="D38" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E38" s="25" t="s">
-        <v>466</v>
+        <v>492</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -15957,16 +16610,16 @@
         <v>3663602678366</v>
       </c>
       <c r="B39" s="25" t="s">
-        <v>503</v>
+        <v>529</v>
       </c>
       <c r="C39" s="25" t="s">
-        <v>487</v>
+        <v>513</v>
       </c>
       <c r="D39" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E39" s="25" t="s">
-        <v>466</v>
+        <v>492</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -15974,169 +16627,169 @@
         <v>3663602678465</v>
       </c>
       <c r="B40" s="25" t="s">
-        <v>504</v>
+        <v>530</v>
       </c>
       <c r="C40" s="25" t="s">
-        <v>487</v>
+        <v>513</v>
       </c>
       <c r="D40" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E40" s="25" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" hidden="1">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
       <c r="A41" s="24">
         <v>5059340720951</v>
       </c>
       <c r="B41" s="25" t="s">
-        <v>505</v>
+        <v>531</v>
       </c>
       <c r="C41" s="25" t="s">
-        <v>506</v>
+        <v>532</v>
       </c>
       <c r="D41" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E41" s="25" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" hidden="1">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
       <c r="A42" s="24">
         <v>5063022645289</v>
       </c>
       <c r="B42" s="25" t="s">
-        <v>507</v>
+        <v>533</v>
       </c>
       <c r="C42" s="25" t="s">
-        <v>506</v>
+        <v>532</v>
       </c>
       <c r="D42" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E42" s="25" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" hidden="1">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
       <c r="A43" s="24">
         <v>8429991798864</v>
       </c>
       <c r="B43" s="25" t="s">
-        <v>508</v>
+        <v>534</v>
       </c>
       <c r="C43" s="25" t="s">
-        <v>506</v>
+        <v>532</v>
       </c>
       <c r="D43" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E43" s="25" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" hidden="1">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
       <c r="A44" s="24">
         <v>5059340721026</v>
       </c>
       <c r="B44" s="25" t="s">
-        <v>509</v>
+        <v>535</v>
       </c>
       <c r="C44" s="25" t="s">
-        <v>506</v>
+        <v>532</v>
       </c>
       <c r="D44" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E44" s="25" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" hidden="1">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
       <c r="A45" s="24">
         <v>3663602677413</v>
       </c>
       <c r="B45" s="25" t="s">
-        <v>510</v>
+        <v>536</v>
       </c>
       <c r="C45" s="25" t="s">
-        <v>506</v>
+        <v>532</v>
       </c>
       <c r="D45" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E45" s="25" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" hidden="1">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
       <c r="A46" s="24">
         <v>8435609317396</v>
       </c>
       <c r="B46" s="25" t="s">
-        <v>511</v>
+        <v>537</v>
       </c>
       <c r="C46" s="25" t="s">
-        <v>506</v>
+        <v>532</v>
       </c>
       <c r="D46" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E46" s="25" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" hidden="1">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
       <c r="A47" s="24">
         <v>8429991953577</v>
       </c>
       <c r="B47" s="25" t="s">
-        <v>512</v>
+        <v>538</v>
       </c>
       <c r="C47" s="25" t="s">
-        <v>506</v>
+        <v>532</v>
       </c>
       <c r="D47" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E47" s="25" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" hidden="1">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
       <c r="A48" s="24">
         <v>8429991798888</v>
       </c>
       <c r="B48" s="25" t="s">
-        <v>513</v>
+        <v>539</v>
       </c>
       <c r="C48" s="25" t="s">
-        <v>506</v>
+        <v>532</v>
       </c>
       <c r="D48" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E48" s="25" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" hidden="1">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
       <c r="A49" s="24">
         <v>8429991798901</v>
       </c>
       <c r="B49" s="25" t="s">
-        <v>514</v>
+        <v>540</v>
       </c>
       <c r="C49" s="25" t="s">
-        <v>506</v>
+        <v>532</v>
       </c>
       <c r="D49" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E49" s="25" t="s">
-        <v>469</v>
+        <v>495</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -16144,16 +16797,16 @@
         <v>5059340460383</v>
       </c>
       <c r="B50" s="25" t="s">
-        <v>515</v>
+        <v>541</v>
       </c>
       <c r="C50" s="25" t="s">
-        <v>506</v>
+        <v>532</v>
       </c>
       <c r="D50" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E50" s="25" t="s">
-        <v>460</v>
+        <v>486</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -16161,16 +16814,16 @@
         <v>5059340721040</v>
       </c>
       <c r="B51" s="25" t="s">
-        <v>516</v>
+        <v>542</v>
       </c>
       <c r="C51" s="25" t="s">
-        <v>506</v>
+        <v>532</v>
       </c>
       <c r="D51" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E51" s="25" t="s">
-        <v>460</v>
+        <v>486</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -16178,16 +16831,16 @@
         <v>5059340720999</v>
       </c>
       <c r="B52" s="25" t="s">
-        <v>517</v>
+        <v>543</v>
       </c>
       <c r="C52" s="25" t="s">
-        <v>506</v>
+        <v>532</v>
       </c>
       <c r="D52" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E52" s="25" t="s">
-        <v>460</v>
+        <v>486</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -16195,16 +16848,16 @@
         <v>8432712270556</v>
       </c>
       <c r="B53" s="25" t="s">
-        <v>518</v>
+        <v>544</v>
       </c>
       <c r="C53" s="25" t="s">
-        <v>506</v>
+        <v>532</v>
       </c>
       <c r="D53" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E53" s="25" t="s">
-        <v>463</v>
+        <v>489</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -16212,16 +16865,16 @@
         <v>8435414101517</v>
       </c>
       <c r="B54" s="25" t="s">
-        <v>519</v>
+        <v>545</v>
       </c>
       <c r="C54" s="25" t="s">
-        <v>506</v>
+        <v>532</v>
       </c>
       <c r="D54" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E54" s="25" t="s">
-        <v>463</v>
+        <v>489</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -16229,138 +16882,138 @@
         <v>8429991787479</v>
       </c>
       <c r="B55" s="25" t="s">
-        <v>520</v>
+        <v>546</v>
       </c>
       <c r="C55" s="25" t="s">
-        <v>506</v>
+        <v>532</v>
       </c>
       <c r="D55" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E55" s="25" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" hidden="1">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
       <c r="A56" s="26">
         <v>5059340720982</v>
       </c>
       <c r="B56" s="27" t="s">
-        <v>521</v>
+        <v>547</v>
       </c>
       <c r="C56" s="25" t="s">
-        <v>522</v>
+        <v>548</v>
       </c>
       <c r="D56" s="27" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E56" s="27" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" hidden="1">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
       <c r="A57" s="26">
         <v>5036581058319</v>
       </c>
       <c r="B57" s="27" t="s">
-        <v>523</v>
+        <v>549</v>
       </c>
       <c r="C57" s="25" t="s">
-        <v>522</v>
+        <v>548</v>
       </c>
       <c r="D57" s="27" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E57" s="27" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" hidden="1">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
       <c r="A58" s="26">
         <v>5036581058326</v>
       </c>
       <c r="B58" s="27" t="s">
-        <v>524</v>
+        <v>550</v>
       </c>
       <c r="C58" s="25" t="s">
-        <v>522</v>
+        <v>548</v>
       </c>
       <c r="D58" s="27" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E58" s="27" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" hidden="1">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
       <c r="A59" s="26">
         <v>8429991787486</v>
       </c>
       <c r="B59" s="27" t="s">
-        <v>525</v>
+        <v>551</v>
       </c>
       <c r="C59" s="25" t="s">
-        <v>522</v>
+        <v>548</v>
       </c>
       <c r="D59" s="27" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E59" s="27" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" hidden="1">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
       <c r="A60" s="26">
-        <v>843543353813</v>
+        <v>8435433538134</v>
       </c>
       <c r="B60" s="27" t="s">
-        <v>526</v>
+        <v>552</v>
       </c>
       <c r="C60" s="25" t="s">
-        <v>522</v>
+        <v>548</v>
       </c>
       <c r="D60" s="27" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E60" s="27" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" hidden="1">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
       <c r="A61" s="26">
         <v>8435414118669</v>
       </c>
       <c r="B61" s="27" t="s">
-        <v>527</v>
+        <v>553</v>
       </c>
       <c r="C61" s="25" t="s">
-        <v>522</v>
+        <v>548</v>
       </c>
       <c r="D61" s="27" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E61" s="27" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" hidden="1">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
       <c r="A62" s="26">
         <v>8435414118645</v>
       </c>
       <c r="B62" s="27" t="s">
-        <v>528</v>
+        <v>554</v>
       </c>
       <c r="C62" s="25" t="s">
-        <v>522</v>
+        <v>548</v>
       </c>
       <c r="D62" s="27" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E62" s="27" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" hidden="1">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
       <c r="A63" s="26">
         <v>8435414120211</v>
       </c>
@@ -16368,81 +17021,81 @@
         <v>151</v>
       </c>
       <c r="C63" s="25" t="s">
-        <v>522</v>
+        <v>548</v>
       </c>
       <c r="D63" s="27" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E63" s="27" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" hidden="1">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
       <c r="A64" s="26">
         <v>8435609351932</v>
       </c>
       <c r="B64" s="27" t="s">
-        <v>529</v>
+        <v>555</v>
       </c>
       <c r="C64" s="25" t="s">
-        <v>522</v>
+        <v>548</v>
       </c>
       <c r="D64" s="27" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E64" s="27" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" hidden="1">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
       <c r="A65" s="26">
         <v>5059340721033</v>
       </c>
       <c r="B65" s="27" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="C65" s="25" t="s">
-        <v>522</v>
+        <v>548</v>
       </c>
       <c r="D65" s="27" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E65" s="27" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" hidden="1">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
       <c r="A66" s="24">
         <v>8435433518471</v>
       </c>
       <c r="B66" s="25" t="s">
-        <v>530</v>
+        <v>556</v>
       </c>
       <c r="C66" s="25" t="s">
-        <v>522</v>
+        <v>548</v>
       </c>
       <c r="D66" s="27" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E66" s="27" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" hidden="1">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
       <c r="A67" s="24">
         <v>8435425577783</v>
       </c>
       <c r="B67" s="25" t="s">
-        <v>531</v>
+        <v>557</v>
       </c>
       <c r="C67" s="25" t="s">
-        <v>522</v>
+        <v>548</v>
       </c>
       <c r="D67" s="27" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E67" s="27" t="s">
-        <v>466</v>
+        <v>492</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -16450,16 +17103,16 @@
         <v>8435433560159</v>
       </c>
       <c r="B68" s="27" t="s">
-        <v>532</v>
+        <v>558</v>
       </c>
       <c r="C68" s="25" t="s">
-        <v>522</v>
+        <v>548</v>
       </c>
       <c r="D68" s="27" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E68" s="27" t="s">
-        <v>460</v>
+        <v>486</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -16467,16 +17120,16 @@
         <v>8435433560210</v>
       </c>
       <c r="B69" s="27" t="s">
-        <v>533</v>
+        <v>559</v>
       </c>
       <c r="C69" s="25" t="s">
-        <v>522</v>
+        <v>548</v>
       </c>
       <c r="D69" s="27" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E69" s="27" t="s">
-        <v>460</v>
+        <v>486</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -16484,16 +17137,16 @@
         <v>8429991787493</v>
       </c>
       <c r="B70" s="27" t="s">
-        <v>534</v>
+        <v>560</v>
       </c>
       <c r="C70" s="25" t="s">
-        <v>522</v>
+        <v>548</v>
       </c>
       <c r="D70" s="27" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E70" s="27" t="s">
-        <v>460</v>
+        <v>486</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -16501,16 +17154,16 @@
         <v>8429991787509</v>
       </c>
       <c r="B71" s="27" t="s">
-        <v>535</v>
+        <v>561</v>
       </c>
       <c r="C71" s="25" t="s">
-        <v>522</v>
+        <v>548</v>
       </c>
       <c r="D71" s="27" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E71" s="27" t="s">
-        <v>463</v>
+        <v>489</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -16518,16 +17171,16 @@
         <v>8429991787516</v>
       </c>
       <c r="B72" s="27" t="s">
-        <v>536</v>
+        <v>562</v>
       </c>
       <c r="C72" s="25" t="s">
-        <v>522</v>
+        <v>548</v>
       </c>
       <c r="D72" s="27" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E72" s="27" t="s">
-        <v>463</v>
+        <v>489</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -16535,16 +17188,16 @@
         <v>8435433538103</v>
       </c>
       <c r="B73" s="27" t="s">
-        <v>537</v>
+        <v>563</v>
       </c>
       <c r="C73" s="25" t="s">
-        <v>522</v>
+        <v>548</v>
       </c>
       <c r="D73" s="27" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E73" s="27" t="s">
-        <v>463</v>
+        <v>489</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -16555,33 +17208,33 @@
         <v>147</v>
       </c>
       <c r="C74" s="25" t="s">
-        <v>522</v>
+        <v>548</v>
       </c>
       <c r="D74" s="27" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E74" s="27" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" hidden="1">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
       <c r="A75" s="24">
         <v>3663602848349</v>
       </c>
       <c r="B75" s="25" t="s">
-        <v>538</v>
+        <v>564</v>
       </c>
       <c r="C75" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D75" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E75" s="25" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" hidden="1">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
       <c r="A76" s="24">
         <v>5059340460222</v>
       </c>
@@ -16589,33 +17242,33 @@
         <v>10</v>
       </c>
       <c r="C76" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D76" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E76" s="25" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" hidden="1">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
       <c r="A77" s="24">
         <v>3663602848363</v>
       </c>
       <c r="B77" s="25" t="s">
-        <v>540</v>
+        <v>566</v>
       </c>
       <c r="C77" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D77" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E77" s="25" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" hidden="1">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
       <c r="A78" s="24">
         <v>5059340719559</v>
       </c>
@@ -16623,84 +17276,84 @@
         <v>28</v>
       </c>
       <c r="C78" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D78" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E78" s="25" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" hidden="1">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
       <c r="A79" s="24">
         <v>8432712279436</v>
       </c>
       <c r="B79" s="25" t="s">
-        <v>541</v>
+        <v>567</v>
       </c>
       <c r="C79" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D79" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E79" s="25" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" hidden="1">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
       <c r="A80" s="24">
         <v>8432712279467</v>
       </c>
       <c r="B80" s="25" t="s">
-        <v>542</v>
+        <v>568</v>
       </c>
       <c r="C80" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D80" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E80" s="25" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" hidden="1">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
       <c r="A81" s="24">
         <v>8435414111127</v>
       </c>
       <c r="B81" s="25" t="s">
-        <v>543</v>
+        <v>569</v>
       </c>
       <c r="C81" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D81" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E81" s="25" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" hidden="1">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
       <c r="A82" s="24">
         <v>8435414124240</v>
       </c>
       <c r="B82" s="25" t="s">
-        <v>544</v>
+        <v>570</v>
       </c>
       <c r="C82" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D82" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E82" s="25" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" hidden="1">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
       <c r="A83" s="24">
         <v>5036581063887</v>
       </c>
@@ -16708,268 +17361,268 @@
         <v>21</v>
       </c>
       <c r="C83" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D83" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E83" s="25" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" hidden="1">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
       <c r="A84" s="24">
         <v>5036581063504</v>
       </c>
       <c r="B84" s="25" t="s">
-        <v>545</v>
+        <v>571</v>
       </c>
       <c r="C84" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D84" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E84" s="25" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" hidden="1">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
       <c r="A85" s="24">
         <v>5036581063542</v>
       </c>
       <c r="B85" s="25" t="s">
-        <v>546</v>
+        <v>572</v>
       </c>
       <c r="C85" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D85" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E85" s="25" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" hidden="1">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
       <c r="A86" s="24">
         <v>5036581063580</v>
       </c>
       <c r="B86" s="25" t="s">
-        <v>547</v>
+        <v>573</v>
       </c>
       <c r="C86" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D86" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E86" s="25" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" hidden="1">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
       <c r="A87" s="24">
         <v>5036581064679</v>
       </c>
       <c r="B87" s="25" t="s">
-        <v>548</v>
+        <v>574</v>
       </c>
       <c r="C87" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D87" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E87" s="25" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" hidden="1">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
       <c r="A88" s="24">
         <v>5036581064716</v>
       </c>
       <c r="B88" s="25" t="s">
-        <v>549</v>
+        <v>575</v>
       </c>
       <c r="C88" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D88" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E88" s="25" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" hidden="1">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
       <c r="A89" s="24">
         <v>5036581064723</v>
       </c>
       <c r="B89" s="25" t="s">
-        <v>550</v>
+        <v>576</v>
       </c>
       <c r="C89" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D89" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E89" s="25" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" hidden="1">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
       <c r="A90" s="24">
         <v>5036581064754</v>
       </c>
       <c r="B90" s="25" t="s">
-        <v>551</v>
+        <v>577</v>
       </c>
       <c r="C90" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D90" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E90" s="25" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" hidden="1">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
       <c r="A91" s="24">
         <v>5036581064686</v>
       </c>
       <c r="B91" s="25" t="s">
-        <v>552</v>
+        <v>578</v>
       </c>
       <c r="C91" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D91" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E91" s="25" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" hidden="1">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
       <c r="A92" s="24">
         <v>5063022089120</v>
       </c>
       <c r="B92" s="25" t="s">
-        <v>553</v>
+        <v>579</v>
       </c>
       <c r="C92" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D92" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E92" s="25" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" hidden="1">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
       <c r="A93" s="24">
         <v>5059340719634</v>
       </c>
       <c r="B93" s="25" t="s">
-        <v>554</v>
+        <v>580</v>
       </c>
       <c r="C93" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D93" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E93" s="25" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" hidden="1">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
       <c r="A94" s="24">
         <v>5059340719603</v>
       </c>
       <c r="B94" s="25" t="s">
-        <v>555</v>
+        <v>581</v>
       </c>
       <c r="C94" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D94" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E94" s="25" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" hidden="1">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
       <c r="A95" s="24">
         <v>5036581064310</v>
       </c>
       <c r="B95" s="25" t="s">
-        <v>556</v>
+        <v>582</v>
       </c>
       <c r="C95" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D95" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E95" s="25" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" hidden="1">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
       <c r="A96" s="24">
         <v>5036581064327</v>
       </c>
       <c r="B96" s="25" t="s">
-        <v>557</v>
+        <v>583</v>
       </c>
       <c r="C96" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D96" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E96" s="25" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" hidden="1">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
       <c r="A97" s="24">
         <v>5059340269535</v>
       </c>
       <c r="B97" s="25" t="s">
-        <v>558</v>
+        <v>584</v>
       </c>
       <c r="C97" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D97" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E97" s="25" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" hidden="1">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
       <c r="A98" s="24">
         <v>8429991787660</v>
       </c>
       <c r="B98" s="25" t="s">
-        <v>559</v>
+        <v>585</v>
       </c>
       <c r="C98" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D98" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E98" s="25" t="s">
-        <v>472</v>
+        <v>495</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -16977,16 +17630,16 @@
         <v>5036581065768</v>
       </c>
       <c r="B99" s="25" t="s">
-        <v>560</v>
+        <v>586</v>
       </c>
       <c r="C99" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D99" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E99" s="25" t="s">
-        <v>460</v>
+        <v>486</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -16994,16 +17647,16 @@
         <v>5036581065775</v>
       </c>
       <c r="B100" s="25" t="s">
-        <v>561</v>
+        <v>587</v>
       </c>
       <c r="C100" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D100" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E100" s="25" t="s">
-        <v>460</v>
+        <v>486</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -17014,13 +17667,13 @@
         <v>38</v>
       </c>
       <c r="C101" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D101" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E101" s="25" t="s">
-        <v>460</v>
+        <v>486</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -17031,13 +17684,13 @@
         <v>64</v>
       </c>
       <c r="C102" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D102" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E102" s="25" t="s">
-        <v>463</v>
+        <v>489</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -17048,13 +17701,13 @@
         <v>58</v>
       </c>
       <c r="C103" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D103" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E103" s="25" t="s">
-        <v>463</v>
+        <v>489</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -17065,13 +17718,13 @@
         <v>61</v>
       </c>
       <c r="C104" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D104" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E104" s="25" t="s">
-        <v>463</v>
+        <v>489</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -17079,16 +17732,16 @@
         <v>5036581065744</v>
       </c>
       <c r="B105" s="25" t="s">
-        <v>562</v>
+        <v>588</v>
       </c>
       <c r="C105" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D105" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E105" s="25" t="s">
-        <v>463</v>
+        <v>489</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -17096,16 +17749,16 @@
         <v>5036581065751</v>
       </c>
       <c r="B106" s="25" t="s">
-        <v>563</v>
+        <v>589</v>
       </c>
       <c r="C106" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D106" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E106" s="25" t="s">
-        <v>463</v>
+        <v>489</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -17113,16 +17766,16 @@
         <v>5036581089542</v>
       </c>
       <c r="B107" s="25" t="s">
-        <v>564</v>
+        <v>590</v>
       </c>
       <c r="C107" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D107" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E107" s="25" t="s">
-        <v>466</v>
+        <v>492</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -17130,16 +17783,16 @@
         <v>5036581089566</v>
       </c>
       <c r="B108" s="25" t="s">
+        <v>591</v>
+      </c>
+      <c r="C108" s="25" t="s">
         <v>565</v>
       </c>
-      <c r="C108" s="25" t="s">
-        <v>539</v>
-      </c>
       <c r="D108" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E108" s="25" t="s">
-        <v>466</v>
+        <v>492</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -17147,16 +17800,16 @@
         <v>5036581089597</v>
       </c>
       <c r="B109" s="25" t="s">
-        <v>566</v>
+        <v>592</v>
       </c>
       <c r="C109" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D109" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E109" s="25" t="s">
-        <v>466</v>
+        <v>492</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -17164,16 +17817,16 @@
         <v>5036581089535</v>
       </c>
       <c r="B110" s="25" t="s">
-        <v>567</v>
+        <v>593</v>
       </c>
       <c r="C110" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D110" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E110" s="25" t="s">
-        <v>466</v>
+        <v>492</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -17181,16 +17834,16 @@
         <v>5036581089559</v>
       </c>
       <c r="B111" s="25" t="s">
-        <v>568</v>
+        <v>594</v>
       </c>
       <c r="C111" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D111" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E111" s="25" t="s">
-        <v>466</v>
+        <v>492</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -17198,16 +17851,16 @@
         <v>5036581089580</v>
       </c>
       <c r="B112" s="25" t="s">
-        <v>569</v>
+        <v>595</v>
       </c>
       <c r="C112" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D112" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E112" s="25" t="s">
-        <v>466</v>
+        <v>492</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -17215,16 +17868,16 @@
         <v>8435433542377</v>
       </c>
       <c r="B113" s="25" t="s">
-        <v>570</v>
+        <v>596</v>
       </c>
       <c r="C113" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D113" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E113" s="25" t="s">
-        <v>469</v>
+        <v>495</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -17232,16 +17885,16 @@
         <v>8435433542438</v>
       </c>
       <c r="B114" s="25" t="s">
-        <v>571</v>
+        <v>597</v>
       </c>
       <c r="C114" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D114" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E114" s="25" t="s">
-        <v>469</v>
+        <v>495</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -17249,16 +17902,16 @@
         <v>8435433544142</v>
       </c>
       <c r="B115" s="25" t="s">
-        <v>572</v>
+        <v>598</v>
       </c>
       <c r="C115" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D115" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E115" s="25" t="s">
-        <v>469</v>
+        <v>495</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -17266,16 +17919,16 @@
         <v>8435433544173</v>
       </c>
       <c r="B116" s="25" t="s">
-        <v>573</v>
+        <v>599</v>
       </c>
       <c r="C116" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D116" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E116" s="25" t="s">
-        <v>469</v>
+        <v>495</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -17283,16 +17936,16 @@
         <v>8429991787707</v>
       </c>
       <c r="B117" s="25" t="s">
-        <v>574</v>
+        <v>600</v>
       </c>
       <c r="C117" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D117" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E117" s="25" t="s">
-        <v>469</v>
+        <v>495</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -17300,16 +17953,16 @@
         <v>8429991787714</v>
       </c>
       <c r="B118" s="25" t="s">
-        <v>575</v>
+        <v>601</v>
       </c>
       <c r="C118" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D118" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E118" s="25" t="s">
-        <v>469</v>
+        <v>495</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -17320,13 +17973,13 @@
         <v>49</v>
       </c>
       <c r="C119" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D119" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E119" s="25" t="s">
-        <v>472</v>
+        <v>498</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -17337,13 +17990,13 @@
         <v>46</v>
       </c>
       <c r="C120" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D120" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E120" s="25" t="s">
-        <v>472</v>
+        <v>498</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -17354,13 +18007,13 @@
         <v>43</v>
       </c>
       <c r="C121" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D121" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E121" s="25" t="s">
-        <v>472</v>
+        <v>498</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -17371,84 +18024,84 @@
         <v>40</v>
       </c>
       <c r="C122" s="25" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D122" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E122" s="25" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" hidden="1">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
       <c r="A123" s="24">
         <v>5036581064877</v>
       </c>
       <c r="B123" s="25" t="s">
-        <v>576</v>
+        <v>602</v>
       </c>
       <c r="C123" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D123" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E123" s="25" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" hidden="1">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
       <c r="A124" s="24">
         <v>5036581064884</v>
       </c>
       <c r="B124" s="25" t="s">
-        <v>578</v>
+        <v>604</v>
       </c>
       <c r="C124" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D124" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E124" s="25" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" hidden="1">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
       <c r="A125" s="24">
         <v>8429991787653</v>
       </c>
       <c r="B125" s="25" t="s">
-        <v>579</v>
+        <v>605</v>
       </c>
       <c r="C125" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D125" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E125" s="25" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" hidden="1">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
       <c r="A126" s="24">
         <v>8435414126275</v>
       </c>
       <c r="B126" s="25" t="s">
-        <v>580</v>
+        <v>606</v>
       </c>
       <c r="C126" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D126" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E126" s="25" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" hidden="1">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
       <c r="A127" s="24">
         <v>5059340719542</v>
       </c>
@@ -17456,16 +18109,16 @@
         <v>72</v>
       </c>
       <c r="C127" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D127" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E127" s="25" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" hidden="1">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
       <c r="A128" s="24">
         <v>5059340719627</v>
       </c>
@@ -17473,16 +18126,16 @@
         <v>71</v>
       </c>
       <c r="C128" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D128" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E128" s="25" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" hidden="1">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5">
       <c r="A129" s="24">
         <v>5059340719528</v>
       </c>
@@ -17490,16 +18143,16 @@
         <v>69</v>
       </c>
       <c r="C129" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D129" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E129" s="25" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" hidden="1">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
       <c r="A130" s="24">
         <v>5059340781976</v>
       </c>
@@ -17507,67 +18160,67 @@
         <v>65</v>
       </c>
       <c r="C130" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D130" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E130" s="25" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" hidden="1">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
       <c r="A131" s="24">
         <v>5036581065201</v>
       </c>
       <c r="B131" s="25" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="C131" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D131" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E131" s="25" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" hidden="1">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5">
       <c r="A132" s="24">
         <v>5036581065218</v>
       </c>
       <c r="B132" s="25" t="s">
-        <v>582</v>
+        <v>608</v>
       </c>
       <c r="C132" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D132" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E132" s="25" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" hidden="1">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
       <c r="A133" s="24">
         <v>8429991787646</v>
       </c>
       <c r="B133" s="25" t="s">
-        <v>583</v>
+        <v>609</v>
       </c>
       <c r="C133" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D133" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E133" s="25" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" hidden="1">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
       <c r="A134" s="24">
         <v>8432712288490</v>
       </c>
@@ -17575,33 +18228,33 @@
         <v>81</v>
       </c>
       <c r="C134" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D134" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E134" s="25" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" hidden="1">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
       <c r="A135" s="24">
         <v>8432712289541</v>
       </c>
       <c r="B135" s="25" t="s">
-        <v>584</v>
+        <v>610</v>
       </c>
       <c r="C135" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D135" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E135" s="25" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" hidden="1">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
       <c r="A136" s="24">
         <v>8432712288551</v>
       </c>
@@ -17609,16 +18262,16 @@
         <v>77</v>
       </c>
       <c r="C136" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D136" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E136" s="25" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" hidden="1">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
       <c r="A137" s="24">
         <v>8432712292367</v>
       </c>
@@ -17626,33 +18279,33 @@
         <v>76</v>
       </c>
       <c r="C137" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D137" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E137" s="25" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" hidden="1">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
       <c r="A138" s="24">
         <v>8432712288582</v>
       </c>
       <c r="B138" s="25" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="C138" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D138" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E138" s="25" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" hidden="1">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
       <c r="A139" s="24">
         <v>8432712292398</v>
       </c>
@@ -17660,98 +18313,98 @@
         <v>70</v>
       </c>
       <c r="C139" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D139" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E139" s="25" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" hidden="1">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
       <c r="A140" s="24">
         <v>5059340719610</v>
       </c>
       <c r="B140" s="25" t="s">
-        <v>585</v>
+        <v>611</v>
       </c>
       <c r="C140" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D140" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E140" s="25" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" hidden="1">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
       <c r="A141" s="24">
         <v>5059340719566</v>
       </c>
       <c r="B141" s="25" t="s">
-        <v>586</v>
+        <v>612</v>
       </c>
       <c r="C141" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D141" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E141" s="25" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" hidden="1">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
       <c r="A142" s="24">
         <v>5059340719511</v>
       </c>
       <c r="B142" s="25" t="s">
-        <v>587</v>
+        <v>613</v>
       </c>
       <c r="C142" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D142" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E142" s="25" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" hidden="1">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
       <c r="A143" s="24">
         <v>5063022525574</v>
       </c>
       <c r="B143" s="25" t="s">
-        <v>588</v>
+        <v>614</v>
       </c>
       <c r="C143" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D143" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E143" s="25" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" hidden="1">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
       <c r="A144" s="24">
         <v>8435433537328</v>
       </c>
       <c r="B144" s="25" t="s">
-        <v>589</v>
+        <v>615</v>
       </c>
       <c r="C144" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D144" s="25" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="E144" s="25" t="s">
-        <v>472</v>
+        <v>498</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -17762,13 +18415,13 @@
         <v>84</v>
       </c>
       <c r="C145" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D145" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E145" s="25" t="s">
-        <v>460</v>
+        <v>486</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -17776,16 +18429,16 @@
         <v>8429991787622</v>
       </c>
       <c r="B146" s="25" t="s">
-        <v>590</v>
+        <v>616</v>
       </c>
       <c r="C146" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D146" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E146" s="25" t="s">
-        <v>460</v>
+        <v>486</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -17793,16 +18446,16 @@
         <v>8429991792282</v>
       </c>
       <c r="B147" s="25" t="s">
-        <v>591</v>
+        <v>617</v>
       </c>
       <c r="C147" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D147" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E147" s="25" t="s">
-        <v>460</v>
+        <v>486</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -17810,16 +18463,16 @@
         <v>5059340719658</v>
       </c>
       <c r="B148" s="25" t="s">
-        <v>368</v>
+        <v>394</v>
       </c>
       <c r="C148" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D148" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E148" s="25" t="s">
-        <v>460</v>
+        <v>486</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -17827,16 +18480,16 @@
         <v>5059340460277</v>
       </c>
       <c r="B149" s="25" t="s">
-        <v>592</v>
+        <v>618</v>
       </c>
       <c r="C149" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D149" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E149" s="25" t="s">
-        <v>463</v>
+        <v>489</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -17844,16 +18497,16 @@
         <v>5059340460284</v>
       </c>
       <c r="B150" s="25" t="s">
-        <v>593</v>
+        <v>619</v>
       </c>
       <c r="C150" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D150" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E150" s="25" t="s">
-        <v>463</v>
+        <v>489</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -17861,16 +18514,16 @@
         <v>5059340719535</v>
       </c>
       <c r="B151" s="25" t="s">
-        <v>365</v>
+        <v>391</v>
       </c>
       <c r="C151" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D151" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E151" s="25" t="s">
-        <v>463</v>
+        <v>489</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -17878,16 +18531,16 @@
         <v>8429991787639</v>
       </c>
       <c r="B152" s="25" t="s">
-        <v>594</v>
+        <v>620</v>
       </c>
       <c r="C152" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D152" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E152" s="25" t="s">
-        <v>466</v>
+        <v>492</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -17898,13 +18551,13 @@
         <v>39</v>
       </c>
       <c r="C153" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D153" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E153" s="25" t="s">
-        <v>466</v>
+        <v>492</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -17915,13 +18568,13 @@
         <v>32</v>
       </c>
       <c r="C154" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D154" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E154" s="25" t="s">
-        <v>466</v>
+        <v>492</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -17932,13 +18585,13 @@
         <v>75</v>
       </c>
       <c r="C155" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D155" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E155" s="25" t="s">
-        <v>466</v>
+        <v>492</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -17946,16 +18599,16 @@
         <v>5059340854229</v>
       </c>
       <c r="B156" s="25" t="s">
-        <v>595</v>
+        <v>621</v>
       </c>
       <c r="C156" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D156" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E156" s="25" t="s">
-        <v>469</v>
+        <v>495</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -17963,16 +18616,16 @@
         <v>5059340854205</v>
       </c>
       <c r="B157" s="25" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="C157" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D157" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E157" s="25" t="s">
-        <v>469</v>
+        <v>495</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -17980,16 +18633,16 @@
         <v>8435414125100</v>
       </c>
       <c r="B158" s="25" t="s">
-        <v>596</v>
+        <v>622</v>
       </c>
       <c r="C158" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D158" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E158" s="25" t="s">
-        <v>472</v>
+        <v>498</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -17997,16 +18650,16 @@
         <v>8435414125131</v>
       </c>
       <c r="B159" s="25" t="s">
-        <v>597</v>
+        <v>623</v>
       </c>
       <c r="C159" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D159" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E159" s="25" t="s">
-        <v>472</v>
+        <v>498</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -18014,16 +18667,16 @@
         <v>8435414124189</v>
       </c>
       <c r="B160" s="25" t="s">
-        <v>598</v>
+        <v>624</v>
       </c>
       <c r="C160" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D160" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E160" s="25" t="s">
-        <v>472</v>
+        <v>498</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -18031,16 +18684,16 @@
         <v>8435414122574</v>
       </c>
       <c r="B161" s="25" t="s">
-        <v>599</v>
+        <v>625</v>
       </c>
       <c r="C161" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D161" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E161" s="25" t="s">
-        <v>472</v>
+        <v>498</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -18048,832 +18701,832 @@
         <v>8435414122468</v>
       </c>
       <c r="B162" s="25" t="s">
-        <v>600</v>
+        <v>626</v>
       </c>
       <c r="C162" s="25" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="D162" s="25" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="E162" s="25" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5" hidden="1">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" ht="15.75">
       <c r="A163" s="24">
         <v>5059340221700</v>
       </c>
-      <c r="B163" s="36" t="s">
-        <v>601</v>
+      <c r="B163" s="25" t="s">
+        <v>627</v>
       </c>
       <c r="C163" s="25" t="s">
-        <v>577</v>
-      </c>
-      <c r="D163" s="36" t="s">
-        <v>459</v>
-      </c>
-      <c r="E163" s="36" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5" hidden="1">
+        <v>628</v>
+      </c>
+      <c r="D163" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="E163" s="25" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" ht="15.75">
       <c r="A164" s="24">
         <v>5063022611239</v>
       </c>
-      <c r="B164" s="36" t="s">
-        <v>602</v>
+      <c r="B164" s="25" t="s">
+        <v>629</v>
       </c>
       <c r="C164" s="25" t="s">
-        <v>577</v>
-      </c>
-      <c r="D164" s="36" t="s">
-        <v>459</v>
-      </c>
-      <c r="E164" s="36" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" hidden="1">
+        <v>628</v>
+      </c>
+      <c r="D164" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="E164" s="25" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" ht="15.75">
       <c r="A165" s="24">
         <v>5059340357447</v>
       </c>
-      <c r="B165" s="36" t="s">
-        <v>603</v>
+      <c r="B165" s="25" t="s">
+        <v>219</v>
       </c>
       <c r="C165" s="25" t="s">
-        <v>577</v>
-      </c>
-      <c r="D165" s="36" t="s">
-        <v>459</v>
-      </c>
-      <c r="E165" s="36" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5" hidden="1">
+        <v>628</v>
+      </c>
+      <c r="D165" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="E165" s="25" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" ht="15.75">
       <c r="A166" s="24">
         <v>5059340357454</v>
       </c>
-      <c r="B166" s="36" t="s">
-        <v>604</v>
+      <c r="B166" s="25" t="s">
+        <v>630</v>
       </c>
       <c r="C166" s="25" t="s">
-        <v>577</v>
-      </c>
-      <c r="D166" s="36" t="s">
-        <v>459</v>
-      </c>
-      <c r="E166" s="36" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5" hidden="1">
+        <v>628</v>
+      </c>
+      <c r="D166" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="E166" s="25" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" ht="15.75">
       <c r="A167" s="24">
         <v>5059340357461</v>
       </c>
-      <c r="B167" s="36" t="s">
-        <v>605</v>
+      <c r="B167" s="25" t="s">
+        <v>631</v>
       </c>
       <c r="C167" s="25" t="s">
-        <v>577</v>
-      </c>
-      <c r="D167" s="36" t="s">
-        <v>459</v>
-      </c>
-      <c r="E167" s="36" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5" hidden="1">
+        <v>628</v>
+      </c>
+      <c r="D167" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="E167" s="25" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" ht="15.75">
       <c r="A168" s="24">
         <v>5059340221717</v>
       </c>
-      <c r="B168" s="36" t="s">
-        <v>606</v>
+      <c r="B168" s="25" t="s">
+        <v>218</v>
       </c>
       <c r="C168" s="25" t="s">
-        <v>577</v>
-      </c>
-      <c r="D168" s="36" t="s">
-        <v>459</v>
-      </c>
-      <c r="E168" s="36" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5" hidden="1">
+        <v>628</v>
+      </c>
+      <c r="D168" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="E168" s="25" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" ht="15.75">
       <c r="A169" s="24">
         <v>5059340802602</v>
       </c>
-      <c r="B169" s="36" t="s">
-        <v>607</v>
+      <c r="B169" s="25" t="s">
+        <v>220</v>
       </c>
       <c r="C169" s="25" t="s">
-        <v>577</v>
-      </c>
-      <c r="D169" s="36" t="s">
-        <v>459</v>
-      </c>
-      <c r="E169" s="36" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5" hidden="1">
+        <v>628</v>
+      </c>
+      <c r="D169" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="E169" s="25" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" ht="15.75">
       <c r="A170" s="24">
         <v>5059340802367</v>
       </c>
-      <c r="B170" s="36" t="s">
-        <v>608</v>
+      <c r="B170" s="25" t="s">
+        <v>217</v>
       </c>
       <c r="C170" s="25" t="s">
-        <v>577</v>
-      </c>
-      <c r="D170" s="36" t="s">
-        <v>459</v>
-      </c>
-      <c r="E170" s="36" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5" hidden="1">
+        <v>628</v>
+      </c>
+      <c r="D170" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="E170" s="25" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" ht="15.75">
       <c r="A171" s="24">
         <v>5059340802305</v>
       </c>
-      <c r="B171" s="36" t="s">
-        <v>609</v>
+      <c r="B171" s="25" t="s">
+        <v>223</v>
       </c>
       <c r="C171" s="25" t="s">
-        <v>577</v>
-      </c>
-      <c r="D171" s="36" t="s">
-        <v>459</v>
-      </c>
-      <c r="E171" s="36" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5" hidden="1">
+        <v>628</v>
+      </c>
+      <c r="D171" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="E171" s="25" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" ht="15.75">
       <c r="A172" s="24">
         <v>5059340802626</v>
       </c>
-      <c r="B172" s="36" t="s">
-        <v>610</v>
+      <c r="B172" s="25" t="s">
+        <v>221</v>
       </c>
       <c r="C172" s="25" t="s">
-        <v>577</v>
-      </c>
-      <c r="D172" s="36" t="s">
-        <v>459</v>
-      </c>
-      <c r="E172" s="36" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5" hidden="1">
+        <v>628</v>
+      </c>
+      <c r="D172" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="E172" s="25" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" ht="15.75">
       <c r="A173" s="24">
         <v>5059340802336</v>
       </c>
-      <c r="B173" s="36" t="s">
-        <v>611</v>
+      <c r="B173" s="25" t="s">
+        <v>222</v>
       </c>
       <c r="C173" s="25" t="s">
-        <v>577</v>
-      </c>
-      <c r="D173" s="36" t="s">
-        <v>459</v>
-      </c>
-      <c r="E173" s="36" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" hidden="1">
+        <v>628</v>
+      </c>
+      <c r="D173" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="E173" s="25" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" ht="15.75">
       <c r="A174" s="24">
         <v>5059340802923</v>
       </c>
-      <c r="B174" s="36" t="s">
-        <v>612</v>
+      <c r="B174" s="25" t="s">
+        <v>227</v>
       </c>
       <c r="C174" s="25" t="s">
-        <v>577</v>
-      </c>
-      <c r="D174" s="36" t="s">
-        <v>459</v>
-      </c>
-      <c r="E174" s="36" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5" hidden="1">
+        <v>628</v>
+      </c>
+      <c r="D174" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="E174" s="25" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" ht="15.75">
       <c r="A175" s="24">
         <v>5059340802558</v>
       </c>
-      <c r="B175" s="36" t="s">
-        <v>613</v>
+      <c r="B175" s="25" t="s">
+        <v>229</v>
       </c>
       <c r="C175" s="25" t="s">
-        <v>577</v>
-      </c>
-      <c r="D175" s="36" t="s">
-        <v>459</v>
-      </c>
-      <c r="E175" s="36" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5" hidden="1">
+        <v>628</v>
+      </c>
+      <c r="D175" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="E175" s="25" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" ht="15.75">
       <c r="A176" s="24">
         <v>5059340802831</v>
       </c>
-      <c r="B176" s="36" t="s">
-        <v>614</v>
+      <c r="B176" s="25" t="s">
+        <v>228</v>
       </c>
       <c r="C176" s="25" t="s">
-        <v>577</v>
-      </c>
-      <c r="D176" s="36" t="s">
-        <v>459</v>
-      </c>
-      <c r="E176" s="36" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5">
+        <v>628</v>
+      </c>
+      <c r="D176" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="E176" s="25" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" ht="15.75">
       <c r="A177" s="24">
         <v>5059340969657</v>
       </c>
-      <c r="B177" s="36" t="s">
-        <v>615</v>
+      <c r="B177" s="25" t="s">
+        <v>632</v>
       </c>
       <c r="C177" s="25" t="s">
-        <v>577</v>
-      </c>
-      <c r="D177" s="36" t="s">
-        <v>475</v>
-      </c>
-      <c r="E177" s="36" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5">
+        <v>628</v>
+      </c>
+      <c r="D177" s="25" t="s">
+        <v>501</v>
+      </c>
+      <c r="E177" s="25" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" ht="15.75">
       <c r="A178" s="24">
         <v>5059340969633</v>
       </c>
-      <c r="B178" s="36" t="s">
-        <v>616</v>
+      <c r="B178" s="25" t="s">
+        <v>633</v>
       </c>
       <c r="C178" s="25" t="s">
-        <v>577</v>
-      </c>
-      <c r="D178" s="36" t="s">
-        <v>475</v>
-      </c>
-      <c r="E178" s="36" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5">
+        <v>628</v>
+      </c>
+      <c r="D178" s="25" t="s">
+        <v>501</v>
+      </c>
+      <c r="E178" s="25" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" ht="15.75">
       <c r="A179" s="24">
         <v>5059340969640</v>
       </c>
-      <c r="B179" s="36" t="s">
-        <v>617</v>
+      <c r="B179" s="25" t="s">
+        <v>634</v>
       </c>
       <c r="C179" s="25" t="s">
-        <v>577</v>
-      </c>
-      <c r="D179" s="36" t="s">
-        <v>475</v>
-      </c>
-      <c r="E179" s="36" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5">
+        <v>628</v>
+      </c>
+      <c r="D179" s="25" t="s">
+        <v>501</v>
+      </c>
+      <c r="E179" s="25" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" ht="15.75">
       <c r="A180" s="24">
         <v>5059340969664</v>
       </c>
-      <c r="B180" s="36" t="s">
-        <v>618</v>
+      <c r="B180" s="25" t="s">
+        <v>635</v>
       </c>
       <c r="C180" s="25" t="s">
-        <v>577</v>
-      </c>
-      <c r="D180" s="36" t="s">
-        <v>475</v>
-      </c>
-      <c r="E180" s="36" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5">
+        <v>628</v>
+      </c>
+      <c r="D180" s="25" t="s">
+        <v>501</v>
+      </c>
+      <c r="E180" s="25" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" ht="15.75">
       <c r="A181" s="24">
         <v>5059340969626</v>
       </c>
-      <c r="B181" s="36" t="s">
-        <v>619</v>
+      <c r="B181" s="25" t="s">
+        <v>636</v>
       </c>
       <c r="C181" s="25" t="s">
-        <v>577</v>
-      </c>
-      <c r="D181" s="36" t="s">
-        <v>475</v>
-      </c>
-      <c r="E181" s="36" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5">
+        <v>628</v>
+      </c>
+      <c r="D181" s="25" t="s">
+        <v>501</v>
+      </c>
+      <c r="E181" s="25" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" ht="15.75">
       <c r="A182" s="24">
         <v>5059340802473</v>
       </c>
-      <c r="B182" s="36" t="s">
-        <v>620</v>
+      <c r="B182" s="25" t="s">
+        <v>226</v>
       </c>
       <c r="C182" s="25" t="s">
-        <v>577</v>
-      </c>
-      <c r="D182" s="36" t="s">
-        <v>475</v>
-      </c>
-      <c r="E182" s="36" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5">
+        <v>628</v>
+      </c>
+      <c r="D182" s="25" t="s">
+        <v>501</v>
+      </c>
+      <c r="E182" s="25" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" ht="15.75">
       <c r="A183" s="24">
         <v>5059340802725</v>
       </c>
-      <c r="B183" s="36" t="s">
-        <v>621</v>
+      <c r="B183" s="25" t="s">
+        <v>225</v>
       </c>
       <c r="C183" s="25" t="s">
-        <v>577</v>
-      </c>
-      <c r="D183" s="36" t="s">
-        <v>475</v>
-      </c>
-      <c r="E183" s="36" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5">
+        <v>628</v>
+      </c>
+      <c r="D183" s="25" t="s">
+        <v>501</v>
+      </c>
+      <c r="E183" s="25" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" ht="15.75">
       <c r="A184" s="24">
         <v>5059340803074</v>
       </c>
-      <c r="B184" s="36" t="s">
-        <v>622</v>
+      <c r="B184" s="25" t="s">
+        <v>224</v>
       </c>
       <c r="C184" s="25" t="s">
-        <v>577</v>
-      </c>
-      <c r="D184" s="36" t="s">
-        <v>475</v>
-      </c>
-      <c r="E184" s="36" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5" hidden="1">
+        <v>628</v>
+      </c>
+      <c r="D184" s="25" t="s">
+        <v>501</v>
+      </c>
+      <c r="E184" s="25" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" ht="15.75">
       <c r="A185" s="24">
         <v>3663602997436</v>
       </c>
-      <c r="B185" s="36" t="s">
-        <v>623</v>
+      <c r="B185" s="25" t="s">
+        <v>637</v>
       </c>
       <c r="C185" s="25" t="s">
-        <v>624</v>
-      </c>
-      <c r="D185" s="36" t="s">
-        <v>459</v>
-      </c>
-      <c r="E185" s="36" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5" hidden="1">
+        <v>638</v>
+      </c>
+      <c r="D185" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="E185" s="25" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" ht="15.75">
       <c r="A186" s="24">
         <v>5063022047847</v>
       </c>
-      <c r="B186" s="36" t="s">
+      <c r="B186" s="25" t="s">
         <v>206</v>
       </c>
       <c r="C186" s="25" t="s">
-        <v>624</v>
-      </c>
-      <c r="D186" s="36" t="s">
-        <v>459</v>
-      </c>
-      <c r="E186" s="36" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5" hidden="1">
+        <v>638</v>
+      </c>
+      <c r="D186" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="E186" s="25" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" ht="15.75">
       <c r="A187" s="24">
         <v>5063022085658</v>
       </c>
-      <c r="B187" s="36" t="s">
-        <v>625</v>
+      <c r="B187" s="25" t="s">
+        <v>639</v>
       </c>
       <c r="C187" s="25" t="s">
-        <v>624</v>
-      </c>
-      <c r="D187" s="36" t="s">
-        <v>459</v>
-      </c>
-      <c r="E187" s="36" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5" hidden="1">
+        <v>638</v>
+      </c>
+      <c r="D187" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="E187" s="25" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" ht="15.75">
       <c r="A188" s="24">
         <v>3663602997962</v>
       </c>
-      <c r="B188" s="36" t="s">
-        <v>626</v>
+      <c r="B188" s="25" t="s">
+        <v>640</v>
       </c>
       <c r="C188" s="25" t="s">
-        <v>624</v>
-      </c>
-      <c r="D188" s="36" t="s">
-        <v>459</v>
-      </c>
-      <c r="E188" s="36" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5" hidden="1">
+        <v>638</v>
+      </c>
+      <c r="D188" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="E188" s="25" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" ht="15.75">
       <c r="A189" s="24">
         <v>5063022069450</v>
       </c>
-      <c r="B189" s="36" t="s">
+      <c r="B189" s="25" t="s">
         <v>191</v>
       </c>
       <c r="C189" s="25" t="s">
-        <v>624</v>
-      </c>
-      <c r="D189" s="36" t="s">
-        <v>459</v>
-      </c>
-      <c r="E189" s="36" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5" hidden="1">
+        <v>638</v>
+      </c>
+      <c r="D189" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="E189" s="25" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" ht="15.75">
       <c r="A190" s="24">
         <v>5063022606525</v>
       </c>
-      <c r="B190" s="36" t="s">
-        <v>627</v>
+      <c r="B190" s="25" t="s">
+        <v>641</v>
       </c>
       <c r="C190" s="25" t="s">
-        <v>624</v>
-      </c>
-      <c r="D190" s="36" t="s">
-        <v>459</v>
-      </c>
-      <c r="E190" s="36" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5" hidden="1">
+        <v>638</v>
+      </c>
+      <c r="D190" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="E190" s="25" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" ht="15.75">
       <c r="A191" s="24">
         <v>5063022047755</v>
       </c>
-      <c r="B191" s="36" t="s">
+      <c r="B191" s="25" t="s">
         <v>190</v>
       </c>
       <c r="C191" s="25" t="s">
-        <v>624</v>
-      </c>
-      <c r="D191" s="36" t="s">
-        <v>459</v>
-      </c>
-      <c r="E191" s="36" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5" hidden="1">
+        <v>638</v>
+      </c>
+      <c r="D191" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="E191" s="25" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" ht="15.75">
       <c r="A192" s="24">
         <v>5059340194042</v>
       </c>
-      <c r="B192" s="36" t="s">
-        <v>628</v>
+      <c r="B192" s="25" t="s">
+        <v>642</v>
       </c>
       <c r="C192" s="25" t="s">
-        <v>624</v>
-      </c>
-      <c r="D192" s="36" t="s">
-        <v>459</v>
-      </c>
-      <c r="E192" s="36" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="193" spans="1:5" hidden="1">
+        <v>638</v>
+      </c>
+      <c r="D192" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="E192" s="25" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" ht="15.75">
       <c r="A193" s="24">
         <v>5063022606068</v>
       </c>
-      <c r="B193" s="36" t="s">
-        <v>629</v>
+      <c r="B193" s="25" t="s">
+        <v>643</v>
       </c>
       <c r="C193" s="25" t="s">
-        <v>624</v>
-      </c>
-      <c r="D193" s="36" t="s">
-        <v>459</v>
-      </c>
-      <c r="E193" s="36" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="194" spans="1:5" hidden="1">
+        <v>638</v>
+      </c>
+      <c r="D193" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="E193" s="25" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" ht="15.75">
       <c r="A194" s="24">
         <v>5059340485362</v>
       </c>
-      <c r="B194" s="36" t="s">
+      <c r="B194" s="25" t="s">
         <v>184</v>
       </c>
       <c r="C194" s="25" t="s">
-        <v>624</v>
-      </c>
-      <c r="D194" s="36" t="s">
-        <v>459</v>
-      </c>
-      <c r="E194" s="36" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="195" spans="1:5" hidden="1">
+        <v>638</v>
+      </c>
+      <c r="D194" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="E194" s="25" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" ht="15.75">
       <c r="A195" s="24">
         <v>5063022085603</v>
       </c>
-      <c r="B195" s="36" t="s">
+      <c r="B195" s="25" t="s">
         <v>193</v>
       </c>
       <c r="C195" s="25" t="s">
-        <v>624</v>
-      </c>
-      <c r="D195" s="36" t="s">
-        <v>459</v>
-      </c>
-      <c r="E195" s="36" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="196" spans="1:5" hidden="1">
+        <v>638</v>
+      </c>
+      <c r="D195" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="E195" s="25" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" ht="15.75">
       <c r="A196" s="24">
         <v>5059340194080</v>
       </c>
-      <c r="B196" s="36" t="s">
+      <c r="B196" s="25" t="s">
         <v>199</v>
       </c>
       <c r="C196" s="25" t="s">
-        <v>624</v>
-      </c>
-      <c r="D196" s="36" t="s">
-        <v>459</v>
-      </c>
-      <c r="E196" s="36" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="197" spans="1:5" hidden="1">
+        <v>638</v>
+      </c>
+      <c r="D196" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="E196" s="25" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" ht="15.75">
       <c r="A197" s="24">
         <v>5059340216034</v>
       </c>
-      <c r="B197" s="36" t="s">
+      <c r="B197" s="25" t="s">
         <v>194</v>
       </c>
       <c r="C197" s="25" t="s">
-        <v>624</v>
-      </c>
-      <c r="D197" s="36" t="s">
-        <v>459</v>
-      </c>
-      <c r="E197" s="36" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="198" spans="1:5" hidden="1">
+        <v>638</v>
+      </c>
+      <c r="D197" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="E197" s="25" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" ht="15.75">
       <c r="A198" s="24">
         <v>5059340194097</v>
       </c>
-      <c r="B198" s="36" t="s">
+      <c r="B198" s="25" t="s">
         <v>185</v>
       </c>
       <c r="C198" s="25" t="s">
-        <v>624</v>
-      </c>
-      <c r="D198" s="36" t="s">
-        <v>459</v>
-      </c>
-      <c r="E198" s="36" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="199" spans="1:5">
+        <v>638</v>
+      </c>
+      <c r="D198" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="E198" s="25" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" ht="15.75">
       <c r="A199" s="24">
         <v>5063022047830</v>
       </c>
-      <c r="B199" s="36" t="s">
+      <c r="B199" s="25" t="s">
         <v>204</v>
       </c>
       <c r="C199" s="25" t="s">
-        <v>624</v>
-      </c>
-      <c r="D199" s="36" t="s">
-        <v>475</v>
-      </c>
-      <c r="E199" s="36" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="200" spans="1:5">
+        <v>638</v>
+      </c>
+      <c r="D199" s="25" t="s">
+        <v>501</v>
+      </c>
+      <c r="E199" s="25" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" ht="15.75">
       <c r="A200" s="24">
         <v>5063022085641</v>
       </c>
-      <c r="B200" s="36" t="s">
-        <v>630</v>
+      <c r="B200" s="25" t="s">
+        <v>644</v>
       </c>
       <c r="C200" s="25" t="s">
-        <v>624</v>
-      </c>
-      <c r="D200" s="36" t="s">
-        <v>475</v>
-      </c>
-      <c r="E200" s="36" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="201" spans="1:5">
+        <v>638</v>
+      </c>
+      <c r="D200" s="25" t="s">
+        <v>501</v>
+      </c>
+      <c r="E200" s="25" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" ht="15.75">
       <c r="A201" s="24">
         <v>5063022034496</v>
       </c>
-      <c r="B201" s="36" t="s">
-        <v>631</v>
+      <c r="B201" s="25" t="s">
+        <v>645</v>
       </c>
       <c r="C201" s="25" t="s">
-        <v>624</v>
-      </c>
-      <c r="D201" s="36" t="s">
-        <v>475</v>
-      </c>
-      <c r="E201" s="36" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="202" spans="1:5">
+        <v>638</v>
+      </c>
+      <c r="D201" s="25" t="s">
+        <v>501</v>
+      </c>
+      <c r="E201" s="25" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" ht="15.75">
       <c r="A202" s="24">
         <v>5059340391441</v>
       </c>
-      <c r="B202" s="36" t="s">
+      <c r="B202" s="25" t="s">
         <v>207</v>
       </c>
       <c r="C202" s="25" t="s">
-        <v>624</v>
-      </c>
-      <c r="D202" s="36" t="s">
-        <v>475</v>
-      </c>
-      <c r="E202" s="36" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="203" spans="1:5">
+        <v>638</v>
+      </c>
+      <c r="D202" s="25" t="s">
+        <v>501</v>
+      </c>
+      <c r="E202" s="25" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" ht="15.75">
       <c r="A203" s="24">
         <v>5063022606020</v>
       </c>
-      <c r="B203" s="36" t="s">
-        <v>632</v>
+      <c r="B203" s="25" t="s">
+        <v>646</v>
       </c>
       <c r="C203" s="25" t="s">
-        <v>624</v>
-      </c>
-      <c r="D203" s="36" t="s">
-        <v>475</v>
-      </c>
-      <c r="E203" s="36" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="204" spans="1:5">
+        <v>638</v>
+      </c>
+      <c r="D203" s="25" t="s">
+        <v>501</v>
+      </c>
+      <c r="E203" s="25" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" ht="15.75">
       <c r="A204" s="24">
         <v>5063022606037</v>
       </c>
-      <c r="B204" s="36" t="s">
-        <v>633</v>
+      <c r="B204" s="25" t="s">
+        <v>647</v>
       </c>
       <c r="C204" s="25" t="s">
-        <v>624</v>
-      </c>
-      <c r="D204" s="36" t="s">
-        <v>475</v>
-      </c>
-      <c r="E204" s="36" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="205" spans="1:5">
+        <v>638</v>
+      </c>
+      <c r="D204" s="25" t="s">
+        <v>501</v>
+      </c>
+      <c r="E204" s="25" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" ht="15.75">
       <c r="A205" s="24">
         <v>5063022606013</v>
       </c>
-      <c r="B205" s="36" t="s">
-        <v>634</v>
+      <c r="B205" s="25" t="s">
+        <v>648</v>
       </c>
       <c r="C205" s="25" t="s">
-        <v>624</v>
-      </c>
-      <c r="D205" s="36" t="s">
-        <v>475</v>
-      </c>
-      <c r="E205" s="36" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="206" spans="1:5">
+        <v>638</v>
+      </c>
+      <c r="D205" s="25" t="s">
+        <v>501</v>
+      </c>
+      <c r="E205" s="25" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" ht="15.75">
       <c r="A206" s="24">
         <v>5063022047816</v>
       </c>
-      <c r="B206" s="36" t="s">
+      <c r="B206" s="25" t="s">
         <v>188</v>
       </c>
       <c r="C206" s="25" t="s">
-        <v>624</v>
-      </c>
-      <c r="D206" s="36" t="s">
-        <v>475</v>
-      </c>
-      <c r="E206" s="36" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="207" spans="1:5">
+        <v>638</v>
+      </c>
+      <c r="D206" s="25" t="s">
+        <v>501</v>
+      </c>
+      <c r="E206" s="25" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" ht="15.75">
       <c r="A207" s="24">
         <v>5059340484303</v>
       </c>
-      <c r="B207" s="36" t="s">
+      <c r="B207" s="25" t="s">
         <v>187</v>
       </c>
       <c r="C207" s="25" t="s">
-        <v>624</v>
-      </c>
-      <c r="D207" s="36" t="s">
-        <v>475</v>
-      </c>
-      <c r="E207" s="36" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="208" spans="1:5">
+        <v>638</v>
+      </c>
+      <c r="D207" s="25" t="s">
+        <v>501</v>
+      </c>
+      <c r="E207" s="25" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" ht="15.75">
       <c r="A208" s="24">
         <v>5063022047823</v>
       </c>
-      <c r="B208" s="36" t="s">
+      <c r="B208" s="25" t="s">
         <v>201</v>
       </c>
       <c r="C208" s="25" t="s">
-        <v>624</v>
-      </c>
-      <c r="D208" s="36" t="s">
-        <v>475</v>
-      </c>
-      <c r="E208" s="36" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="209" spans="1:5">
+        <v>638</v>
+      </c>
+      <c r="D208" s="25" t="s">
+        <v>501</v>
+      </c>
+      <c r="E208" s="25" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" ht="15.75">
       <c r="A209" s="24">
         <v>5059340194035</v>
       </c>
-      <c r="B209" s="36" t="s">
-        <v>635</v>
+      <c r="B209" s="25" t="s">
+        <v>649</v>
       </c>
       <c r="C209" s="25" t="s">
-        <v>624</v>
-      </c>
-      <c r="D209" s="36" t="s">
-        <v>475</v>
-      </c>
-      <c r="E209" s="36" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="210" spans="1:5">
+        <v>638</v>
+      </c>
+      <c r="D209" s="25" t="s">
+        <v>501</v>
+      </c>
+      <c r="E209" s="25" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" ht="15.75">
       <c r="A210" s="24">
         <v>5059340194073</v>
       </c>
-      <c r="B210" s="36" t="s">
+      <c r="B210" s="25" t="s">
         <v>183</v>
       </c>
       <c r="C210" s="25" t="s">
-        <v>624</v>
-      </c>
-      <c r="D210" s="36" t="s">
-        <v>475</v>
-      </c>
-      <c r="E210" s="36" t="s">
-        <v>472</v>
+        <v>638</v>
+      </c>
+      <c r="D210" s="25" t="s">
+        <v>501</v>
+      </c>
+      <c r="E210" s="25" t="s">
+        <v>498</v>
       </c>
     </row>
   </sheetData>

--- a/ceramica_proyecto.xlsx
+++ b/ceramica_proyecto.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Camero\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF455C7E-FD3B-469C-BCFA-6261F67DC0D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3DF71F0E-0D2D-4975-963A-DAA5B3AB22D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{6A0D054A-EA90-43D3-9946-5E896568E0A7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="3" xr2:uid="{6A0D054A-EA90-43D3-9946-5E896568E0A7}"/>
   </bookViews>
   <sheets>
     <sheet name="EXISTENCIA TOTAL" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1472" uniqueCount="650">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1488" uniqueCount="657">
   <si>
     <t>EAN</t>
   </si>
@@ -1522,6 +1522,30 @@
     <t>28-01-603</t>
   </si>
   <si>
+    <t>28-01-103</t>
+  </si>
+  <si>
+    <t>28-02-203</t>
+  </si>
+  <si>
+    <t>28-02-101</t>
+  </si>
+  <si>
+    <t>28-02-103</t>
+  </si>
+  <si>
+    <t>28-02-102</t>
+  </si>
+  <si>
+    <t>28-02-201</t>
+  </si>
+  <si>
+    <t>28-01-101</t>
+  </si>
+  <si>
+    <t>28-01-102</t>
+  </si>
+  <si>
     <t>AZ. OCTAVIO 30X90 MADERA NATURAL</t>
   </si>
   <si>
@@ -3605,6 +3629,12 @@
     <t>UCLES NATURAL 22X90</t>
   </si>
   <si>
+    <t>MODULO 2</t>
+  </si>
+  <si>
+    <t>FILA 4</t>
+  </si>
+  <si>
     <t>MEDINA 45X45</t>
   </si>
   <si>
@@ -3626,9 +3656,6 @@
     <t>CLIZI GRIS 24X88</t>
   </si>
   <si>
-    <t>FILA 4</t>
-  </si>
-  <si>
     <t>TORAN HAYA</t>
   </si>
   <si>
@@ -3644,13 +3671,7 @@
     <t>AMAGA BEIGE 24X88</t>
   </si>
   <si>
-    <t>MODULO 2</t>
-  </si>
-  <si>
     <t>COLTON HAYA MATE 23X120</t>
-  </si>
-  <si>
-    <t>FILA1</t>
   </si>
   <si>
     <t>CONCORDE HAYA MATE 30X60</t>
@@ -4286,7 +4307,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4364,6 +4385,7 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4863,8 +4885,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E092D5E8-DDBA-4DC5-B48F-DE814A493E02}" name="ALMACEN" displayName="ALMACEN" ref="A1:C141" totalsRowShown="0" dataDxfId="19" headerRowBorderDxfId="17" tableBorderDxfId="18">
-  <autoFilter ref="A1:C141" xr:uid="{E092D5E8-DDBA-4DC5-B48F-DE814A493E02}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E092D5E8-DDBA-4DC5-B48F-DE814A493E02}" name="ALMACEN" displayName="ALMACEN" ref="A1:C149" totalsRowShown="0" dataDxfId="19" headerRowBorderDxfId="17" tableBorderDxfId="18">
+  <autoFilter ref="A1:C149" xr:uid="{E092D5E8-DDBA-4DC5-B48F-DE814A493E02}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{3A65B69D-D98E-4AEB-961F-5593E79CA067}" name="EAN" dataDxfId="16"/>
     <tableColumn id="2" xr3:uid="{469CD1D5-7294-47E9-B0FB-BA7DD9CCC96D}" name="descrpcion_es" dataDxfId="15"/>
@@ -7806,15 +7828,15 @@
       </c>
       <c r="H67" s="15" t="str">
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="I67" s="16" t="str">
         <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>NO</v>
       </c>
-      <c r="J67" s="13" t="e">
-        <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
-        <v>#N/A</v>
+      <c r="J67" s="13" t="str">
+        <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
+        <v>28-01-103</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="15.75">
@@ -8305,11 +8327,11 @@
       </c>
       <c r="F80" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
-        <v>MODULO 1</v>
+        <v>MODULO 2</v>
       </c>
       <c r="G80" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
-        <v>FILA 1</v>
+        <v>FILA 4</v>
       </c>
       <c r="H80" s="15" t="str">
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
@@ -8391,15 +8413,15 @@
       </c>
       <c r="H82" s="15" t="str">
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="I82" s="16" t="str">
         <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>NO</v>
       </c>
-      <c r="J82" s="13" t="e">
-        <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
-        <v>#N/A</v>
+      <c r="J82" s="13" t="str">
+        <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
+        <v>28-02-203</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="15.75">
@@ -8539,11 +8561,11 @@
       </c>
       <c r="F86" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
-        <v>MODULO 2</v>
+        <v>MODULO 1</v>
       </c>
       <c r="G86" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
-        <v>FILA 4</v>
+        <v>FILA 1</v>
       </c>
       <c r="H86" s="15" t="str">
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
@@ -8937,15 +8959,15 @@
       </c>
       <c r="H96" s="15" t="str">
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="I96" s="16" t="str">
         <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>NO</v>
       </c>
-      <c r="J96" s="13" t="e">
-        <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
-        <v>#N/A</v>
+      <c r="J96" s="13" t="str">
+        <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
+        <v>28-02-101</v>
       </c>
     </row>
     <row r="97" spans="1:10" ht="15.75">
@@ -9366,15 +9388,15 @@
       </c>
       <c r="H107" s="15" t="str">
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="I107" s="16" t="str">
         <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>NO</v>
       </c>
-      <c r="J107" s="13" t="e">
-        <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
-        <v>#N/A</v>
+      <c r="J107" s="13" t="str">
+        <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
+        <v>28-01-102</v>
       </c>
     </row>
     <row r="108" spans="1:10" ht="15.75">
@@ -10458,15 +10480,15 @@
       </c>
       <c r="H135" s="15" t="str">
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="I135" s="16" t="str">
         <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>NO</v>
       </c>
-      <c r="J135" s="13" t="e">
-        <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
-        <v>#N/A</v>
+      <c r="J135" s="13" t="str">
+        <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
+        <v>28-02-103</v>
       </c>
     </row>
     <row r="136" spans="1:10" ht="15.75">
@@ -11082,15 +11104,15 @@
       </c>
       <c r="H151" s="15" t="str">
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="I151" s="16" t="str">
         <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>NO</v>
       </c>
-      <c r="J151" s="13" t="e">
-        <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
-        <v>#N/A</v>
+      <c r="J151" s="13" t="str">
+        <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
+        <v>28-02-102</v>
       </c>
     </row>
     <row r="152" spans="1:10" ht="15.75">
@@ -11696,7 +11718,7 @@
       </c>
       <c r="G167" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
-        <v>FILA1</v>
+        <v>FILA 1</v>
       </c>
       <c r="H167" s="15" t="str">
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
@@ -11922,15 +11944,15 @@
       </c>
       <c r="H173" s="15" t="str">
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="I173" s="16" t="str">
         <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>NO</v>
       </c>
-      <c r="J173" s="13" t="e">
-        <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
-        <v>#N/A</v>
+      <c r="J173" s="13" t="str">
+        <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
+        <v>28-02-201</v>
       </c>
     </row>
     <row r="174" spans="1:10" ht="15.75">
@@ -11959,15 +11981,15 @@
       </c>
       <c r="H174" s="15" t="str">
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="I174" s="16" t="str">
         <f>IF(COUNTIF(SELF[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
         <v>NO</v>
       </c>
-      <c r="J174" s="13" t="e">
-        <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
-        <v>#N/A</v>
+      <c r="J174" s="13" t="str">
+        <f>IF(EXISTENCIA[[#This Row],[en_self]]="SI", VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SELF[],3,FALSE), VLOOKUP(EXISTENCIA[[#This Row],[EAN]],ALMACEN[],3,FALSE))</f>
+        <v>28-01-101</v>
       </c>
     </row>
     <row r="175" spans="1:10" ht="15.75">
@@ -12414,7 +12436,7 @@
         <v>28-03-403</v>
       </c>
     </row>
-    <row r="187" spans="1:10" ht="30">
+    <row r="187" spans="1:10" ht="15.75">
       <c r="A187" s="39">
         <v>5063022606068</v>
       </c>
@@ -12451,7 +12473,7 @@
         <v>28-02-202</v>
       </c>
     </row>
-    <row r="188" spans="1:10" ht="30">
+    <row r="188" spans="1:10" ht="15.75">
       <c r="A188" s="39">
         <v>5063022606020</v>
       </c>
@@ -12488,7 +12510,7 @@
         <v>28-02-301</v>
       </c>
     </row>
-    <row r="189" spans="1:10" ht="30">
+    <row r="189" spans="1:10" ht="15.75">
       <c r="A189" s="39">
         <v>5063022606037</v>
       </c>
@@ -12525,7 +12547,7 @@
         <v>28-02-302</v>
       </c>
     </row>
-    <row r="190" spans="1:10" ht="30">
+    <row r="190" spans="1:10" ht="15.75">
       <c r="A190" s="39">
         <v>5063022606013</v>
       </c>
@@ -13228,7 +13250,7 @@
         <v>22-15-103</v>
       </c>
     </row>
-    <row r="209" spans="1:10" ht="16.5">
+    <row r="209" spans="1:10" ht="15.75">
       <c r="A209" s="39">
         <v>5059340802367</v>
       </c>
@@ -13265,7 +13287,7 @@
         <v>28-01-202</v>
       </c>
     </row>
-    <row r="210" spans="1:10" ht="16.5">
+    <row r="210" spans="1:10" ht="15.75">
       <c r="A210" s="39">
         <v>5059340221717</v>
       </c>
@@ -13302,7 +13324,7 @@
         <v>28-01-301</v>
       </c>
     </row>
-    <row r="211" spans="1:10" ht="16.5">
+    <row r="211" spans="1:10" ht="15.75">
       <c r="A211" s="39">
         <v>5059340357447</v>
       </c>
@@ -13339,7 +13361,7 @@
         <v>28-01-302</v>
       </c>
     </row>
-    <row r="212" spans="1:10" ht="16.5">
+    <row r="212" spans="1:10" ht="15.75">
       <c r="A212" s="39">
         <v>5059340802602</v>
       </c>
@@ -13376,7 +13398,7 @@
         <v>28-01-303</v>
       </c>
     </row>
-    <row r="213" spans="1:10" ht="16.5">
+    <row r="213" spans="1:10" ht="15.75">
       <c r="A213" s="39">
         <v>5059340802626</v>
       </c>
@@ -13413,7 +13435,7 @@
         <v>28-01-401</v>
       </c>
     </row>
-    <row r="214" spans="1:10" ht="16.5">
+    <row r="214" spans="1:10" ht="15.75">
       <c r="A214" s="39">
         <v>5059340802336</v>
       </c>
@@ -13450,7 +13472,7 @@
         <v>28-01-402</v>
       </c>
     </row>
-    <row r="215" spans="1:10" ht="16.5">
+    <row r="215" spans="1:10" ht="15.75">
       <c r="A215" s="39">
         <v>5059340802305</v>
       </c>
@@ -13487,7 +13509,7 @@
         <v>28-01-403</v>
       </c>
     </row>
-    <row r="216" spans="1:10" ht="16.5">
+    <row r="216" spans="1:10" ht="15.75">
       <c r="A216" s="39">
         <v>5059340803074</v>
       </c>
@@ -13524,7 +13546,7 @@
         <v>28-01-501</v>
       </c>
     </row>
-    <row r="217" spans="1:10" ht="16.5">
+    <row r="217" spans="1:10" ht="15.75">
       <c r="A217" s="39">
         <v>5059340802725</v>
       </c>
@@ -13561,7 +13583,7 @@
         <v>28-01-502</v>
       </c>
     </row>
-    <row r="218" spans="1:10" ht="16.5">
+    <row r="218" spans="1:10" ht="15.75">
       <c r="A218" s="39">
         <v>5059340802473</v>
       </c>
@@ -13598,7 +13620,7 @@
         <v>28-01-503</v>
       </c>
     </row>
-    <row r="219" spans="1:10" ht="16.5">
+    <row r="219" spans="1:10" ht="15.75">
       <c r="A219" s="39">
         <v>5059340802923</v>
       </c>
@@ -13635,7 +13657,7 @@
         <v>28-01-601</v>
       </c>
     </row>
-    <row r="220" spans="1:10" ht="16.5">
+    <row r="220" spans="1:10" ht="15.75">
       <c r="A220" s="39">
         <v>5059340802831</v>
       </c>
@@ -13672,7 +13694,7 @@
         <v>28-01-602</v>
       </c>
     </row>
-    <row r="221" spans="1:10" ht="16.5">
+    <row r="221" spans="1:10" ht="15.75">
       <c r="A221" s="39">
         <v>5059340802558</v>
       </c>
@@ -13720,7 +13742,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DD18BE2-0DBC-4BB4-8FBE-BFB232B0B51D}">
-  <dimension ref="A1:C141"/>
+  <dimension ref="A1:C149"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
@@ -15276,6 +15298,94 @@
       </c>
       <c r="C141" s="31" t="s">
         <v>390</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3">
+      <c r="A142" s="28">
+        <v>5059340781921</v>
+      </c>
+      <c r="B142" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="C142" s="43" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3">
+      <c r="A143" s="28">
+        <v>3663602679318</v>
+      </c>
+      <c r="B143" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="C143" s="43" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3">
+      <c r="A144" s="28">
+        <v>8435609333891</v>
+      </c>
+      <c r="B144" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="C144" s="43" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3">
+      <c r="A145" s="28">
+        <v>5059340719597</v>
+      </c>
+      <c r="B145" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="C145" s="43" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3">
+      <c r="A146" s="28">
+        <v>8435433538134</v>
+      </c>
+      <c r="B146" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="C146" s="43" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3">
+      <c r="A147" s="28">
+        <v>5059340815282</v>
+      </c>
+      <c r="B147" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="C147" s="43" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3">
+      <c r="A148" s="28">
+        <v>5059340854212</v>
+      </c>
+      <c r="B148" s="29" t="s">
+        <v>182</v>
+      </c>
+      <c r="C148" s="43" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3">
+      <c r="A149" s="28">
+        <v>5059340269610</v>
+      </c>
+      <c r="B149" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="C149" s="43" t="s">
+        <v>398</v>
       </c>
     </row>
   </sheetData>
@@ -15315,13 +15425,13 @@
         <v>5059340719535</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="J2" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -15329,10 +15439,10 @@
         <v>5059340719658</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -15343,7 +15453,7 @@
         <v>64</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -15354,7 +15464,7 @@
         <v>46</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -15362,10 +15472,10 @@
         <v>5036581065768</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -15376,7 +15486,7 @@
         <v>72</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -15384,10 +15494,10 @@
         <v>8435414126275</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -15395,10 +15505,10 @@
         <v>5036581064877</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -15409,7 +15519,7 @@
         <v>28</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -15420,7 +15530,7 @@
         <v>20</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -15428,10 +15538,10 @@
         <v>5036581064310</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -15442,7 +15552,7 @@
         <v>21</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -15450,10 +15560,10 @@
         <v>3663602848349</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -15461,10 +15571,10 @@
         <v>5036581064679</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -15472,10 +15582,10 @@
         <v>5059340433233</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -15483,10 +15593,10 @@
         <v>8435414126282</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -15494,10 +15604,10 @@
         <v>3663602679332</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -15505,10 +15615,10 @@
         <v>8435414127845</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -15516,10 +15626,10 @@
         <v>8429178156050</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -15527,10 +15637,10 @@
         <v>8429178398283</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -15538,10 +15648,10 @@
         <v>8435609333952</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -15549,10 +15659,10 @@
         <v>8429178840003</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -15560,10 +15670,10 @@
         <v>8432712278026</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -15571,10 +15681,10 @@
         <v>5059340433240</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -15582,10 +15692,10 @@
         <v>5059340460383</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="C26" s="27" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -15593,10 +15703,10 @@
         <v>5059340720968</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -15604,10 +15714,10 @@
         <v>8435609330777</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="C28" s="27" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -15615,10 +15725,10 @@
         <v>8429991953478</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -15626,10 +15736,10 @@
         <v>5059340720951</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="C30" s="27" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -15637,10 +15747,10 @@
         <v>5063022645289</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -15648,10 +15758,10 @@
         <v>8429991953577</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="C32" s="27" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -15659,10 +15769,10 @@
         <v>5059340870663</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="C33" s="27" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -15670,10 +15780,10 @@
         <v>3663602678366</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="C34" s="27" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -15681,10 +15791,10 @@
         <v>5059340719610</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="C35" s="27" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -15692,10 +15802,10 @@
         <v>5059340720982</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="C36" s="27" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -15703,10 +15813,10 @@
         <v>5059340720975</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="C37" s="27" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -15714,10 +15824,10 @@
         <v>8435414120211</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="C38" s="27" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -15725,10 +15835,10 @@
         <v>8435414118669</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="C39" s="27" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -15736,10 +15846,10 @@
         <v>5036581058319</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="C40" s="27" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -15747,10 +15857,10 @@
         <v>5036581058326</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="C41" s="27" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -15761,7 +15871,7 @@
         <v>105</v>
       </c>
       <c r="C42" s="27" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -15772,7 +15882,7 @@
         <v>171</v>
       </c>
       <c r="C43" s="27" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -15783,7 +15893,7 @@
         <v>202</v>
       </c>
       <c r="C44" s="27" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -15794,7 +15904,7 @@
         <v>203</v>
       </c>
       <c r="C45" s="27" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -15805,7 +15915,7 @@
         <v>204</v>
       </c>
       <c r="C46" s="27" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -15816,7 +15926,7 @@
         <v>205</v>
       </c>
       <c r="C47" s="27" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -15827,7 +15937,7 @@
         <v>206</v>
       </c>
       <c r="C48" s="27" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -15838,7 +15948,7 @@
         <v>207</v>
       </c>
       <c r="C49" s="27" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -15849,7 +15959,7 @@
         <v>208</v>
       </c>
       <c r="C50" s="27" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -15860,7 +15970,7 @@
         <v>209</v>
       </c>
       <c r="C51" s="27" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -15871,7 +15981,7 @@
         <v>210</v>
       </c>
       <c r="C52" s="27" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -15882,7 +15992,7 @@
         <v>211</v>
       </c>
       <c r="C53" s="27" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -15893,7 +16003,7 @@
         <v>212</v>
       </c>
       <c r="C54" s="27" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -15904,7 +16014,7 @@
         <v>213</v>
       </c>
       <c r="C55" s="27" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -15915,7 +16025,7 @@
         <v>214</v>
       </c>
       <c r="C56" s="27" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -15926,7 +16036,7 @@
         <v>215</v>
       </c>
       <c r="C57" s="27" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -15937,7 +16047,7 @@
         <v>216</v>
       </c>
       <c r="C58" s="27" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
     </row>
   </sheetData>
@@ -15981,16 +16091,16 @@
         <v>8432712278026</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -15998,16 +16108,16 @@
         <v>8435414127845</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="D3" s="25" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -16015,16 +16125,16 @@
         <v>5059340433240</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="D4" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E4" s="25" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -16032,16 +16142,16 @@
         <v>8429178398283</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E5" s="25" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -16049,16 +16159,16 @@
         <v>5059340433233</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>491</v>
+        <v>501</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -16066,16 +16176,16 @@
         <v>8429991784881</v>
       </c>
       <c r="B7" s="25" t="s">
+        <v>503</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>492</v>
+      </c>
+      <c r="D7" s="25" t="s">
         <v>493</v>
       </c>
-      <c r="C7" s="25" t="s">
-        <v>484</v>
-      </c>
-      <c r="D7" s="25" t="s">
-        <v>485</v>
-      </c>
       <c r="E7" s="25" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -16083,16 +16193,16 @@
         <v>5063022022561</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -16100,16 +16210,16 @@
         <v>8435609333952</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E9" s="25" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -16117,16 +16227,16 @@
         <v>8429991784904</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -16134,16 +16244,16 @@
         <v>8429991784898</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -16151,16 +16261,16 @@
         <v>8429178840003</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -16168,16 +16278,16 @@
         <v>8435609373682</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -16185,16 +16295,16 @@
         <v>8435609378458</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="D14" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -16202,16 +16312,16 @@
         <v>8429178156050</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="D15" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -16219,16 +16329,16 @@
         <v>8435414126282</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -16236,16 +16346,16 @@
         <v>8435609333921</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -16253,16 +16363,16 @@
         <v>5059340433424</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="C18" s="25" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E18" s="25" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -16270,16 +16380,16 @@
         <v>3663602679332</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="C19" s="25" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="D19" s="25" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="E19" s="25" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -16287,16 +16397,16 @@
         <v>8435414109278</v>
       </c>
       <c r="B20" s="25" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="D20" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -16304,16 +16414,16 @@
         <v>3663602675846</v>
       </c>
       <c r="B21" s="25" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="D21" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E21" s="25" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -16321,16 +16431,16 @@
         <v>5059340721002</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="D22" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E22" s="25" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -16338,16 +16448,16 @@
         <v>8435609330777</v>
       </c>
       <c r="B23" s="25" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="C23" s="25" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="D23" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E23" s="25" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -16355,16 +16465,16 @@
         <v>8429991798857</v>
       </c>
       <c r="B24" s="25" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="D24" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E24" s="25" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -16372,16 +16482,16 @@
         <v>5059340720968</v>
       </c>
       <c r="B25" s="25" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="D25" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E25" s="25" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -16389,16 +16499,16 @@
         <v>5063022605061</v>
       </c>
       <c r="B26" s="25" t="s">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="D26" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E26" s="25" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -16406,16 +16516,16 @@
         <v>5059340812311</v>
       </c>
       <c r="B27" s="25" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="D27" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E27" s="25" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -16423,16 +16533,16 @@
         <v>8429991953478</v>
       </c>
       <c r="B28" s="25" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="C28" s="25" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="D28" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E28" s="25" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -16440,16 +16550,16 @@
         <v>5059340269610</v>
       </c>
       <c r="B29" s="25" t="s">
+        <v>527</v>
+      </c>
+      <c r="C29" s="25" t="s">
         <v>520</v>
       </c>
-      <c r="C29" s="25" t="s">
-        <v>513</v>
-      </c>
       <c r="D29" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E29" s="25" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -16457,16 +16567,16 @@
         <v>5059340874937</v>
       </c>
       <c r="B30" s="25" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="C30" s="25" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="D30" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E30" s="25" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -16477,13 +16587,13 @@
         <v>181</v>
       </c>
       <c r="C31" s="25" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="D31" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E31" s="25" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -16491,16 +16601,16 @@
         <v>5059340854212</v>
       </c>
       <c r="B32" s="25" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="C32" s="25" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="D32" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E32" s="25" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -16508,16 +16618,16 @@
         <v>8429991793449</v>
       </c>
       <c r="B33" s="25" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="D33" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E33" s="25" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -16525,16 +16635,16 @@
         <v>5059340870663</v>
       </c>
       <c r="B34" s="25" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="C34" s="25" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="D34" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E34" s="25" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -16542,16 +16652,16 @@
         <v>5059340854267</v>
       </c>
       <c r="B35" s="25" t="s">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="D35" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E35" s="25" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -16559,16 +16669,16 @@
         <v>3663602678298</v>
       </c>
       <c r="B36" s="25" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="C36" s="25" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="D36" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E36" s="25" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -16576,16 +16686,16 @@
         <v>5059340459912</v>
       </c>
       <c r="B37" s="25" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="C37" s="25" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="D37" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E37" s="25" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -16593,16 +16703,16 @@
         <v>5059340854236</v>
       </c>
       <c r="B38" s="25" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="C38" s="25" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="D38" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E38" s="25" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -16610,16 +16720,16 @@
         <v>3663602678366</v>
       </c>
       <c r="B39" s="25" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="C39" s="25" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="D39" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E39" s="25" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -16627,16 +16737,16 @@
         <v>3663602678465</v>
       </c>
       <c r="B40" s="25" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="C40" s="25" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="D40" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E40" s="25" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -16644,16 +16754,16 @@
         <v>5059340720951</v>
       </c>
       <c r="B41" s="25" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="C41" s="25" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="D41" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E41" s="25" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -16661,16 +16771,16 @@
         <v>5063022645289</v>
       </c>
       <c r="B42" s="25" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="C42" s="25" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="D42" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E42" s="25" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -16678,16 +16788,16 @@
         <v>8429991798864</v>
       </c>
       <c r="B43" s="25" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="C43" s="25" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="D43" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E43" s="25" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -16695,16 +16805,16 @@
         <v>5059340721026</v>
       </c>
       <c r="B44" s="25" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="C44" s="25" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="D44" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E44" s="25" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -16712,16 +16822,16 @@
         <v>3663602677413</v>
       </c>
       <c r="B45" s="25" t="s">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="C45" s="25" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="D45" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E45" s="25" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -16729,16 +16839,16 @@
         <v>8435609317396</v>
       </c>
       <c r="B46" s="25" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="C46" s="25" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="D46" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E46" s="25" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -16746,16 +16856,16 @@
         <v>8429991953577</v>
       </c>
       <c r="B47" s="25" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="C47" s="25" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="D47" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E47" s="25" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -16763,16 +16873,16 @@
         <v>8429991798888</v>
       </c>
       <c r="B48" s="25" t="s">
+        <v>546</v>
+      </c>
+      <c r="C48" s="25" t="s">
         <v>539</v>
       </c>
-      <c r="C48" s="25" t="s">
-        <v>532</v>
-      </c>
       <c r="D48" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E48" s="25" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -16780,16 +16890,16 @@
         <v>8429991798901</v>
       </c>
       <c r="B49" s="25" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="C49" s="25" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="D49" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E49" s="25" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -16797,16 +16907,16 @@
         <v>5059340460383</v>
       </c>
       <c r="B50" s="25" t="s">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="C50" s="25" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="D50" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E50" s="25" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -16814,16 +16924,16 @@
         <v>5059340721040</v>
       </c>
       <c r="B51" s="25" t="s">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="C51" s="25" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="D51" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E51" s="25" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -16831,16 +16941,16 @@
         <v>5059340720999</v>
       </c>
       <c r="B52" s="25" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="C52" s="25" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="D52" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E52" s="25" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -16848,16 +16958,16 @@
         <v>8432712270556</v>
       </c>
       <c r="B53" s="25" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="C53" s="25" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="D53" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E53" s="25" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -16865,16 +16975,16 @@
         <v>8435414101517</v>
       </c>
       <c r="B54" s="25" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="C54" s="25" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="D54" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E54" s="25" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -16882,16 +16992,16 @@
         <v>8429991787479</v>
       </c>
       <c r="B55" s="25" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="C55" s="25" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="D55" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E55" s="25" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -16899,16 +17009,16 @@
         <v>5059340720982</v>
       </c>
       <c r="B56" s="27" t="s">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="C56" s="25" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="D56" s="27" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E56" s="27" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -16916,16 +17026,16 @@
         <v>5036581058319</v>
       </c>
       <c r="B57" s="27" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="C57" s="25" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="D57" s="27" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E57" s="27" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -16933,16 +17043,16 @@
         <v>5036581058326</v>
       </c>
       <c r="B58" s="27" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="C58" s="25" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="D58" s="27" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E58" s="27" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -16950,16 +17060,16 @@
         <v>8429991787486</v>
       </c>
       <c r="B59" s="27" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="C59" s="25" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="D59" s="27" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E59" s="27" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -16967,16 +17077,16 @@
         <v>8435433538134</v>
       </c>
       <c r="B60" s="27" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="C60" s="25" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="D60" s="27" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E60" s="27" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -16984,16 +17094,16 @@
         <v>8435414118669</v>
       </c>
       <c r="B61" s="27" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="C61" s="25" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="D61" s="27" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E61" s="27" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -17001,16 +17111,16 @@
         <v>8435414118645</v>
       </c>
       <c r="B62" s="27" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="C62" s="25" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="D62" s="27" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E62" s="27" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -17021,13 +17131,13 @@
         <v>151</v>
       </c>
       <c r="C63" s="25" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="D63" s="27" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E63" s="27" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -17035,16 +17145,16 @@
         <v>8435609351932</v>
       </c>
       <c r="B64" s="27" t="s">
+        <v>562</v>
+      </c>
+      <c r="C64" s="25" t="s">
         <v>555</v>
       </c>
-      <c r="C64" s="25" t="s">
-        <v>548</v>
-      </c>
       <c r="D64" s="27" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E64" s="27" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -17055,13 +17165,13 @@
         <v>296</v>
       </c>
       <c r="C65" s="25" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="D65" s="27" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E65" s="27" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -17069,16 +17179,16 @@
         <v>8435433518471</v>
       </c>
       <c r="B66" s="25" t="s">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="C66" s="25" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="D66" s="27" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E66" s="27" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -17086,16 +17196,16 @@
         <v>8435425577783</v>
       </c>
       <c r="B67" s="25" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="C67" s="25" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="D67" s="27" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E67" s="27" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -17103,16 +17213,16 @@
         <v>8435433560159</v>
       </c>
       <c r="B68" s="27" t="s">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="C68" s="25" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="D68" s="27" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E68" s="27" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -17120,16 +17230,16 @@
         <v>8435433560210</v>
       </c>
       <c r="B69" s="27" t="s">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="C69" s="25" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="D69" s="27" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E69" s="27" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -17137,16 +17247,16 @@
         <v>8429991787493</v>
       </c>
       <c r="B70" s="27" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="C70" s="25" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="D70" s="27" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E70" s="27" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -17154,16 +17264,16 @@
         <v>8429991787509</v>
       </c>
       <c r="B71" s="27" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="C71" s="25" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="D71" s="27" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E71" s="27" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -17171,16 +17281,16 @@
         <v>8429991787516</v>
       </c>
       <c r="B72" s="27" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="C72" s="25" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="D72" s="27" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E72" s="27" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -17188,16 +17298,16 @@
         <v>8435433538103</v>
       </c>
       <c r="B73" s="27" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="C73" s="25" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="D73" s="27" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E73" s="27" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -17208,13 +17318,13 @@
         <v>147</v>
       </c>
       <c r="C74" s="25" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="D74" s="27" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E74" s="27" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -17222,16 +17332,16 @@
         <v>3663602848349</v>
       </c>
       <c r="B75" s="25" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="C75" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D75" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E75" s="25" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -17242,13 +17352,13 @@
         <v>10</v>
       </c>
       <c r="C76" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D76" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E76" s="25" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -17256,16 +17366,16 @@
         <v>3663602848363</v>
       </c>
       <c r="B77" s="25" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="C77" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D77" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E77" s="25" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -17276,13 +17386,13 @@
         <v>28</v>
       </c>
       <c r="C78" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D78" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E78" s="25" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -17290,16 +17400,16 @@
         <v>8432712279436</v>
       </c>
       <c r="B79" s="25" t="s">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="C79" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D79" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E79" s="25" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -17307,16 +17417,16 @@
         <v>8432712279467</v>
       </c>
       <c r="B80" s="25" t="s">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="C80" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D80" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E80" s="25" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -17324,16 +17434,16 @@
         <v>8435414111127</v>
       </c>
       <c r="B81" s="25" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="C81" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D81" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E81" s="25" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -17341,16 +17451,16 @@
         <v>8435414124240</v>
       </c>
       <c r="B82" s="25" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="C82" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D82" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E82" s="25" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -17361,13 +17471,13 @@
         <v>21</v>
       </c>
       <c r="C83" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D83" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E83" s="25" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -17375,16 +17485,16 @@
         <v>5036581063504</v>
       </c>
       <c r="B84" s="25" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="C84" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D84" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E84" s="25" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -17392,16 +17502,16 @@
         <v>5036581063542</v>
       </c>
       <c r="B85" s="25" t="s">
+        <v>579</v>
+      </c>
+      <c r="C85" s="25" t="s">
         <v>572</v>
       </c>
-      <c r="C85" s="25" t="s">
-        <v>565</v>
-      </c>
       <c r="D85" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E85" s="25" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -17409,16 +17519,16 @@
         <v>5036581063580</v>
       </c>
       <c r="B86" s="25" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="C86" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D86" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E86" s="25" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -17426,16 +17536,16 @@
         <v>5036581064679</v>
       </c>
       <c r="B87" s="25" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="C87" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D87" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E87" s="25" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -17443,16 +17553,16 @@
         <v>5036581064716</v>
       </c>
       <c r="B88" s="25" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="C88" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D88" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E88" s="25" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -17460,16 +17570,16 @@
         <v>5036581064723</v>
       </c>
       <c r="B89" s="25" t="s">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="C89" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D89" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E89" s="25" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -17477,16 +17587,16 @@
         <v>5036581064754</v>
       </c>
       <c r="B90" s="25" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="C90" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D90" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E90" s="25" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -17494,16 +17604,16 @@
         <v>5036581064686</v>
       </c>
       <c r="B91" s="25" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="C91" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D91" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E91" s="25" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -17511,16 +17621,16 @@
         <v>5063022089120</v>
       </c>
       <c r="B92" s="25" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="C92" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D92" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E92" s="25" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -17528,16 +17638,16 @@
         <v>5059340719634</v>
       </c>
       <c r="B93" s="25" t="s">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="C93" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D93" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E93" s="25" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -17545,16 +17655,16 @@
         <v>5059340719603</v>
       </c>
       <c r="B94" s="25" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="C94" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D94" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E94" s="25" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -17562,16 +17672,16 @@
         <v>5036581064310</v>
       </c>
       <c r="B95" s="25" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="C95" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D95" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E95" s="25" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -17579,16 +17689,16 @@
         <v>5036581064327</v>
       </c>
       <c r="B96" s="25" t="s">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="C96" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D96" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E96" s="25" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -17596,16 +17706,16 @@
         <v>5059340269535</v>
       </c>
       <c r="B97" s="25" t="s">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="C97" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D97" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E97" s="25" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -17613,16 +17723,16 @@
         <v>8429991787660</v>
       </c>
       <c r="B98" s="25" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="C98" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D98" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E98" s="25" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -17630,16 +17740,16 @@
         <v>5036581065768</v>
       </c>
       <c r="B99" s="25" t="s">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="C99" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D99" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E99" s="25" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -17647,16 +17757,16 @@
         <v>5036581065775</v>
       </c>
       <c r="B100" s="25" t="s">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="C100" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D100" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E100" s="25" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -17667,13 +17777,13 @@
         <v>38</v>
       </c>
       <c r="C101" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D101" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E101" s="25" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -17684,13 +17794,13 @@
         <v>64</v>
       </c>
       <c r="C102" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D102" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E102" s="25" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -17701,13 +17811,13 @@
         <v>58</v>
       </c>
       <c r="C103" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D103" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E103" s="25" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -17718,13 +17828,13 @@
         <v>61</v>
       </c>
       <c r="C104" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D104" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E104" s="25" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -17732,16 +17842,16 @@
         <v>5036581065744</v>
       </c>
       <c r="B105" s="25" t="s">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="C105" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D105" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E105" s="25" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -17749,16 +17859,16 @@
         <v>5036581065751</v>
       </c>
       <c r="B106" s="25" t="s">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="C106" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D106" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E106" s="25" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -17766,16 +17876,16 @@
         <v>5036581089542</v>
       </c>
       <c r="B107" s="25" t="s">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="C107" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D107" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E107" s="25" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -17783,16 +17893,16 @@
         <v>5036581089566</v>
       </c>
       <c r="B108" s="25" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="C108" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D108" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E108" s="25" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -17800,16 +17910,16 @@
         <v>5036581089597</v>
       </c>
       <c r="B109" s="25" t="s">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="C109" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D109" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E109" s="25" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -17817,16 +17927,16 @@
         <v>5036581089535</v>
       </c>
       <c r="B110" s="25" t="s">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="C110" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D110" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E110" s="25" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -17834,16 +17944,16 @@
         <v>5036581089559</v>
       </c>
       <c r="B111" s="25" t="s">
-        <v>594</v>
+        <v>601</v>
       </c>
       <c r="C111" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D111" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E111" s="25" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -17851,16 +17961,16 @@
         <v>5036581089580</v>
       </c>
       <c r="B112" s="25" t="s">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="C112" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D112" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E112" s="25" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -17868,16 +17978,16 @@
         <v>8435433542377</v>
       </c>
       <c r="B113" s="25" t="s">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="C113" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D113" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E113" s="25" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -17885,16 +17995,16 @@
         <v>8435433542438</v>
       </c>
       <c r="B114" s="25" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="C114" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D114" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E114" s="25" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -17902,16 +18012,16 @@
         <v>8435433544142</v>
       </c>
       <c r="B115" s="25" t="s">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="C115" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D115" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E115" s="25" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -17919,16 +18029,16 @@
         <v>8435433544173</v>
       </c>
       <c r="B116" s="25" t="s">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="C116" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D116" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E116" s="25" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -17936,16 +18046,16 @@
         <v>8429991787707</v>
       </c>
       <c r="B117" s="25" t="s">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="C117" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D117" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E117" s="25" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -17953,16 +18063,16 @@
         <v>8429991787714</v>
       </c>
       <c r="B118" s="25" t="s">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="C118" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D118" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E118" s="25" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -17973,13 +18083,13 @@
         <v>49</v>
       </c>
       <c r="C119" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D119" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E119" s="25" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -17990,13 +18100,13 @@
         <v>46</v>
       </c>
       <c r="C120" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D120" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E120" s="25" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -18007,13 +18117,13 @@
         <v>43</v>
       </c>
       <c r="C121" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D121" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E121" s="25" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -18024,13 +18134,13 @@
         <v>40</v>
       </c>
       <c r="C122" s="25" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D122" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E122" s="25" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -18038,16 +18148,16 @@
         <v>5036581064877</v>
       </c>
       <c r="B123" s="25" t="s">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="C123" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D123" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E123" s="25" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -18055,16 +18165,16 @@
         <v>5036581064884</v>
       </c>
       <c r="B124" s="25" t="s">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="C124" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D124" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E124" s="25" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -18072,16 +18182,16 @@
         <v>8429991787653</v>
       </c>
       <c r="B125" s="25" t="s">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="C125" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D125" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E125" s="25" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -18089,16 +18199,16 @@
         <v>8435414126275</v>
       </c>
       <c r="B126" s="25" t="s">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="C126" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D126" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E126" s="25" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -18109,13 +18219,13 @@
         <v>72</v>
       </c>
       <c r="C127" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D127" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E127" s="25" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -18126,13 +18236,13 @@
         <v>71</v>
       </c>
       <c r="C128" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D128" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E128" s="25" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -18143,13 +18253,13 @@
         <v>69</v>
       </c>
       <c r="C129" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D129" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E129" s="25" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -18160,13 +18270,13 @@
         <v>65</v>
       </c>
       <c r="C130" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D130" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E130" s="25" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -18174,16 +18284,16 @@
         <v>5036581065201</v>
       </c>
       <c r="B131" s="25" t="s">
-        <v>607</v>
+        <v>614</v>
       </c>
       <c r="C131" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D131" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E131" s="25" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -18191,16 +18301,16 @@
         <v>5036581065218</v>
       </c>
       <c r="B132" s="25" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="C132" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D132" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E132" s="25" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -18208,16 +18318,16 @@
         <v>8429991787646</v>
       </c>
       <c r="B133" s="25" t="s">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="C133" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D133" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E133" s="25" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -18228,13 +18338,13 @@
         <v>81</v>
       </c>
       <c r="C134" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D134" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E134" s="25" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -18242,16 +18352,16 @@
         <v>8432712289541</v>
       </c>
       <c r="B135" s="25" t="s">
+        <v>617</v>
+      </c>
+      <c r="C135" s="25" t="s">
         <v>610</v>
       </c>
-      <c r="C135" s="25" t="s">
-        <v>603</v>
-      </c>
       <c r="D135" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E135" s="25" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -18262,13 +18372,13 @@
         <v>77</v>
       </c>
       <c r="C136" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D136" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E136" s="25" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -18279,13 +18389,13 @@
         <v>76</v>
       </c>
       <c r="C137" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D137" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E137" s="25" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -18296,13 +18406,13 @@
         <v>262</v>
       </c>
       <c r="C138" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D138" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E138" s="25" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -18313,13 +18423,13 @@
         <v>70</v>
       </c>
       <c r="C139" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D139" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E139" s="25" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -18327,16 +18437,16 @@
         <v>5059340719610</v>
       </c>
       <c r="B140" s="25" t="s">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="C140" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D140" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E140" s="25" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -18344,16 +18454,16 @@
         <v>5059340719566</v>
       </c>
       <c r="B141" s="25" t="s">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="C141" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D141" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E141" s="25" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -18361,16 +18471,16 @@
         <v>5059340719511</v>
       </c>
       <c r="B142" s="25" t="s">
-        <v>613</v>
+        <v>620</v>
       </c>
       <c r="C142" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D142" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E142" s="25" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -18378,16 +18488,16 @@
         <v>5063022525574</v>
       </c>
       <c r="B143" s="25" t="s">
-        <v>614</v>
+        <v>621</v>
       </c>
       <c r="C143" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D143" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E143" s="25" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -18395,16 +18505,16 @@
         <v>8435433537328</v>
       </c>
       <c r="B144" s="25" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="C144" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D144" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E144" s="25" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -18415,13 +18525,13 @@
         <v>84</v>
       </c>
       <c r="C145" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D145" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E145" s="25" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -18429,16 +18539,16 @@
         <v>8429991787622</v>
       </c>
       <c r="B146" s="25" t="s">
-        <v>616</v>
+        <v>623</v>
       </c>
       <c r="C146" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D146" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E146" s="25" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -18446,16 +18556,16 @@
         <v>8429991792282</v>
       </c>
       <c r="B147" s="25" t="s">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="C147" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D147" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E147" s="25" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -18463,16 +18573,16 @@
         <v>5059340719658</v>
       </c>
       <c r="B148" s="25" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="C148" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D148" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E148" s="25" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -18480,16 +18590,16 @@
         <v>5059340460277</v>
       </c>
       <c r="B149" s="25" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="C149" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D149" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E149" s="25" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -18497,16 +18607,16 @@
         <v>5059340460284</v>
       </c>
       <c r="B150" s="25" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="C150" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D150" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E150" s="25" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -18514,16 +18624,16 @@
         <v>5059340719535</v>
       </c>
       <c r="B151" s="25" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="C151" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D151" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E151" s="25" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -18531,16 +18641,16 @@
         <v>8429991787639</v>
       </c>
       <c r="B152" s="25" t="s">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="C152" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D152" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E152" s="25" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -18551,13 +18661,13 @@
         <v>39</v>
       </c>
       <c r="C153" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D153" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E153" s="25" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -18568,13 +18678,13 @@
         <v>32</v>
       </c>
       <c r="C154" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D154" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E154" s="25" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -18585,13 +18695,13 @@
         <v>75</v>
       </c>
       <c r="C155" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D155" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E155" s="25" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -18599,16 +18709,16 @@
         <v>5059340854229</v>
       </c>
       <c r="B156" s="25" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="C156" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D156" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E156" s="25" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -18619,13 +18729,13 @@
         <v>276</v>
       </c>
       <c r="C157" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D157" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E157" s="25" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -18633,16 +18743,16 @@
         <v>8435414125100</v>
       </c>
       <c r="B158" s="25" t="s">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="C158" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D158" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E158" s="25" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -18650,16 +18760,16 @@
         <v>8435414125131</v>
       </c>
       <c r="B159" s="25" t="s">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="C159" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D159" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E159" s="25" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -18667,16 +18777,16 @@
         <v>8435414124189</v>
       </c>
       <c r="B160" s="25" t="s">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="C160" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D160" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E160" s="25" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -18684,16 +18794,16 @@
         <v>8435414122574</v>
       </c>
       <c r="B161" s="25" t="s">
-        <v>625</v>
+        <v>632</v>
       </c>
       <c r="C161" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D161" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E161" s="25" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -18701,53 +18811,53 @@
         <v>8435414122468</v>
       </c>
       <c r="B162" s="25" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="C162" s="25" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D162" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E162" s="25" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5" ht="15.75">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5">
       <c r="A163" s="24">
         <v>5059340221700</v>
       </c>
       <c r="B163" s="25" t="s">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="C163" s="25" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="D163" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E163" s="25" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5" ht="15.75">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5">
       <c r="A164" s="24">
         <v>5063022611239</v>
       </c>
       <c r="B164" s="25" t="s">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="C164" s="25" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="D164" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E164" s="25" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" ht="15.75">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5">
       <c r="A165" s="24">
         <v>5059340357447</v>
       </c>
@@ -18755,50 +18865,50 @@
         <v>219</v>
       </c>
       <c r="C165" s="25" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="D165" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E165" s="25" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5" ht="15.75">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5">
       <c r="A166" s="24">
         <v>5059340357454</v>
       </c>
       <c r="B166" s="25" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="C166" s="25" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="D166" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E166" s="25" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5" ht="15.75">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5">
       <c r="A167" s="24">
         <v>5059340357461</v>
       </c>
       <c r="B167" s="25" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="C167" s="25" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="D167" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E167" s="25" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5" ht="15.75">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5">
       <c r="A168" s="24">
         <v>5059340221717</v>
       </c>
@@ -18806,16 +18916,16 @@
         <v>218</v>
       </c>
       <c r="C168" s="25" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="D168" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E168" s="25" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5" ht="15.75">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5">
       <c r="A169" s="24">
         <v>5059340802602</v>
       </c>
@@ -18823,16 +18933,16 @@
         <v>220</v>
       </c>
       <c r="C169" s="25" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="D169" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E169" s="25" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5" ht="15.75">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5">
       <c r="A170" s="24">
         <v>5059340802367</v>
       </c>
@@ -18840,16 +18950,16 @@
         <v>217</v>
       </c>
       <c r="C170" s="25" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="D170" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E170" s="25" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5" ht="15.75">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5">
       <c r="A171" s="24">
         <v>5059340802305</v>
       </c>
@@ -18857,16 +18967,16 @@
         <v>223</v>
       </c>
       <c r="C171" s="25" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="D171" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E171" s="25" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5" ht="15.75">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5">
       <c r="A172" s="24">
         <v>5059340802626</v>
       </c>
@@ -18874,16 +18984,16 @@
         <v>221</v>
       </c>
       <c r="C172" s="25" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="D172" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E172" s="25" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5" ht="15.75">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5">
       <c r="A173" s="24">
         <v>5059340802336</v>
       </c>
@@ -18891,16 +19001,16 @@
         <v>222</v>
       </c>
       <c r="C173" s="25" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="D173" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E173" s="25" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" ht="15.75">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
       <c r="A174" s="24">
         <v>5059340802923</v>
       </c>
@@ -18908,16 +19018,16 @@
         <v>227</v>
       </c>
       <c r="C174" s="25" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="D174" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E174" s="25" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5" ht="15.75">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5">
       <c r="A175" s="24">
         <v>5059340802558</v>
       </c>
@@ -18925,16 +19035,16 @@
         <v>229</v>
       </c>
       <c r="C175" s="25" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="D175" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E175" s="25" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5" ht="15.75">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5">
       <c r="A176" s="24">
         <v>5059340802831</v>
       </c>
@@ -18942,101 +19052,101 @@
         <v>228</v>
       </c>
       <c r="C176" s="25" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="D176" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E176" s="25" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5" ht="15.75">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5">
       <c r="A177" s="24">
         <v>5059340969657</v>
       </c>
       <c r="B177" s="25" t="s">
-        <v>632</v>
+        <v>639</v>
       </c>
       <c r="C177" s="25" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="D177" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E177" s="25" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5" ht="15.75">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5">
       <c r="A178" s="24">
         <v>5059340969633</v>
       </c>
       <c r="B178" s="25" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="C178" s="25" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="D178" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E178" s="25" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5" ht="15.75">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5">
       <c r="A179" s="24">
         <v>5059340969640</v>
       </c>
       <c r="B179" s="25" t="s">
-        <v>634</v>
+        <v>641</v>
       </c>
       <c r="C179" s="25" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="D179" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E179" s="25" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5" ht="15.75">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5">
       <c r="A180" s="24">
         <v>5059340969664</v>
       </c>
       <c r="B180" s="25" t="s">
+        <v>642</v>
+      </c>
+      <c r="C180" s="25" t="s">
         <v>635</v>
       </c>
-      <c r="C180" s="25" t="s">
-        <v>628</v>
-      </c>
       <c r="D180" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E180" s="25" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5" ht="15.75">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5">
       <c r="A181" s="24">
         <v>5059340969626</v>
       </c>
       <c r="B181" s="25" t="s">
-        <v>636</v>
+        <v>643</v>
       </c>
       <c r="C181" s="25" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="D181" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E181" s="25" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5" ht="15.75">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5">
       <c r="A182" s="24">
         <v>5059340802473</v>
       </c>
@@ -19044,16 +19154,16 @@
         <v>226</v>
       </c>
       <c r="C182" s="25" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="D182" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E182" s="25" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5" ht="15.75">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5">
       <c r="A183" s="24">
         <v>5059340802725</v>
       </c>
@@ -19061,16 +19171,16 @@
         <v>225</v>
       </c>
       <c r="C183" s="25" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="D183" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E183" s="25" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5" ht="15.75">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5">
       <c r="A184" s="24">
         <v>5059340803074</v>
       </c>
@@ -19078,33 +19188,33 @@
         <v>224</v>
       </c>
       <c r="C184" s="25" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="D184" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E184" s="25" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5" ht="15.75">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5">
       <c r="A185" s="24">
         <v>3663602997436</v>
       </c>
       <c r="B185" s="25" t="s">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="C185" s="25" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="D185" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E185" s="25" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5" ht="15.75">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5">
       <c r="A186" s="24">
         <v>5063022047847</v>
       </c>
@@ -19112,50 +19222,50 @@
         <v>206</v>
       </c>
       <c r="C186" s="25" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="D186" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E186" s="25" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5" ht="15.75">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5">
       <c r="A187" s="24">
         <v>5063022085658</v>
       </c>
       <c r="B187" s="25" t="s">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="C187" s="25" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="D187" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E187" s="25" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5" ht="15.75">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5">
       <c r="A188" s="24">
         <v>3663602997962</v>
       </c>
       <c r="B188" s="25" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="C188" s="25" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="D188" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E188" s="25" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5" ht="15.75">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5">
       <c r="A189" s="24">
         <v>5063022069450</v>
       </c>
@@ -19163,33 +19273,33 @@
         <v>191</v>
       </c>
       <c r="C189" s="25" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="D189" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E189" s="25" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5" ht="15.75">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5">
       <c r="A190" s="24">
         <v>5063022606525</v>
       </c>
       <c r="B190" s="25" t="s">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="C190" s="25" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="D190" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E190" s="25" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5" ht="15.75">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5">
       <c r="A191" s="24">
         <v>5063022047755</v>
       </c>
@@ -19197,50 +19307,50 @@
         <v>190</v>
       </c>
       <c r="C191" s="25" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="D191" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E191" s="25" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5" ht="15.75">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
       <c r="A192" s="24">
         <v>5059340194042</v>
       </c>
       <c r="B192" s="25" t="s">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="C192" s="25" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="D192" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E192" s="25" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="193" spans="1:5" ht="15.75">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5">
       <c r="A193" s="24">
         <v>5063022606068</v>
       </c>
       <c r="B193" s="25" t="s">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="C193" s="25" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="D193" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E193" s="25" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="194" spans="1:5" ht="15.75">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
       <c r="A194" s="24">
         <v>5059340485362</v>
       </c>
@@ -19248,16 +19358,16 @@
         <v>184</v>
       </c>
       <c r="C194" s="25" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="D194" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E194" s="25" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="195" spans="1:5" ht="15.75">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
       <c r="A195" s="24">
         <v>5063022085603</v>
       </c>
@@ -19265,16 +19375,16 @@
         <v>193</v>
       </c>
       <c r="C195" s="25" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="D195" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E195" s="25" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="196" spans="1:5" ht="15.75">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
       <c r="A196" s="24">
         <v>5059340194080</v>
       </c>
@@ -19282,16 +19392,16 @@
         <v>199</v>
       </c>
       <c r="C196" s="25" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="D196" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E196" s="25" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="197" spans="1:5" ht="15.75">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
       <c r="A197" s="24">
         <v>5059340216034</v>
       </c>
@@ -19299,16 +19409,16 @@
         <v>194</v>
       </c>
       <c r="C197" s="25" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="D197" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E197" s="25" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="198" spans="1:5" ht="15.75">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
       <c r="A198" s="24">
         <v>5059340194097</v>
       </c>
@@ -19316,16 +19426,16 @@
         <v>185</v>
       </c>
       <c r="C198" s="25" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="D198" s="25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E198" s="25" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="199" spans="1:5" ht="15.75">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
       <c r="A199" s="24">
         <v>5063022047830</v>
       </c>
@@ -19333,50 +19443,50 @@
         <v>204</v>
       </c>
       <c r="C199" s="25" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="D199" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E199" s="25" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="200" spans="1:5" ht="15.75">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
       <c r="A200" s="24">
         <v>5063022085641</v>
       </c>
       <c r="B200" s="25" t="s">
-        <v>644</v>
+        <v>651</v>
       </c>
       <c r="C200" s="25" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="D200" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E200" s="25" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="201" spans="1:5" ht="15.75">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
       <c r="A201" s="24">
         <v>5063022034496</v>
       </c>
       <c r="B201" s="25" t="s">
+        <v>652</v>
+      </c>
+      <c r="C201" s="25" t="s">
         <v>645</v>
       </c>
-      <c r="C201" s="25" t="s">
-        <v>638</v>
-      </c>
       <c r="D201" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E201" s="25" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="202" spans="1:5" ht="15.75">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
       <c r="A202" s="24">
         <v>5059340391441</v>
       </c>
@@ -19384,67 +19494,67 @@
         <v>207</v>
       </c>
       <c r="C202" s="25" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="D202" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E202" s="25" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="203" spans="1:5" ht="15.75">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
       <c r="A203" s="24">
         <v>5063022606020</v>
       </c>
       <c r="B203" s="25" t="s">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="C203" s="25" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="D203" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E203" s="25" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="204" spans="1:5" ht="15.75">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
       <c r="A204" s="24">
         <v>5063022606037</v>
       </c>
       <c r="B204" s="25" t="s">
-        <v>647</v>
+        <v>654</v>
       </c>
       <c r="C204" s="25" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="D204" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E204" s="25" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="205" spans="1:5" ht="15.75">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
       <c r="A205" s="24">
         <v>5063022606013</v>
       </c>
       <c r="B205" s="25" t="s">
-        <v>648</v>
+        <v>655</v>
       </c>
       <c r="C205" s="25" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="D205" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E205" s="25" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="206" spans="1:5" ht="15.75">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
       <c r="A206" s="24">
         <v>5063022047816</v>
       </c>
@@ -19452,16 +19562,16 @@
         <v>188</v>
       </c>
       <c r="C206" s="25" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="D206" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E206" s="25" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="207" spans="1:5" ht="15.75">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
       <c r="A207" s="24">
         <v>5059340484303</v>
       </c>
@@ -19469,16 +19579,16 @@
         <v>187</v>
       </c>
       <c r="C207" s="25" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="D207" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E207" s="25" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="208" spans="1:5" ht="15.75">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
       <c r="A208" s="24">
         <v>5063022047823</v>
       </c>
@@ -19486,33 +19596,33 @@
         <v>201</v>
       </c>
       <c r="C208" s="25" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="D208" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E208" s="25" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="209" spans="1:5" ht="15.75">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
       <c r="A209" s="24">
         <v>5059340194035</v>
       </c>
       <c r="B209" s="25" t="s">
-        <v>649</v>
+        <v>656</v>
       </c>
       <c r="C209" s="25" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="D209" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E209" s="25" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="210" spans="1:5" ht="15.75">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
       <c r="A210" s="24">
         <v>5059340194073</v>
       </c>
@@ -19520,13 +19630,13 @@
         <v>183</v>
       </c>
       <c r="C210" s="25" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="D210" s="25" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E210" s="25" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
     </row>
   </sheetData>

--- a/ceramica_proyecto.xlsx
+++ b/ceramica_proyecto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Camero\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3DF71F0E-0D2D-4975-963A-DAA5B3AB22D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{797BE069-283E-4A7A-A987-1907FC11A957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="3" xr2:uid="{6A0D054A-EA90-43D3-9946-5E896568E0A7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1488" uniqueCount="657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="654">
   <si>
     <t>EAN</t>
   </si>
@@ -3740,6 +3740,9 @@
     <t>PAV. SHADED 30X60 GRIS</t>
   </si>
   <si>
+    <t>RACK 10</t>
+  </si>
+  <si>
     <t>PAV. NATURAL BLANCO 30X60</t>
   </si>
   <si>
@@ -3806,15 +3809,9 @@
     <t>PAV. CARYO SALIDA 33X33 MARRÓN</t>
   </si>
   <si>
-    <t>RACK 10</t>
-  </si>
-  <si>
     <t>PAV.WOLFY BEIGE 30X60</t>
   </si>
   <si>
-    <t>PAV.WOLFY GRIS 30X60</t>
-  </si>
-  <si>
     <t>PAV. PORC. SOMO GRIS C2</t>
   </si>
   <si>
@@ -3860,9 +3857,6 @@
     <t>RACK 09</t>
   </si>
   <si>
-    <t>#A AZ. DEC.BL ALEXAND 25X40</t>
-  </si>
-  <si>
     <t>#A AZ. BLANCO BRILLO 20X20.</t>
   </si>
   <si>
@@ -3912,9 +3906,6 @@
   </si>
   <si>
     <t>#A AZ. PEROUSO 30X60 DECOR</t>
-  </si>
-  <si>
-    <t>#AZ CRIZI BLANCO MATE 30X60</t>
   </si>
   <si>
     <t>BLANCO BRILLO 30X60 RECT</t>
@@ -4307,7 +4298,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4385,7 +4376,6 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4909,8 +4899,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{04895F0D-CED9-49B0-B76F-B45DB5CC94A2}" name="SHOWROOM" displayName="SHOWROOM" ref="A1:E210" totalsRowShown="0" dataDxfId="7" headerRowBorderDxfId="5" tableBorderDxfId="6">
-  <autoFilter ref="A1:E210" xr:uid="{04895F0D-CED9-49B0-B76F-B45DB5CC94A2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{04895F0D-CED9-49B0-B76F-B45DB5CC94A2}" name="SHOWROOM" displayName="SHOWROOM" ref="A1:E207" totalsRowShown="0" dataDxfId="7" headerRowBorderDxfId="5" tableBorderDxfId="6">
+  <autoFilter ref="A1:E207" xr:uid="{04895F0D-CED9-49B0-B76F-B45DB5CC94A2}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{988177E9-8B74-4DA8-8D93-E60B539BC797}" name="EAN" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{9354D9B3-F652-4D41-B841-C67C7F44B562}" name="descrpcion_es" dataDxfId="3"/>
@@ -5433,19 +5423,19 @@
       </c>
       <c r="D6" s="14" t="str">
         <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="E6" s="14" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 09</v>
-      </c>
-      <c r="F6" s="14" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
-        <v>MODULO 1</v>
-      </c>
-      <c r="G6" s="14" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
-        <v>FILA 1</v>
+        <v>NO</v>
+      </c>
+      <c r="E6" s="14" t="e">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F6" s="14" t="e">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G6" s="14" t="e">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
+        <v>#N/A</v>
       </c>
       <c r="H6" s="15" t="str">
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
@@ -5667,19 +5657,19 @@
       </c>
       <c r="D12" s="14" t="str">
         <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="E12" s="14" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 09</v>
-      </c>
-      <c r="F12" s="14" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
-        <v>MODULO 1</v>
-      </c>
-      <c r="G12" s="14" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
-        <v>FILA 4</v>
+        <v>NO</v>
+      </c>
+      <c r="E12" s="14" t="e">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F12" s="14" t="e">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G12" s="14" t="e">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
+        <v>#N/A</v>
       </c>
       <c r="H12" s="15" t="str">
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
@@ -5952,7 +5942,7 @@
       </c>
       <c r="G19" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
-        <v>FILA 4</v>
+        <v>FILA 5</v>
       </c>
       <c r="H19" s="15" t="str">
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
@@ -6369,19 +6359,19 @@
       </c>
       <c r="D30" s="14" t="str">
         <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="E30" s="14" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 09</v>
-      </c>
-      <c r="F30" s="14" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
-        <v>MODULO 2</v>
-      </c>
-      <c r="G30" s="14" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
-        <v>FILA 1</v>
+        <v>NO</v>
+      </c>
+      <c r="E30" s="14" t="e">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F30" s="14" t="e">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G30" s="14" t="e">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
+        <v>#N/A</v>
       </c>
       <c r="H30" s="15" t="str">
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
@@ -7356,7 +7346,7 @@
       </c>
       <c r="G55" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
-        <v>FILA 3</v>
+        <v>FILA 1</v>
       </c>
       <c r="H55" s="15" t="str">
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
@@ -9298,7 +9288,7 @@
       </c>
       <c r="E105" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 12</v>
+        <v>RACK 10</v>
       </c>
       <c r="F105" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
@@ -9306,7 +9296,7 @@
       </c>
       <c r="G105" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
-        <v>FILA 2</v>
+        <v>FILA 1</v>
       </c>
       <c r="H105" s="15" t="str">
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
@@ -9657,7 +9647,7 @@
       </c>
       <c r="G114" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
-        <v>FILA 2</v>
+        <v>FILA 3</v>
       </c>
       <c r="H114" s="15" t="str">
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
@@ -9774,7 +9764,7 @@
       </c>
       <c r="G117" s="14" t="str">
         <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
-        <v>FILA 3</v>
+        <v>FILA 2</v>
       </c>
       <c r="H117" s="15" t="str">
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
@@ -10893,19 +10883,19 @@
       </c>
       <c r="D146" s="14" t="str">
         <f>IF(COUNTIF(SHOWROOM[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
-        <v>SI</v>
-      </c>
-      <c r="E146" s="14" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
-        <v>RACK 10</v>
-      </c>
-      <c r="F146" s="14" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
-        <v>MODULO 1</v>
-      </c>
-      <c r="G146" s="14" t="str">
-        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
-        <v>FILA 1</v>
+        <v>NO</v>
+      </c>
+      <c r="E146" s="14" t="e">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],3,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F146" s="14" t="e">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],4,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G146" s="14" t="e">
+        <f>VLOOKUP(EXISTENCIA[[#This Row],[EAN]],SHOWROOM[],5,FALSE)</f>
+        <v>#N/A</v>
       </c>
       <c r="H146" s="15" t="str">
         <f>IF(COUNTIF(ALMACEN[EAN],EXISTENCIA[[#This Row],[EAN]])&gt;0,"SI","NO")</f>
@@ -15307,7 +15297,7 @@
       <c r="B142" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="C142" s="43" t="s">
+      <c r="C142" s="31" t="s">
         <v>391</v>
       </c>
     </row>
@@ -15318,7 +15308,7 @@
       <c r="B143" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="C143" s="43" t="s">
+      <c r="C143" s="31" t="s">
         <v>392</v>
       </c>
     </row>
@@ -15329,7 +15319,7 @@
       <c r="B144" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="C144" s="43" t="s">
+      <c r="C144" s="31" t="s">
         <v>393</v>
       </c>
     </row>
@@ -15340,7 +15330,7 @@
       <c r="B145" s="29" t="s">
         <v>143</v>
       </c>
-      <c r="C145" s="43" t="s">
+      <c r="C145" s="31" t="s">
         <v>394</v>
       </c>
     </row>
@@ -15351,7 +15341,7 @@
       <c r="B146" s="29" t="s">
         <v>159</v>
       </c>
-      <c r="C146" s="43" t="s">
+      <c r="C146" s="31" t="s">
         <v>395</v>
       </c>
     </row>
@@ -15362,7 +15352,7 @@
       <c r="B147" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="C147" s="43" t="s">
+      <c r="C147" s="31" t="s">
         <v>396</v>
       </c>
     </row>
@@ -15373,7 +15363,7 @@
       <c r="B148" s="29" t="s">
         <v>182</v>
       </c>
-      <c r="C148" s="43" t="s">
+      <c r="C148" s="31" t="s">
         <v>397</v>
       </c>
     </row>
@@ -15384,7 +15374,7 @@
       <c r="B149" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="C149" s="43" t="s">
+      <c r="C149" s="31" t="s">
         <v>398</v>
       </c>
     </row>
@@ -16060,7 +16050,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD330A52-AB76-4016-8757-0329F27DD631}">
-  <dimension ref="A1:E210"/>
+  <dimension ref="A1:E207"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
@@ -16508,7 +16498,7 @@
         <v>493</v>
       </c>
       <c r="E26" s="25" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -16542,7 +16532,7 @@
         <v>493</v>
       </c>
       <c r="E28" s="25" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -16655,13 +16645,13 @@
         <v>532</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>520</v>
+        <v>533</v>
       </c>
       <c r="D35" s="25" t="s">
         <v>496</v>
       </c>
       <c r="E35" s="25" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -16669,7 +16659,7 @@
         <v>3663602678298</v>
       </c>
       <c r="B36" s="25" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C36" s="25" t="s">
         <v>520</v>
@@ -16686,7 +16676,7 @@
         <v>5059340459912</v>
       </c>
       <c r="B37" s="25" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C37" s="25" t="s">
         <v>520</v>
@@ -16703,7 +16693,7 @@
         <v>5059340854236</v>
       </c>
       <c r="B38" s="25" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C38" s="25" t="s">
         <v>520</v>
@@ -16720,7 +16710,7 @@
         <v>3663602678366</v>
       </c>
       <c r="B39" s="25" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C39" s="25" t="s">
         <v>520</v>
@@ -16737,7 +16727,7 @@
         <v>3663602678465</v>
       </c>
       <c r="B40" s="25" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C40" s="25" t="s">
         <v>520</v>
@@ -16754,10 +16744,10 @@
         <v>5059340720951</v>
       </c>
       <c r="B41" s="25" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C41" s="25" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D41" s="25" t="s">
         <v>493</v>
@@ -16771,10 +16761,10 @@
         <v>5063022645289</v>
       </c>
       <c r="B42" s="25" t="s">
+        <v>541</v>
+      </c>
+      <c r="C42" s="25" t="s">
         <v>540</v>
-      </c>
-      <c r="C42" s="25" t="s">
-        <v>539</v>
       </c>
       <c r="D42" s="25" t="s">
         <v>493</v>
@@ -16788,10 +16778,10 @@
         <v>8429991798864</v>
       </c>
       <c r="B43" s="25" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C43" s="25" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D43" s="25" t="s">
         <v>493</v>
@@ -16805,10 +16795,10 @@
         <v>5059340721026</v>
       </c>
       <c r="B44" s="25" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C44" s="25" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D44" s="25" t="s">
         <v>493</v>
@@ -16822,10 +16812,10 @@
         <v>3663602677413</v>
       </c>
       <c r="B45" s="25" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C45" s="25" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D45" s="25" t="s">
         <v>493</v>
@@ -16839,10 +16829,10 @@
         <v>8435609317396</v>
       </c>
       <c r="B46" s="25" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C46" s="25" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D46" s="25" t="s">
         <v>493</v>
@@ -16856,10 +16846,10 @@
         <v>8429991953577</v>
       </c>
       <c r="B47" s="25" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C47" s="25" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D47" s="25" t="s">
         <v>493</v>
@@ -16873,10 +16863,10 @@
         <v>8429991798888</v>
       </c>
       <c r="B48" s="25" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C48" s="25" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D48" s="25" t="s">
         <v>493</v>
@@ -16890,10 +16880,10 @@
         <v>8429991798901</v>
       </c>
       <c r="B49" s="25" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C49" s="25" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D49" s="25" t="s">
         <v>493</v>
@@ -16907,10 +16897,10 @@
         <v>5059340460383</v>
       </c>
       <c r="B50" s="25" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C50" s="25" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D50" s="25" t="s">
         <v>496</v>
@@ -16924,10 +16914,10 @@
         <v>5059340721040</v>
       </c>
       <c r="B51" s="25" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C51" s="25" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D51" s="25" t="s">
         <v>496</v>
@@ -16941,10 +16931,10 @@
         <v>5059340720999</v>
       </c>
       <c r="B52" s="25" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C52" s="25" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D52" s="25" t="s">
         <v>496</v>
@@ -16958,10 +16948,10 @@
         <v>8432712270556</v>
       </c>
       <c r="B53" s="25" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C53" s="25" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D53" s="25" t="s">
         <v>496</v>
@@ -16975,10 +16965,10 @@
         <v>8435414101517</v>
       </c>
       <c r="B54" s="25" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C54" s="25" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D54" s="25" t="s">
         <v>496</v>
@@ -16992,10 +16982,10 @@
         <v>8429991787479</v>
       </c>
       <c r="B55" s="25" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C55" s="25" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D55" s="25" t="s">
         <v>496</v>
@@ -17009,10 +16999,10 @@
         <v>5059340720982</v>
       </c>
       <c r="B56" s="27" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C56" s="25" t="s">
-        <v>555</v>
+        <v>533</v>
       </c>
       <c r="D56" s="27" t="s">
         <v>493</v>
@@ -17029,7 +17019,7 @@
         <v>556</v>
       </c>
       <c r="C57" s="25" t="s">
-        <v>555</v>
+        <v>533</v>
       </c>
       <c r="D57" s="27" t="s">
         <v>493</v>
@@ -17040,13 +17030,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="26">
-        <v>5036581058326</v>
+        <v>8429991787486</v>
       </c>
       <c r="B58" s="27" t="s">
         <v>557</v>
       </c>
       <c r="C58" s="25" t="s">
-        <v>555</v>
+        <v>533</v>
       </c>
       <c r="D58" s="27" t="s">
         <v>493</v>
@@ -17057,30 +17047,30 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="26">
-        <v>8429991787486</v>
+        <v>8435433538134</v>
       </c>
       <c r="B59" s="27" t="s">
         <v>558</v>
       </c>
       <c r="C59" s="25" t="s">
-        <v>555</v>
+        <v>533</v>
       </c>
       <c r="D59" s="27" t="s">
         <v>493</v>
       </c>
       <c r="E59" s="27" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="26">
-        <v>8435433538134</v>
+        <v>8435414118669</v>
       </c>
       <c r="B60" s="27" t="s">
         <v>559</v>
       </c>
       <c r="C60" s="25" t="s">
-        <v>555</v>
+        <v>533</v>
       </c>
       <c r="D60" s="27" t="s">
         <v>493</v>
@@ -17091,13 +17081,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="26">
-        <v>8435414118669</v>
+        <v>8435414118645</v>
       </c>
       <c r="B61" s="27" t="s">
         <v>560</v>
       </c>
       <c r="C61" s="25" t="s">
-        <v>555</v>
+        <v>533</v>
       </c>
       <c r="D61" s="27" t="s">
         <v>493</v>
@@ -17108,13 +17098,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="26">
-        <v>8435414118645</v>
+        <v>8435414120211</v>
       </c>
       <c r="B62" s="27" t="s">
-        <v>561</v>
+        <v>151</v>
       </c>
       <c r="C62" s="25" t="s">
-        <v>555</v>
+        <v>533</v>
       </c>
       <c r="D62" s="27" t="s">
         <v>493</v>
@@ -17125,13 +17115,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="26">
-        <v>8435414120211</v>
+        <v>8435609351932</v>
       </c>
       <c r="B63" s="27" t="s">
-        <v>151</v>
+        <v>561</v>
       </c>
       <c r="C63" s="25" t="s">
-        <v>555</v>
+        <v>533</v>
       </c>
       <c r="D63" s="27" t="s">
         <v>493</v>
@@ -17142,30 +17132,30 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="26">
-        <v>8435609351932</v>
+        <v>5059340721033</v>
       </c>
       <c r="B64" s="27" t="s">
-        <v>562</v>
+        <v>296</v>
       </c>
       <c r="C64" s="25" t="s">
-        <v>555</v>
+        <v>533</v>
       </c>
       <c r="D64" s="27" t="s">
         <v>493</v>
       </c>
       <c r="E64" s="27" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="65" spans="1:5">
-      <c r="A65" s="26">
-        <v>5059340721033</v>
-      </c>
-      <c r="B65" s="27" t="s">
-        <v>296</v>
+      <c r="A65" s="24">
+        <v>8435433518471</v>
+      </c>
+      <c r="B65" s="25" t="s">
+        <v>562</v>
       </c>
       <c r="C65" s="25" t="s">
-        <v>555</v>
+        <v>533</v>
       </c>
       <c r="D65" s="27" t="s">
         <v>493</v>
@@ -17176,13 +17166,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="24">
-        <v>8435433518471</v>
+        <v>8435425577783</v>
       </c>
       <c r="B66" s="25" t="s">
         <v>563</v>
       </c>
       <c r="C66" s="25" t="s">
-        <v>555</v>
+        <v>533</v>
       </c>
       <c r="D66" s="27" t="s">
         <v>493</v>
@@ -17192,31 +17182,31 @@
       </c>
     </row>
     <row r="67" spans="1:5">
-      <c r="A67" s="24">
-        <v>8435425577783</v>
-      </c>
-      <c r="B67" s="25" t="s">
+      <c r="A67" s="26">
+        <v>8435433560159</v>
+      </c>
+      <c r="B67" s="27" t="s">
         <v>564</v>
       </c>
       <c r="C67" s="25" t="s">
-        <v>555</v>
+        <v>533</v>
       </c>
       <c r="D67" s="27" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E67" s="27" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="26">
-        <v>8435433560159</v>
+        <v>8435433560210</v>
       </c>
       <c r="B68" s="27" t="s">
         <v>565</v>
       </c>
       <c r="C68" s="25" t="s">
-        <v>555</v>
+        <v>533</v>
       </c>
       <c r="D68" s="27" t="s">
         <v>496</v>
@@ -17227,13 +17217,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="26">
-        <v>8435433560210</v>
+        <v>8429991787493</v>
       </c>
       <c r="B69" s="27" t="s">
         <v>566</v>
       </c>
       <c r="C69" s="25" t="s">
-        <v>555</v>
+        <v>533</v>
       </c>
       <c r="D69" s="27" t="s">
         <v>496</v>
@@ -17244,30 +17234,30 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="26">
-        <v>8429991787493</v>
+        <v>8429991787509</v>
       </c>
       <c r="B70" s="27" t="s">
         <v>567</v>
       </c>
       <c r="C70" s="25" t="s">
-        <v>555</v>
+        <v>533</v>
       </c>
       <c r="D70" s="27" t="s">
         <v>496</v>
       </c>
       <c r="E70" s="27" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="26">
-        <v>8429991787509</v>
+        <v>8429991787516</v>
       </c>
       <c r="B71" s="27" t="s">
         <v>568</v>
       </c>
       <c r="C71" s="25" t="s">
-        <v>555</v>
+        <v>533</v>
       </c>
       <c r="D71" s="27" t="s">
         <v>496</v>
@@ -17278,13 +17268,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="26">
-        <v>8429991787516</v>
+        <v>8435433538103</v>
       </c>
       <c r="B72" s="27" t="s">
         <v>569</v>
       </c>
       <c r="C72" s="25" t="s">
-        <v>555</v>
+        <v>533</v>
       </c>
       <c r="D72" s="27" t="s">
         <v>496</v>
@@ -17295,13 +17285,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="26">
-        <v>8435433538103</v>
+        <v>5059340830179</v>
       </c>
       <c r="B73" s="27" t="s">
-        <v>570</v>
+        <v>147</v>
       </c>
       <c r="C73" s="25" t="s">
-        <v>555</v>
+        <v>533</v>
       </c>
       <c r="D73" s="27" t="s">
         <v>496</v>
@@ -17311,31 +17301,31 @@
       </c>
     </row>
     <row r="74" spans="1:5">
-      <c r="A74" s="26">
-        <v>5059340830179</v>
-      </c>
-      <c r="B74" s="27" t="s">
-        <v>147</v>
+      <c r="A74" s="24">
+        <v>3663602848349</v>
+      </c>
+      <c r="B74" s="25" t="s">
+        <v>570</v>
       </c>
       <c r="C74" s="25" t="s">
-        <v>555</v>
-      </c>
-      <c r="D74" s="27" t="s">
-        <v>496</v>
-      </c>
-      <c r="E74" s="27" t="s">
-        <v>499</v>
+        <v>571</v>
+      </c>
+      <c r="D74" s="25" t="s">
+        <v>493</v>
+      </c>
+      <c r="E74" s="25" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="24">
-        <v>3663602848349</v>
+        <v>5059340460222</v>
       </c>
       <c r="B75" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C75" s="25" t="s">
         <v>571</v>
-      </c>
-      <c r="C75" s="25" t="s">
-        <v>572</v>
       </c>
       <c r="D75" s="25" t="s">
         <v>493</v>
@@ -17346,13 +17336,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="24">
-        <v>5059340460222</v>
+        <v>5059340719559</v>
       </c>
       <c r="B76" s="25" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="C76" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D76" s="25" t="s">
         <v>493</v>
@@ -17363,47 +17353,47 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="24">
-        <v>3663602848363</v>
+        <v>8432712279436</v>
       </c>
       <c r="B77" s="25" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C77" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D77" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E77" s="25" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="24">
-        <v>5059340719559</v>
+        <v>8432712279467</v>
       </c>
       <c r="B78" s="25" t="s">
-        <v>28</v>
+        <v>573</v>
       </c>
       <c r="C78" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D78" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E78" s="25" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="24">
-        <v>8432712279436</v>
+        <v>8435414111127</v>
       </c>
       <c r="B79" s="25" t="s">
         <v>574</v>
       </c>
       <c r="C79" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D79" s="25" t="s">
         <v>493</v>
@@ -17414,13 +17404,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="24">
-        <v>8432712279467</v>
+        <v>8435414124240</v>
       </c>
       <c r="B80" s="25" t="s">
         <v>575</v>
       </c>
       <c r="C80" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D80" s="25" t="s">
         <v>493</v>
@@ -17431,47 +17421,47 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="24">
-        <v>8435414111127</v>
+        <v>5036581063887</v>
       </c>
       <c r="B81" s="25" t="s">
-        <v>576</v>
+        <v>21</v>
       </c>
       <c r="C81" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D81" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E81" s="25" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="24">
-        <v>8435414124240</v>
+        <v>5036581063504</v>
       </c>
       <c r="B82" s="25" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C82" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D82" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E82" s="25" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="24">
-        <v>5036581063887</v>
+        <v>5036581063542</v>
       </c>
       <c r="B83" s="25" t="s">
-        <v>21</v>
+        <v>577</v>
       </c>
       <c r="C83" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D83" s="25" t="s">
         <v>493</v>
@@ -17482,13 +17472,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="24">
-        <v>5036581063504</v>
+        <v>5036581063580</v>
       </c>
       <c r="B84" s="25" t="s">
         <v>578</v>
       </c>
       <c r="C84" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D84" s="25" t="s">
         <v>493</v>
@@ -17499,64 +17489,64 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="24">
-        <v>5036581063542</v>
+        <v>5036581064679</v>
       </c>
       <c r="B85" s="25" t="s">
         <v>579</v>
       </c>
       <c r="C85" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D85" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E85" s="25" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="24">
-        <v>5036581063580</v>
+        <v>5036581064716</v>
       </c>
       <c r="B86" s="25" t="s">
         <v>580</v>
       </c>
       <c r="C86" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D86" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E86" s="25" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="24">
-        <v>5036581064679</v>
+        <v>5036581064723</v>
       </c>
       <c r="B87" s="25" t="s">
         <v>581</v>
       </c>
       <c r="C87" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D87" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E87" s="25" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="24">
-        <v>5036581064716</v>
+        <v>5036581064754</v>
       </c>
       <c r="B88" s="25" t="s">
         <v>582</v>
       </c>
       <c r="C88" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D88" s="25" t="s">
         <v>493</v>
@@ -17567,13 +17557,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="24">
-        <v>5036581064723</v>
+        <v>5036581064686</v>
       </c>
       <c r="B89" s="25" t="s">
         <v>583</v>
       </c>
       <c r="C89" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D89" s="25" t="s">
         <v>493</v>
@@ -17584,13 +17574,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="24">
-        <v>5036581064754</v>
+        <v>5063022089120</v>
       </c>
       <c r="B90" s="25" t="s">
         <v>584</v>
       </c>
       <c r="C90" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D90" s="25" t="s">
         <v>493</v>
@@ -17601,13 +17591,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="24">
-        <v>5036581064686</v>
+        <v>5059340719634</v>
       </c>
       <c r="B91" s="25" t="s">
         <v>585</v>
       </c>
       <c r="C91" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D91" s="25" t="s">
         <v>493</v>
@@ -17618,13 +17608,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="24">
-        <v>5063022089120</v>
+        <v>5059340719603</v>
       </c>
       <c r="B92" s="25" t="s">
         <v>586</v>
       </c>
       <c r="C92" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D92" s="25" t="s">
         <v>493</v>
@@ -17635,47 +17625,47 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="24">
-        <v>5059340719634</v>
+        <v>5036581064310</v>
       </c>
       <c r="B93" s="25" t="s">
         <v>587</v>
       </c>
       <c r="C93" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D93" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E93" s="25" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="24">
-        <v>5059340719603</v>
+        <v>5036581064327</v>
       </c>
       <c r="B94" s="25" t="s">
         <v>588</v>
       </c>
       <c r="C94" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D94" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E94" s="25" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="24">
-        <v>5036581064310</v>
+        <v>8429991787660</v>
       </c>
       <c r="B95" s="25" t="s">
         <v>589</v>
       </c>
       <c r="C95" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D95" s="25" t="s">
         <v>493</v>
@@ -17686,115 +17676,115 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="24">
-        <v>5036581064327</v>
+        <v>5036581065768</v>
       </c>
       <c r="B96" s="25" t="s">
         <v>590</v>
       </c>
       <c r="C96" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D96" s="25" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E96" s="25" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="24">
-        <v>5059340269535</v>
+        <v>5036581065775</v>
       </c>
       <c r="B97" s="25" t="s">
         <v>591</v>
       </c>
       <c r="C97" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D97" s="25" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E97" s="25" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5">
-      <c r="A98" s="24">
-        <v>8429991787660</v>
-      </c>
-      <c r="B98" s="25" t="s">
-        <v>592</v>
+        <v>494</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="15.75">
+      <c r="A98" s="12">
+        <v>5036581089535</v>
+      </c>
+      <c r="B98" s="13" t="s">
+        <v>63</v>
       </c>
       <c r="C98" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D98" s="25" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E98" s="25" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="24">
-        <v>5036581065768</v>
+        <v>5059340460208</v>
       </c>
       <c r="B99" s="25" t="s">
-        <v>593</v>
+        <v>64</v>
       </c>
       <c r="C99" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D99" s="25" t="s">
         <v>496</v>
       </c>
       <c r="E99" s="25" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="24">
-        <v>5036581065775</v>
+        <v>5059340460215</v>
       </c>
       <c r="B100" s="25" t="s">
-        <v>594</v>
+        <v>58</v>
       </c>
       <c r="C100" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D100" s="25" t="s">
         <v>496</v>
       </c>
       <c r="E100" s="25" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="24">
-        <v>5036581066345</v>
+        <v>5059340460239</v>
       </c>
       <c r="B101" s="25" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="C101" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D101" s="25" t="s">
         <v>496</v>
       </c>
       <c r="E101" s="25" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="24">
-        <v>5059340460208</v>
+        <v>5036581065744</v>
       </c>
       <c r="B102" s="25" t="s">
-        <v>64</v>
+        <v>592</v>
       </c>
       <c r="C102" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D102" s="25" t="s">
         <v>496</v>
@@ -17805,13 +17795,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="24">
-        <v>5059340460215</v>
+        <v>5036581065751</v>
       </c>
       <c r="B103" s="25" t="s">
-        <v>58</v>
+        <v>593</v>
       </c>
       <c r="C103" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D103" s="25" t="s">
         <v>496</v>
@@ -17822,64 +17812,64 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="24">
-        <v>5059340460239</v>
+        <v>5036581089542</v>
       </c>
       <c r="B104" s="25" t="s">
-        <v>61</v>
+        <v>594</v>
       </c>
       <c r="C104" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D104" s="25" t="s">
         <v>496</v>
       </c>
       <c r="E104" s="25" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="24">
-        <v>5036581065744</v>
+        <v>5036581089566</v>
       </c>
       <c r="B105" s="25" t="s">
         <v>595</v>
       </c>
       <c r="C105" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D105" s="25" t="s">
         <v>496</v>
       </c>
       <c r="E105" s="25" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="24">
-        <v>5036581065751</v>
+        <v>5036581089597</v>
       </c>
       <c r="B106" s="25" t="s">
         <v>596</v>
       </c>
       <c r="C106" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D106" s="25" t="s">
         <v>496</v>
       </c>
       <c r="E106" s="25" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="24">
-        <v>5036581089542</v>
+        <v>5036581089535</v>
       </c>
       <c r="B107" s="25" t="s">
         <v>597</v>
       </c>
       <c r="C107" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D107" s="25" t="s">
         <v>496</v>
@@ -17890,13 +17880,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="24">
-        <v>5036581089566</v>
+        <v>5036581089559</v>
       </c>
       <c r="B108" s="25" t="s">
         <v>598</v>
       </c>
       <c r="C108" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D108" s="25" t="s">
         <v>496</v>
@@ -17907,13 +17897,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="24">
-        <v>5036581089597</v>
+        <v>5036581089580</v>
       </c>
       <c r="B109" s="25" t="s">
         <v>599</v>
       </c>
       <c r="C109" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D109" s="25" t="s">
         <v>496</v>
@@ -17924,64 +17914,64 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="24">
-        <v>5036581089535</v>
+        <v>8435433542377</v>
       </c>
       <c r="B110" s="25" t="s">
         <v>600</v>
       </c>
       <c r="C110" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D110" s="25" t="s">
         <v>496</v>
       </c>
       <c r="E110" s="25" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="24">
-        <v>5036581089559</v>
+        <v>8435433542438</v>
       </c>
       <c r="B111" s="25" t="s">
         <v>601</v>
       </c>
       <c r="C111" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D111" s="25" t="s">
         <v>496</v>
       </c>
       <c r="E111" s="25" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="24">
-        <v>5036581089580</v>
+        <v>8435433544142</v>
       </c>
       <c r="B112" s="25" t="s">
         <v>602</v>
       </c>
       <c r="C112" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D112" s="25" t="s">
         <v>496</v>
       </c>
       <c r="E112" s="25" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="24">
-        <v>8435433542377</v>
+        <v>8435433544173</v>
       </c>
       <c r="B113" s="25" t="s">
         <v>603</v>
       </c>
       <c r="C113" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D113" s="25" t="s">
         <v>496</v>
@@ -17992,13 +17982,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="24">
-        <v>8435433542438</v>
+        <v>8429991787707</v>
       </c>
       <c r="B114" s="25" t="s">
         <v>604</v>
       </c>
       <c r="C114" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D114" s="25" t="s">
         <v>496</v>
@@ -18009,13 +17999,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="24">
-        <v>8435433544142</v>
+        <v>8429991787714</v>
       </c>
       <c r="B115" s="25" t="s">
         <v>605</v>
       </c>
       <c r="C115" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D115" s="25" t="s">
         <v>496</v>
@@ -18026,64 +18016,64 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="24">
-        <v>8435433544173</v>
+        <v>5036581066406</v>
       </c>
       <c r="B116" s="25" t="s">
-        <v>606</v>
+        <v>49</v>
       </c>
       <c r="C116" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D116" s="25" t="s">
         <v>496</v>
       </c>
       <c r="E116" s="25" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="24">
-        <v>8429991787707</v>
+        <v>5059340781969</v>
       </c>
       <c r="B117" s="25" t="s">
-        <v>607</v>
+        <v>46</v>
       </c>
       <c r="C117" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D117" s="25" t="s">
         <v>496</v>
       </c>
       <c r="E117" s="25" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="24">
-        <v>8429991787714</v>
+        <v>5059340815510</v>
       </c>
       <c r="B118" s="25" t="s">
-        <v>608</v>
+        <v>43</v>
       </c>
       <c r="C118" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D118" s="25" t="s">
         <v>496</v>
       </c>
       <c r="E118" s="25" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="24">
-        <v>5036581066406</v>
+        <v>8435414120945</v>
       </c>
       <c r="B119" s="25" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C119" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D119" s="25" t="s">
         <v>496</v>
@@ -18094,64 +18084,64 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="24">
-        <v>5059340781969</v>
+        <v>5036581064877</v>
       </c>
       <c r="B120" s="25" t="s">
-        <v>46</v>
+        <v>606</v>
       </c>
       <c r="C120" s="25" t="s">
-        <v>572</v>
+        <v>607</v>
       </c>
       <c r="D120" s="25" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="E120" s="25" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="24">
-        <v>5059340815510</v>
+        <v>5036581064884</v>
       </c>
       <c r="B121" s="25" t="s">
-        <v>43</v>
+        <v>608</v>
       </c>
       <c r="C121" s="25" t="s">
-        <v>572</v>
+        <v>607</v>
       </c>
       <c r="D121" s="25" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="E121" s="25" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="24">
-        <v>8435414120945</v>
+        <v>8429991787653</v>
       </c>
       <c r="B122" s="25" t="s">
-        <v>40</v>
+        <v>609</v>
       </c>
       <c r="C122" s="25" t="s">
-        <v>572</v>
+        <v>607</v>
       </c>
       <c r="D122" s="25" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="E122" s="25" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="24">
-        <v>5036581064877</v>
+        <v>8435414126275</v>
       </c>
       <c r="B123" s="25" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C123" s="25" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D123" s="25" t="s">
         <v>493</v>
@@ -18162,64 +18152,64 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="24">
-        <v>5036581064884</v>
+        <v>5059340719542</v>
       </c>
       <c r="B124" s="25" t="s">
-        <v>611</v>
+        <v>72</v>
       </c>
       <c r="C124" s="25" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D124" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E124" s="25" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="24">
-        <v>8429991787653</v>
+        <v>5059340719627</v>
       </c>
       <c r="B125" s="25" t="s">
-        <v>612</v>
+        <v>71</v>
       </c>
       <c r="C125" s="25" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D125" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E125" s="25" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="24">
-        <v>8435414126275</v>
+        <v>5059340719528</v>
       </c>
       <c r="B126" s="25" t="s">
-        <v>613</v>
+        <v>69</v>
       </c>
       <c r="C126" s="25" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D126" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E126" s="25" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="24">
-        <v>5059340719542</v>
+        <v>5059340781976</v>
       </c>
       <c r="B127" s="25" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C127" s="25" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D127" s="25" t="s">
         <v>493</v>
@@ -18230,115 +18220,115 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="24">
-        <v>5059340719627</v>
+        <v>5036581065201</v>
       </c>
       <c r="B128" s="25" t="s">
-        <v>71</v>
+        <v>611</v>
       </c>
       <c r="C128" s="25" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D128" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E128" s="25" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="24">
-        <v>5059340719528</v>
+        <v>5036581065218</v>
       </c>
       <c r="B129" s="25" t="s">
-        <v>69</v>
+        <v>612</v>
       </c>
       <c r="C129" s="25" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D129" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E129" s="25" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="24">
-        <v>5059340781976</v>
+        <v>8429991787646</v>
       </c>
       <c r="B130" s="25" t="s">
-        <v>65</v>
+        <v>613</v>
       </c>
       <c r="C130" s="25" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D130" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E130" s="25" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="24">
-        <v>5036581065201</v>
+        <v>8432712288490</v>
       </c>
       <c r="B131" s="25" t="s">
-        <v>614</v>
+        <v>81</v>
       </c>
       <c r="C131" s="25" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D131" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E131" s="25" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="24">
-        <v>5036581065218</v>
+        <v>8432712289541</v>
       </c>
       <c r="B132" s="25" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C132" s="25" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D132" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E132" s="25" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="24">
-        <v>8429991787646</v>
+        <v>8432712288551</v>
       </c>
       <c r="B133" s="25" t="s">
-        <v>616</v>
+        <v>77</v>
       </c>
       <c r="C133" s="25" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D133" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E133" s="25" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="24">
-        <v>8432712288490</v>
+        <v>8432712292367</v>
       </c>
       <c r="B134" s="25" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C134" s="25" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D134" s="25" t="s">
         <v>493</v>
@@ -18349,13 +18339,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="24">
-        <v>8432712289541</v>
+        <v>8432712288582</v>
       </c>
       <c r="B135" s="25" t="s">
-        <v>617</v>
+        <v>262</v>
       </c>
       <c r="C135" s="25" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D135" s="25" t="s">
         <v>493</v>
@@ -18366,13 +18356,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="24">
-        <v>8432712288551</v>
+        <v>8432712292398</v>
       </c>
       <c r="B136" s="25" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C136" s="25" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D136" s="25" t="s">
         <v>493</v>
@@ -18383,64 +18373,64 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="24">
-        <v>8432712292367</v>
+        <v>5059340719610</v>
       </c>
       <c r="B137" s="25" t="s">
-        <v>76</v>
+        <v>615</v>
       </c>
       <c r="C137" s="25" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D137" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E137" s="25" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="24">
-        <v>8432712288582</v>
+        <v>5059340719566</v>
       </c>
       <c r="B138" s="25" t="s">
-        <v>262</v>
+        <v>616</v>
       </c>
       <c r="C138" s="25" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D138" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E138" s="25" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="24">
-        <v>8432712292398</v>
+        <v>5059340719511</v>
       </c>
       <c r="B139" s="25" t="s">
-        <v>70</v>
+        <v>617</v>
       </c>
       <c r="C139" s="25" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D139" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E139" s="25" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="24">
-        <v>5059340719610</v>
+        <v>5063022525574</v>
       </c>
       <c r="B140" s="25" t="s">
         <v>618</v>
       </c>
       <c r="C140" s="25" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D140" s="25" t="s">
         <v>493</v>
@@ -18451,13 +18441,13 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="24">
-        <v>5059340719566</v>
+        <v>8435433537328</v>
       </c>
       <c r="B141" s="25" t="s">
         <v>619</v>
       </c>
       <c r="C141" s="25" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D141" s="25" t="s">
         <v>493</v>
@@ -18468,64 +18458,64 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="24">
-        <v>5059340719511</v>
+        <v>5063022638397</v>
       </c>
       <c r="B142" s="25" t="s">
-        <v>620</v>
+        <v>84</v>
       </c>
       <c r="C142" s="25" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D142" s="25" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E142" s="25" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="24">
-        <v>5063022525574</v>
+        <v>8429991787622</v>
       </c>
       <c r="B143" s="25" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C143" s="25" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D143" s="25" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E143" s="25" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="24">
-        <v>8435433537328</v>
+        <v>8429991792282</v>
       </c>
       <c r="B144" s="25" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C144" s="25" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D144" s="25" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E144" s="25" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="24">
-        <v>5063022638397</v>
+        <v>5059340719658</v>
       </c>
       <c r="B145" s="25" t="s">
-        <v>84</v>
+        <v>402</v>
       </c>
       <c r="C145" s="25" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D145" s="25" t="s">
         <v>496</v>
@@ -18536,115 +18526,115 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="24">
-        <v>8429991787622</v>
+        <v>5059340460277</v>
       </c>
       <c r="B146" s="25" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C146" s="25" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D146" s="25" t="s">
         <v>496</v>
       </c>
       <c r="E146" s="25" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="24">
-        <v>8429991792282</v>
+        <v>5059340460284</v>
       </c>
       <c r="B147" s="25" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C147" s="25" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D147" s="25" t="s">
         <v>496</v>
       </c>
       <c r="E147" s="25" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="24">
-        <v>5059340719658</v>
+        <v>5059340719535</v>
       </c>
       <c r="B148" s="25" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C148" s="25" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D148" s="25" t="s">
         <v>496</v>
       </c>
       <c r="E148" s="25" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="24">
-        <v>5059340460277</v>
+        <v>8429991787639</v>
       </c>
       <c r="B149" s="25" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C149" s="25" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D149" s="25" t="s">
         <v>496</v>
       </c>
       <c r="E149" s="25" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="24">
-        <v>5059340460284</v>
+        <v>8429991953584</v>
       </c>
       <c r="B150" s="25" t="s">
-        <v>626</v>
+        <v>39</v>
       </c>
       <c r="C150" s="25" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D150" s="25" t="s">
         <v>496</v>
       </c>
       <c r="E150" s="25" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="24">
-        <v>5059340719535</v>
+        <v>5059340781938</v>
       </c>
       <c r="B151" s="25" t="s">
-        <v>399</v>
+        <v>32</v>
       </c>
       <c r="C151" s="25" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D151" s="25" t="s">
         <v>496</v>
       </c>
       <c r="E151" s="25" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="24">
-        <v>8429991787639</v>
+        <v>5059340781921</v>
       </c>
       <c r="B152" s="25" t="s">
-        <v>627</v>
+        <v>75</v>
       </c>
       <c r="C152" s="25" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D152" s="25" t="s">
         <v>496</v>
@@ -18655,98 +18645,98 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="24">
-        <v>8429991953584</v>
+        <v>5059340854229</v>
       </c>
       <c r="B153" s="25" t="s">
-        <v>39</v>
+        <v>625</v>
       </c>
       <c r="C153" s="25" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D153" s="25" t="s">
         <v>496</v>
       </c>
       <c r="E153" s="25" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="24">
-        <v>5059340781938</v>
+        <v>5059340854205</v>
       </c>
       <c r="B154" s="25" t="s">
-        <v>32</v>
+        <v>276</v>
       </c>
       <c r="C154" s="25" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D154" s="25" t="s">
         <v>496</v>
       </c>
       <c r="E154" s="25" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="24">
-        <v>5059340781921</v>
+        <v>8435414125100</v>
       </c>
       <c r="B155" s="25" t="s">
-        <v>75</v>
+        <v>626</v>
       </c>
       <c r="C155" s="25" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D155" s="25" t="s">
         <v>496</v>
       </c>
       <c r="E155" s="25" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="24">
-        <v>5059340854229</v>
+        <v>8435414125131</v>
       </c>
       <c r="B156" s="25" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C156" s="25" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D156" s="25" t="s">
         <v>496</v>
       </c>
       <c r="E156" s="25" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="24">
-        <v>5059340854205</v>
+        <v>8435414124189</v>
       </c>
       <c r="B157" s="25" t="s">
-        <v>276</v>
+        <v>628</v>
       </c>
       <c r="C157" s="25" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D157" s="25" t="s">
         <v>496</v>
       </c>
       <c r="E157" s="25" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="24">
-        <v>8435414125100</v>
+        <v>8435414122574</v>
       </c>
       <c r="B158" s="25" t="s">
         <v>629</v>
       </c>
       <c r="C158" s="25" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D158" s="25" t="s">
         <v>496</v>
@@ -18757,13 +18747,13 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="24">
-        <v>8435414125131</v>
+        <v>8435414122468</v>
       </c>
       <c r="B159" s="25" t="s">
         <v>630</v>
       </c>
       <c r="C159" s="25" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D159" s="25" t="s">
         <v>496</v>
@@ -18774,868 +18764,817 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="24">
-        <v>8435414124189</v>
+        <v>5059340221700</v>
       </c>
       <c r="B160" s="25" t="s">
         <v>631</v>
       </c>
       <c r="C160" s="25" t="s">
-        <v>610</v>
+        <v>632</v>
       </c>
       <c r="D160" s="25" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="E160" s="25" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="24">
-        <v>8435414122574</v>
+        <v>5063022611239</v>
       </c>
       <c r="B161" s="25" t="s">
+        <v>633</v>
+      </c>
+      <c r="C161" s="25" t="s">
         <v>632</v>
       </c>
-      <c r="C161" s="25" t="s">
-        <v>610</v>
-      </c>
       <c r="D161" s="25" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="E161" s="25" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="24">
-        <v>8435414122468</v>
+        <v>5059340357447</v>
       </c>
       <c r="B162" s="25" t="s">
-        <v>633</v>
+        <v>219</v>
       </c>
       <c r="C162" s="25" t="s">
-        <v>610</v>
+        <v>632</v>
       </c>
       <c r="D162" s="25" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="E162" s="25" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="24">
-        <v>5059340221700</v>
+        <v>5059340357454</v>
       </c>
       <c r="B163" s="25" t="s">
         <v>634</v>
       </c>
       <c r="C163" s="25" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="D163" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E163" s="25" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="24">
-        <v>5063022611239</v>
+        <v>5059340357461</v>
       </c>
       <c r="B164" s="25" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C164" s="25" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="D164" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E164" s="25" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="24">
-        <v>5059340357447</v>
+        <v>5059340221717</v>
       </c>
       <c r="B165" s="25" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C165" s="25" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="D165" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E165" s="25" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="24">
-        <v>5059340357454</v>
+        <v>5059340802602</v>
       </c>
       <c r="B166" s="25" t="s">
-        <v>637</v>
+        <v>220</v>
       </c>
       <c r="C166" s="25" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="D166" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E166" s="25" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="24">
-        <v>5059340357461</v>
+        <v>5059340802367</v>
       </c>
       <c r="B167" s="25" t="s">
-        <v>638</v>
+        <v>217</v>
       </c>
       <c r="C167" s="25" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="D167" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E167" s="25" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="24">
-        <v>5059340221717</v>
+        <v>5059340802305</v>
       </c>
       <c r="B168" s="25" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C168" s="25" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="D168" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E168" s="25" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="24">
-        <v>5059340802602</v>
+        <v>5059340802626</v>
       </c>
       <c r="B169" s="25" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C169" s="25" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="D169" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E169" s="25" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="24">
-        <v>5059340802367</v>
+        <v>5059340802336</v>
       </c>
       <c r="B170" s="25" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C170" s="25" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="D170" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E170" s="25" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="24">
-        <v>5059340802305</v>
+        <v>5059340802923</v>
       </c>
       <c r="B171" s="25" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C171" s="25" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="D171" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E171" s="25" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="24">
-        <v>5059340802626</v>
+        <v>5059340802558</v>
       </c>
       <c r="B172" s="25" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="C172" s="25" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="D172" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E172" s="25" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="24">
-        <v>5059340802336</v>
+        <v>5059340802831</v>
       </c>
       <c r="B173" s="25" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C173" s="25" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="D173" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E173" s="25" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="24">
-        <v>5059340802923</v>
+        <v>5059340969657</v>
       </c>
       <c r="B174" s="25" t="s">
-        <v>227</v>
+        <v>636</v>
       </c>
       <c r="C174" s="25" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="D174" s="25" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E174" s="25" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="24">
-        <v>5059340802558</v>
+        <v>5059340969633</v>
       </c>
       <c r="B175" s="25" t="s">
-        <v>229</v>
+        <v>637</v>
       </c>
       <c r="C175" s="25" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="D175" s="25" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E175" s="25" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="24">
-        <v>5059340802831</v>
+        <v>5059340969640</v>
       </c>
       <c r="B176" s="25" t="s">
-        <v>228</v>
+        <v>638</v>
       </c>
       <c r="C176" s="25" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="D176" s="25" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E176" s="25" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="24">
-        <v>5059340969657</v>
+        <v>5059340969664</v>
       </c>
       <c r="B177" s="25" t="s">
         <v>639</v>
       </c>
       <c r="C177" s="25" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="D177" s="25" t="s">
         <v>496</v>
       </c>
       <c r="E177" s="25" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="24">
-        <v>5059340969633</v>
+        <v>5059340969626</v>
       </c>
       <c r="B178" s="25" t="s">
         <v>640</v>
       </c>
       <c r="C178" s="25" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="D178" s="25" t="s">
         <v>496</v>
       </c>
       <c r="E178" s="25" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="24">
-        <v>5059340969640</v>
+        <v>5059340802473</v>
       </c>
       <c r="B179" s="25" t="s">
-        <v>641</v>
+        <v>226</v>
       </c>
       <c r="C179" s="25" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="D179" s="25" t="s">
         <v>496</v>
       </c>
       <c r="E179" s="25" t="s">
-        <v>494</v>
+        <v>507</v>
       </c>
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="24">
-        <v>5059340969664</v>
+        <v>5059340802725</v>
       </c>
       <c r="B180" s="25" t="s">
-        <v>642</v>
+        <v>225</v>
       </c>
       <c r="C180" s="25" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="D180" s="25" t="s">
         <v>496</v>
       </c>
       <c r="E180" s="25" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="24">
-        <v>5059340969626</v>
+        <v>5059340803074</v>
       </c>
       <c r="B181" s="25" t="s">
-        <v>643</v>
+        <v>224</v>
       </c>
       <c r="C181" s="25" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="D181" s="25" t="s">
         <v>496</v>
       </c>
       <c r="E181" s="25" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="24">
-        <v>5059340802473</v>
+        <v>3663602997436</v>
       </c>
       <c r="B182" s="25" t="s">
-        <v>226</v>
+        <v>641</v>
       </c>
       <c r="C182" s="25" t="s">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="D182" s="25" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="E182" s="25" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="24">
-        <v>5059340802725</v>
+        <v>5063022047847</v>
       </c>
       <c r="B183" s="25" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="C183" s="25" t="s">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="D183" s="25" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="E183" s="25" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="24">
-        <v>5059340803074</v>
+        <v>5063022085658</v>
       </c>
       <c r="B184" s="25" t="s">
-        <v>224</v>
+        <v>643</v>
       </c>
       <c r="C184" s="25" t="s">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="D184" s="25" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="E184" s="25" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="24">
-        <v>3663602997436</v>
+        <v>3663602997962</v>
       </c>
       <c r="B185" s="25" t="s">
         <v>644</v>
       </c>
       <c r="C185" s="25" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="D185" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E185" s="25" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="24">
-        <v>5063022047847</v>
+        <v>5063022069450</v>
       </c>
       <c r="B186" s="25" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="C186" s="25" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="D186" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E186" s="25" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="24">
-        <v>5063022085658</v>
+        <v>5063022606525</v>
       </c>
       <c r="B187" s="25" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C187" s="25" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="D187" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E187" s="25" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="24">
-        <v>3663602997962</v>
+        <v>5063022047755</v>
       </c>
       <c r="B188" s="25" t="s">
-        <v>647</v>
+        <v>190</v>
       </c>
       <c r="C188" s="25" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="D188" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E188" s="25" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="24">
-        <v>5063022069450</v>
+        <v>5059340194042</v>
       </c>
       <c r="B189" s="25" t="s">
-        <v>191</v>
+        <v>646</v>
       </c>
       <c r="C189" s="25" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="D189" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E189" s="25" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="24">
-        <v>5063022606525</v>
+        <v>5063022606068</v>
       </c>
       <c r="B190" s="25" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C190" s="25" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="D190" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E190" s="25" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="24">
-        <v>5063022047755</v>
+        <v>5059340485362</v>
       </c>
       <c r="B191" s="25" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C191" s="25" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="D191" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E191" s="25" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="24">
-        <v>5059340194042</v>
+        <v>5063022085603</v>
       </c>
       <c r="B192" s="25" t="s">
-        <v>649</v>
+        <v>193</v>
       </c>
       <c r="C192" s="25" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="D192" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E192" s="25" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="24">
-        <v>5063022606068</v>
+        <v>5059340194080</v>
       </c>
       <c r="B193" s="25" t="s">
-        <v>650</v>
+        <v>199</v>
       </c>
       <c r="C193" s="25" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="D193" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E193" s="25" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="24">
-        <v>5059340485362</v>
+        <v>5059340216034</v>
       </c>
       <c r="B194" s="25" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="C194" s="25" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="D194" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E194" s="25" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="24">
-        <v>5063022085603</v>
+        <v>5059340194097</v>
       </c>
       <c r="B195" s="25" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="C195" s="25" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="D195" s="25" t="s">
         <v>493</v>
       </c>
       <c r="E195" s="25" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
     </row>
     <row r="196" spans="1:5">
       <c r="A196" s="24">
-        <v>5059340194080</v>
+        <v>5063022047830</v>
       </c>
       <c r="B196" s="25" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C196" s="25" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="D196" s="25" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E196" s="25" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="197" spans="1:5">
       <c r="A197" s="24">
-        <v>5059340216034</v>
+        <v>5063022085641</v>
       </c>
       <c r="B197" s="25" t="s">
-        <v>194</v>
+        <v>648</v>
       </c>
       <c r="C197" s="25" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="D197" s="25" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E197" s="25" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
     </row>
     <row r="198" spans="1:5">
       <c r="A198" s="24">
-        <v>5059340194097</v>
+        <v>5063022034496</v>
       </c>
       <c r="B198" s="25" t="s">
-        <v>185</v>
+        <v>649</v>
       </c>
       <c r="C198" s="25" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="D198" s="25" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E198" s="25" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
     </row>
     <row r="199" spans="1:5">
       <c r="A199" s="24">
-        <v>5063022047830</v>
+        <v>5059340391441</v>
       </c>
       <c r="B199" s="25" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C199" s="25" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="D199" s="25" t="s">
         <v>496</v>
       </c>
       <c r="E199" s="25" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="200" spans="1:5">
       <c r="A200" s="24">
-        <v>5063022085641</v>
+        <v>5063022606020</v>
       </c>
       <c r="B200" s="25" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C200" s="25" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="D200" s="25" t="s">
         <v>496</v>
       </c>
       <c r="E200" s="25" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
     </row>
     <row r="201" spans="1:5">
       <c r="A201" s="24">
-        <v>5063022034496</v>
+        <v>5063022606037</v>
       </c>
       <c r="B201" s="25" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C201" s="25" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="D201" s="25" t="s">
         <v>496</v>
       </c>
       <c r="E201" s="25" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="202" spans="1:5">
       <c r="A202" s="24">
-        <v>5059340391441</v>
+        <v>5063022606013</v>
       </c>
       <c r="B202" s="25" t="s">
-        <v>207</v>
+        <v>652</v>
       </c>
       <c r="C202" s="25" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="D202" s="25" t="s">
         <v>496</v>
       </c>
       <c r="E202" s="25" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="203" spans="1:5">
       <c r="A203" s="24">
-        <v>5063022606020</v>
+        <v>5063022047816</v>
       </c>
       <c r="B203" s="25" t="s">
-        <v>653</v>
+        <v>188</v>
       </c>
       <c r="C203" s="25" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="D203" s="25" t="s">
         <v>496</v>
       </c>
       <c r="E203" s="25" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
     </row>
     <row r="204" spans="1:5">
       <c r="A204" s="24">
-        <v>5063022606037</v>
+        <v>5059340484303</v>
       </c>
       <c r="B204" s="25" t="s">
-        <v>654</v>
+        <v>187</v>
       </c>
       <c r="C204" s="25" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="D204" s="25" t="s">
         <v>496</v>
       </c>
       <c r="E204" s="25" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
     </row>
     <row r="205" spans="1:5">
       <c r="A205" s="24">
-        <v>5063022606013</v>
+        <v>5063022047823</v>
       </c>
       <c r="B205" s="25" t="s">
-        <v>655</v>
+        <v>201</v>
       </c>
       <c r="C205" s="25" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="D205" s="25" t="s">
         <v>496</v>
       </c>
       <c r="E205" s="25" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="206" spans="1:5">
       <c r="A206" s="24">
-        <v>5063022047816</v>
+        <v>5059340194035</v>
       </c>
       <c r="B206" s="25" t="s">
-        <v>188</v>
+        <v>653</v>
       </c>
       <c r="C206" s="25" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="D206" s="25" t="s">
         <v>496</v>
       </c>
       <c r="E206" s="25" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
     </row>
     <row r="207" spans="1:5">
       <c r="A207" s="24">
-        <v>5059340484303</v>
+        <v>5059340194073</v>
       </c>
       <c r="B207" s="25" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C207" s="25" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="D207" s="25" t="s">
         <v>496</v>
       </c>
       <c r="E207" s="25" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="208" spans="1:5">
-      <c r="A208" s="24">
-        <v>5063022047823</v>
-      </c>
-      <c r="B208" s="25" t="s">
-        <v>201</v>
-      </c>
-      <c r="C208" s="25" t="s">
-        <v>645</v>
-      </c>
-      <c r="D208" s="25" t="s">
-        <v>496</v>
-      </c>
-      <c r="E208" s="25" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="209" spans="1:5">
-      <c r="A209" s="24">
-        <v>5059340194035</v>
-      </c>
-      <c r="B209" s="25" t="s">
-        <v>656</v>
-      </c>
-      <c r="C209" s="25" t="s">
-        <v>645</v>
-      </c>
-      <c r="D209" s="25" t="s">
-        <v>496</v>
-      </c>
-      <c r="E209" s="25" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="210" spans="1:5">
-      <c r="A210" s="24">
-        <v>5059340194073</v>
-      </c>
-      <c r="B210" s="25" t="s">
-        <v>183</v>
-      </c>
-      <c r="C210" s="25" t="s">
-        <v>645</v>
-      </c>
-      <c r="D210" s="25" t="s">
-        <v>496</v>
-      </c>
-      <c r="E210" s="25" t="s">
         <v>507</v>
       </c>
     </row>
